--- a/balance_tables/时间轴.xlsx
+++ b/balance_tables/时间轴.xlsx
@@ -8,17 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gameproduct\小厨西\balance_tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A31FEB1F-7D9A-44B1-BAD4-F502823CB0B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38E2EF53-B82D-49AA-97CC-6433C784A553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="配置" sheetId="1" r:id="rId1"/>
-    <sheet name="事件" sheetId="2" r:id="rId2"/>
-    <sheet name="说明" sheetId="3" r:id="rId3"/>
+    <sheet name="时间轴预览" sheetId="1" r:id="rId1"/>
+    <sheet name="配置" sheetId="2" r:id="rId2"/>
+    <sheet name="事件" sheetId="3" r:id="rId3"/>
+    <sheet name="说明" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -27,7 +37,139 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="120">
+  <si>
+    <t>小厨西 · 时间轴策划预览</t>
+  </si>
+  <si>
+    <t>黄色单元格在“配置 / 事件”页修改；本页全部自动联动。曲线表示全局基准胃口，实际食客胃口还会乘类型倍率与奖励百分位；事件时间是请求时刻，生成安全距离不足时可能顺延。</t>
+  </si>
+  <si>
+    <t>核心曲线参数</t>
+  </si>
+  <si>
+    <t>时间(s)</t>
+  </si>
+  <si>
+    <t>基准胃口</t>
+  </si>
+  <si>
+    <t>参数</t>
+  </si>
+  <si>
+    <t>当前值</t>
+  </si>
+  <si>
+    <t>事件概览</t>
+  </si>
+  <si>
+    <t>起始胃口</t>
+  </si>
+  <si>
+    <t>显式事件数</t>
+  </si>
+  <si>
+    <t>结束胃口</t>
+  </si>
+  <si>
+    <t>普通强化门数</t>
+  </si>
+  <si>
+    <t>增长结束时间(s)</t>
+  </si>
+  <si>
+    <t>精英请求时间(s)</t>
+  </si>
+  <si>
+    <t>增长指数</t>
+  </si>
+  <si>
+    <t>Boss 请求时间(s)</t>
+  </si>
+  <si>
+    <t>显式事件压力预览与调参说明</t>
+  </si>
+  <si>
+    <t>请求时间(s)</t>
+  </si>
+  <si>
+    <t>事件ID</t>
+  </si>
+  <si>
+    <t>类型</t>
+  </si>
+  <si>
+    <t>普通p0</t>
+  </si>
+  <si>
+    <t>普通p1</t>
+  </si>
+  <si>
+    <t>快速p0</t>
+  </si>
+  <si>
+    <t>远程p1</t>
+  </si>
+  <si>
+    <t>门基础范围</t>
+  </si>
+  <si>
+    <t>参数含义与修改方向</t>
+  </si>
+  <si>
+    <t>主要控制开局食客、开局门与漏怪伤害基准；降低它会直接放松前几十秒。</t>
+  </si>
+  <si>
+    <t>控制曲线封顶后的压力；主要影响中后段、精英与 Boss 前后的基础需求。</t>
+  </si>
+  <si>
+    <t>增长结束时间</t>
+  </si>
+  <si>
+    <t>基准胃口达到终点的时刻；时间越长，整条曲线爬升越慢。</t>
+  </si>
+  <si>
+    <t>1 为线性；大于 1 时前缓后陡，数值越大越把压力推迟到后段。</t>
+  </si>
+  <si>
+    <t>事件时间</t>
+  </si>
+  <si>
+    <t>只表示请求生成时刻；场上安全距离不足时会排队，因此实机出现可能稍晚。</t>
+  </si>
+  <si>
+    <t>普通波次</t>
+  </si>
+  <si>
+    <t>普通食客波次仍由 scripts/run.gd 的规则生成，不在本表逐条控制。</t>
+  </si>
+  <si>
+    <t>策划修改须知</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>只修改黄色单元格；预览页和蓝色公式区不需要手填。</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>保存并关闭 Excel 后，重新开始本局或重新运行 run.tscn 才会重新读取。</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>事件按行顺序读取，请求时间必须从小到大或相等；事件ID必须保持唯一且受支持。</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>文件缺失或数据非法时会回退到 data/timelines/vertical_slice.tres，并在输出面板提示。</t>
+  </si>
   <si>
     <t>参数ID</t>
   </si>
@@ -38,6 +180,12 @@
     <t>说明</t>
   </si>
   <si>
+    <t>对游戏的影响</t>
+  </si>
+  <si>
+    <t>修改建议</t>
+  </si>
+  <si>
     <t>schema_id</t>
   </si>
   <si>
@@ -47,43 +195,82 @@
     <t>表结构标识，请勿修改</t>
   </si>
   <si>
+    <t>用于确认这是小厨西时间轴表</t>
+  </si>
+  <si>
+    <t>不要修改</t>
+  </si>
+  <si>
     <t>schema_version</t>
   </si>
   <si>
     <t>表结构版本，请勿修改</t>
   </si>
   <si>
+    <t>用于识别表结构兼容性</t>
+  </si>
+  <si>
     <t>baseline_appetite_start</t>
   </si>
   <si>
     <t>基准胃口曲线起点</t>
   </si>
   <si>
+    <t>决定开局食客、门和漏怪伤害的基准</t>
+  </si>
+  <si>
+    <t>开局太难时优先降低</t>
+  </si>
+  <si>
     <t>baseline_appetite_end</t>
   </si>
   <si>
     <t>基准胃口曲线终点</t>
   </si>
   <si>
+    <t>决定曲线封顶后的中后期基础压力</t>
+  </si>
+  <si>
+    <t>后段太难时降低</t>
+  </si>
+  <si>
     <t>baseline_appetite_end_time</t>
   </si>
   <si>
     <t>达到终点胃口的时间（秒）</t>
   </si>
   <si>
+    <t>越大则整体增长越慢、封顶越晚</t>
+  </si>
+  <si>
+    <t>想延缓压力可提高</t>
+  </si>
+  <si>
     <t>baseline_appetite_exponent</t>
   </si>
   <si>
-    <t>曲线指数；大于 1 时前缓后陡</t>
-  </si>
-  <si>
-    <t>请求时间(s)</t>
-  </si>
-  <si>
-    <t>事件ID</t>
-  </si>
-  <si>
-    <t>类型</t>
+    <t>曲线指数</t>
+  </si>
+  <si>
+    <t>大于1时前缓后陡；1为线性</t>
+  </si>
+  <si>
+    <t>想让前期更松可提高</t>
+  </si>
+  <si>
+    <t>快速p1</t>
+  </si>
+  <si>
+    <t>远程p0</t>
+  </si>
+  <si>
+    <t>精英胃口</t>
+  </si>
+  <si>
+    <t>门基础最低</t>
+  </si>
+  <si>
+    <t>门基础最高</t>
   </si>
   <si>
     <t>start_gate</t>
@@ -92,12 +279,18 @@
     <t>开局食材门</t>
   </si>
   <si>
+    <t>开局食材门，提供第一组构筑选择</t>
+  </si>
+  <si>
     <t>gate_0</t>
   </si>
   <si>
     <t>普通强化门</t>
   </si>
   <si>
+    <t>普通强化门，请求后仍受安全生成距离约束</t>
+  </si>
+  <si>
     <t>gate_1</t>
   </si>
   <si>
@@ -119,6 +312,9 @@
     <t>精英</t>
   </si>
   <si>
+    <t>精英检查；满足后进入特殊强化选择</t>
+  </si>
+  <si>
     <t>gate_6</t>
   </si>
   <si>
@@ -143,25 +339,46 @@
     <t>Boss</t>
   </si>
   <si>
+    <t>Boss 检查；通过后进入胜利结算</t>
+  </si>
+  <si>
     <t>项目</t>
   </si>
   <si>
+    <t>推荐入口</t>
+  </si>
+  <si>
+    <t>先看“时间轴预览”页；到“配置 / 事件”页修改黄色单元格。</t>
+  </si>
+  <si>
     <t>生效方式</t>
   </si>
   <si>
-    <t>保存工作簿后，重新开始本局或重新运行 run.tscn；游戏启动时直接读取此文件。</t>
+    <t>保存并关闭工作簿后，重新开始本局或重新运行 run.tscn；游戏启动时直接读取此文件。</t>
+  </si>
+  <si>
+    <t>颜色含义</t>
+  </si>
+  <si>
+    <t>黄色是人工输入；蓝色是联动公式；绿色是说明或分类。</t>
   </si>
   <si>
     <t>输入规则</t>
   </si>
   <si>
-    <t>黄色单元格是输入。关键数值和事件时间请填写常量，不使用公式。</t>
+    <t>关键参数和事件时间必须填写常量，不要在黄色输入格使用公式。</t>
   </si>
   <si>
     <t>事件顺序</t>
   </si>
   <si>
     <t>事件按行顺序读取，请求时间必须从小到大或相等，事件ID不能为空。</t>
+  </si>
+  <si>
+    <t>预览范围</t>
+  </si>
+  <si>
+    <t>食客与门的数字用于观察压力。普通波次频率、随机百分位和安全生成延迟仍由游戏逻辑决定。</t>
   </si>
   <si>
     <t>失败回退</t>
@@ -189,10 +406,33 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF243238"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -210,6 +450,14 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF243238"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Carlito"/>
     </font>
@@ -220,7 +468,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -234,12 +482,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF3CD"/>
+        <fgColor rgb="FFF5F7F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2D6F6A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F0F8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE8F3EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9A441"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -283,63 +551,126 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="8" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="8" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="8" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="8" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -359,31 +690,323 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <c:style val="2"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr lang="zh-CN" altLang="en-US"/>
+              <a:t>基准胃口随时间增长</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="1"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>基准胃口</c:v>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>时间轴预览!$H$6:$H$15</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>135</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>时间轴预览!$I$6:$I$15</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>69</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>111</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>231</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>308</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>398</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>500</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-32EF-401A-818A-8948F3A7D2AC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="48650112"/>
+        <c:axId val="48672768"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="48650112"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:r>
+                  <a:rPr lang="zh-CN" altLang="en-US"/>
+                  <a:t>时间（秒）</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="1"/>
+        </c:title>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="48672768"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="48672768"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:r>
+                  <a:rPr lang="zh-CN" altLang="en-US"/>
+                  <a:t>基准胃口</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="1"/>
+        </c:title>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="48650112"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TimelineConfigTable" displayName="TimelineConfigTable" ref="A1:C7" totalsRowShown="0">
-  <tableColumns count="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TimelineConfigTable" displayName="TimelineConfigTable" ref="A1:E7" totalsRowShown="0">
+  <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="参数ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="数值"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="说明"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="对游戏的影响"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="修改建议"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="TimelineEventsTable" displayName="TimelineEventsTable" ref="A1:D16" totalsRowShown="0">
-  <tableColumns count="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="TimelineEventsTable" displayName="TimelineEventsTable" ref="A1:N16" totalsRowShown="0">
+  <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="请求时间(s)"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="事件ID"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="类型"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="说明"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="基准胃口"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="普通p0"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="普通p1"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="快速p0"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="快速p1"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="远程p0"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="远程p1"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="精英胃口"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="门基础最低"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="门基础最高"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="TimelineNotesTable" displayName="TimelineNotesTable" ref="A1:B7" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="TimelineNotesTable" displayName="TimelineNotesTable" ref="A1:B10" totalsRowShown="0">
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="项目"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="说明"/>
@@ -587,307 +1210,1423 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:Q42"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="48" customWidth="1"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="23" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="17" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="17" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="30" customHeight="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:17" ht="37.950000000000003" customHeight="1">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="38" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="38" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="38" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="38" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="38" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="38" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="38" t="s">
+        <v>0</v>
+      </c>
+      <c r="I1" s="38" t="s">
+        <v>0</v>
+      </c>
+      <c r="J1" s="38" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1" s="38" t="s">
+        <v>0</v>
+      </c>
+      <c r="L1" s="38" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1" s="38" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="38" t="s">
+        <v>0</v>
+      </c>
+      <c r="O1" s="38" t="s">
+        <v>0</v>
+      </c>
+      <c r="P1" s="38" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q1" s="38" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="24" customHeight="1">
+      <c r="A2" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B2" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="J2" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="K2" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="L2" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="N2" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="O2" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="P2" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="36" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" ht="24" customHeight="1">
+      <c r="A3" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="K3" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="L3" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="M3" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="N3" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="O3" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="P3" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="36" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="30" customHeight="1">
+      <c r="A5" s="37" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="15">
-      <c r="A2" s="2" t="s">
+      <c r="B5" s="37" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="37" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="37" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" s="37" t="s">
+        <v>2</v>
+      </c>
+      <c r="F5" s="37" t="s">
+        <v>2</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="I5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="2" t="s">
+    </row>
+    <row r="6" spans="1:17" ht="30" customHeight="1">
+      <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="15">
-      <c r="A3" s="3" t="s">
+      <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="8">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3" t="s">
+      <c r="D6" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="15">
-      <c r="A4" s="3" t="s">
+      <c r="E6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H6" s="11">
+        <f>配置!$B$6*0/9</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="14">
+        <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(H6/配置!$B$6,0),1),配置!$B$7),0)</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="15">
+      <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B7" s="8">
+        <f>配置!B4</f>
+        <v>15</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="11">
+        <f>COUNTA(事件!B2:B100)</f>
+        <v>15</v>
+      </c>
+      <c r="H7" s="12">
+        <f>配置!$B$6*1/9</f>
+        <v>15</v>
+      </c>
+      <c r="I7" s="15">
+        <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(H7/配置!$B$6,0),1),配置!$B$7),0)</f>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="15">
+      <c r="A8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="9">
+        <f>配置!B5</f>
+        <v>500</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="12">
+        <f>COUNTIF(事件!C2:C100,"普通强化门")</f>
+        <v>12</v>
+      </c>
+      <c r="H8" s="12">
+        <f>配置!$B$6*2/9</f>
+        <v>30</v>
+      </c>
+      <c r="I8" s="15">
+        <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(H8/配置!$B$6,0),1),配置!$B$7),0)</f>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="15">
+      <c r="A9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="9">
+        <f>配置!B6</f>
+        <v>135</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="12">
+        <f>SUMIF(事件!B2:B100,"elite",事件!A2:A100)</f>
+        <v>80</v>
+      </c>
+      <c r="H9" s="12">
+        <f>配置!$B$6*3/9</f>
+        <v>45</v>
+      </c>
+      <c r="I9" s="15">
+        <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(H9/配置!$B$6,0),1),配置!$B$7),0)</f>
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" ht="15">
+      <c r="A10" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="10">
+        <f>配置!B7</f>
+        <v>2</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="13">
+        <f>SUMIF(事件!B2:B100,"boss",事件!A2:A100)</f>
+        <v>135</v>
+      </c>
+      <c r="H10" s="12">
+        <f>配置!$B$6*4/9</f>
+        <v>60</v>
+      </c>
+      <c r="I10" s="15">
+        <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(H10/配置!$B$6,0),1),配置!$B$7),0)</f>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="15">
+      <c r="H11" s="12">
+        <f>配置!$B$6*5/9</f>
+        <v>75</v>
+      </c>
+      <c r="I11" s="15">
+        <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(H11/配置!$B$6,0),1),配置!$B$7),0)</f>
+        <v>165</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="15">
+      <c r="H12" s="12">
+        <f>配置!$B$6*6/9</f>
+        <v>90</v>
+      </c>
+      <c r="I12" s="15">
+        <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(H12/配置!$B$6,0),1),配置!$B$7),0)</f>
+        <v>231</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="15">
+      <c r="H13" s="12">
+        <f>配置!$B$6*7/9</f>
+        <v>105</v>
+      </c>
+      <c r="I13" s="15">
+        <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(H13/配置!$B$6,0),1),配置!$B$7),0)</f>
+        <v>308</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="15">
+      <c r="H14" s="12">
+        <f>配置!$B$6*8/9</f>
+        <v>120</v>
+      </c>
+      <c r="I14" s="15">
+        <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(H14/配置!$B$6,0),1),配置!$B$7),0)</f>
+        <v>398</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" ht="15">
+      <c r="H15" s="13">
+        <f>配置!$B$6*9/9</f>
+        <v>135</v>
+      </c>
+      <c r="I15" s="16">
+        <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(H15/配置!$B$6,0),1),配置!$B$7),0)</f>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="28.05" customHeight="1">
+      <c r="A20" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="F20" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="G20" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="H20" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="J20" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="K20" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="L20" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="M20" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="N20" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="O20" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="P20" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q20" s="37" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" ht="30" customHeight="1">
+      <c r="A21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="15">
-      <c r="A5" s="3" t="s">
+      <c r="F21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J21" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="K21" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="L21" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="M21" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="N21" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="O21" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="P21" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q21" s="39" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" ht="34.049999999999997" customHeight="1">
+      <c r="A22" s="11">
+        <f>事件!A2</f>
+        <v>2</v>
+      </c>
+      <c r="B22" s="5" t="str">
+        <f>事件!B2</f>
+        <v>start_gate</v>
+      </c>
+      <c r="C22" s="5" t="str">
+        <f>事件!C2</f>
+        <v>开局食材门</v>
+      </c>
+      <c r="D22" s="14">
+        <f>事件!E2</f>
+        <v>15</v>
+      </c>
+      <c r="E22" s="14">
+        <f>事件!F2</f>
+        <v>15</v>
+      </c>
+      <c r="F22" s="14">
+        <f>事件!G2</f>
+        <v>30</v>
+      </c>
+      <c r="G22" s="14">
+        <f>事件!H2</f>
+        <v>11</v>
+      </c>
+      <c r="H22" s="14">
+        <f>事件!K2</f>
+        <v>45</v>
+      </c>
+      <c r="I22" s="5" t="str">
+        <f>TEXT(事件!M2,"0")&amp;"–"&amp;TEXT(事件!N2,"0")</f>
+        <v>15–30</v>
+      </c>
+      <c r="J22" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="L22" s="36"/>
+      <c r="M22" s="36"/>
+      <c r="N22" s="36"/>
+      <c r="O22" s="36"/>
+      <c r="P22" s="36"/>
+      <c r="Q22" s="36"/>
+    </row>
+    <row r="23" spans="1:17" ht="34.049999999999997" customHeight="1">
+      <c r="A23" s="12">
+        <f>事件!A3</f>
+        <v>18</v>
+      </c>
+      <c r="B23" s="6" t="str">
+        <f>事件!B3</f>
+        <v>gate_0</v>
+      </c>
+      <c r="C23" s="6" t="str">
+        <f>事件!C3</f>
+        <v>普通强化门</v>
+      </c>
+      <c r="D23" s="15">
+        <f>事件!E3</f>
+        <v>24</v>
+      </c>
+      <c r="E23" s="15">
+        <f>事件!F3</f>
+        <v>24</v>
+      </c>
+      <c r="F23" s="15">
+        <f>事件!G3</f>
+        <v>48</v>
+      </c>
+      <c r="G23" s="15">
+        <f>事件!H3</f>
+        <v>18</v>
+      </c>
+      <c r="H23" s="15">
+        <f>事件!K3</f>
+        <v>72</v>
+      </c>
+      <c r="I23" s="6" t="str">
+        <f>TEXT(事件!M3,"0")&amp;"–"&amp;TEXT(事件!N3,"0")</f>
+        <v>24–48</v>
+      </c>
+      <c r="J23" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="8">
-        <v>300</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="15">
-      <c r="A6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="8">
+      <c r="K23" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="L23" s="36"/>
+      <c r="M23" s="36"/>
+      <c r="N23" s="36"/>
+      <c r="O23" s="36"/>
+      <c r="P23" s="36"/>
+      <c r="Q23" s="36"/>
+    </row>
+    <row r="24" spans="1:17" ht="34.049999999999997" customHeight="1">
+      <c r="A24" s="12">
+        <f>事件!A4</f>
+        <v>27</v>
+      </c>
+      <c r="B24" s="6" t="str">
+        <f>事件!B4</f>
+        <v>gate_1</v>
+      </c>
+      <c r="C24" s="6" t="str">
+        <f>事件!C4</f>
+        <v>普通强化门</v>
+      </c>
+      <c r="D24" s="15">
+        <f>事件!E4</f>
+        <v>34</v>
+      </c>
+      <c r="E24" s="15">
+        <f>事件!F4</f>
+        <v>34</v>
+      </c>
+      <c r="F24" s="15">
+        <f>事件!G4</f>
+        <v>68</v>
+      </c>
+      <c r="G24" s="15">
+        <f>事件!H4</f>
+        <v>26</v>
+      </c>
+      <c r="H24" s="15">
+        <f>事件!K4</f>
+        <v>102</v>
+      </c>
+      <c r="I24" s="6" t="str">
+        <f>TEXT(事件!M4,"0")&amp;"–"&amp;TEXT(事件!N4,"0")</f>
+        <v>34–68</v>
+      </c>
+      <c r="J24" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="K24" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="L24" s="36"/>
+      <c r="M24" s="36"/>
+      <c r="N24" s="36"/>
+      <c r="O24" s="36"/>
+      <c r="P24" s="36"/>
+      <c r="Q24" s="36"/>
+    </row>
+    <row r="25" spans="1:17" ht="34.049999999999997" customHeight="1">
+      <c r="A25" s="12">
+        <f>事件!A5</f>
+        <v>39</v>
+      </c>
+      <c r="B25" s="6" t="str">
+        <f>事件!B5</f>
+        <v>gate_2</v>
+      </c>
+      <c r="C25" s="6" t="str">
+        <f>事件!C5</f>
+        <v>普通强化门</v>
+      </c>
+      <c r="D25" s="15">
+        <f>事件!E5</f>
+        <v>55</v>
+      </c>
+      <c r="E25" s="15">
+        <f>事件!F5</f>
+        <v>55</v>
+      </c>
+      <c r="F25" s="15">
+        <f>事件!G5</f>
+        <v>110</v>
+      </c>
+      <c r="G25" s="15">
+        <f>事件!H5</f>
+        <v>41</v>
+      </c>
+      <c r="H25" s="15">
+        <f>事件!K5</f>
+        <v>165</v>
+      </c>
+      <c r="I25" s="6" t="str">
+        <f>TEXT(事件!M5,"0")&amp;"–"&amp;TEXT(事件!N5,"0")</f>
+        <v>55–110</v>
+      </c>
+      <c r="J25" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="K25" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="L25" s="36"/>
+      <c r="M25" s="36"/>
+      <c r="N25" s="36"/>
+      <c r="O25" s="36"/>
+      <c r="P25" s="36"/>
+      <c r="Q25" s="36"/>
+    </row>
+    <row r="26" spans="1:17" ht="34.049999999999997" customHeight="1">
+      <c r="A26" s="12">
+        <f>事件!A6</f>
+        <v>50</v>
+      </c>
+      <c r="B26" s="6" t="str">
+        <f>事件!B6</f>
+        <v>gate_3</v>
+      </c>
+      <c r="C26" s="6" t="str">
+        <f>事件!C6</f>
+        <v>普通强化门</v>
+      </c>
+      <c r="D26" s="15">
+        <f>事件!E6</f>
+        <v>82</v>
+      </c>
+      <c r="E26" s="15">
+        <f>事件!F6</f>
+        <v>82</v>
+      </c>
+      <c r="F26" s="15">
+        <f>事件!G6</f>
+        <v>164</v>
+      </c>
+      <c r="G26" s="15">
+        <f>事件!H6</f>
+        <v>62</v>
+      </c>
+      <c r="H26" s="15">
+        <f>事件!K6</f>
+        <v>246</v>
+      </c>
+      <c r="I26" s="6" t="str">
+        <f>TEXT(事件!M6,"0")&amp;"–"&amp;TEXT(事件!N6,"0")</f>
+        <v>82–164</v>
+      </c>
+      <c r="J26" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="K26" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="L26" s="36"/>
+      <c r="M26" s="36"/>
+      <c r="N26" s="36"/>
+      <c r="O26" s="36"/>
+      <c r="P26" s="36"/>
+      <c r="Q26" s="36"/>
+    </row>
+    <row r="27" spans="1:17" ht="34.049999999999997" customHeight="1">
+      <c r="A27" s="12">
+        <f>事件!A7</f>
+        <v>62</v>
+      </c>
+      <c r="B27" s="6" t="str">
+        <f>事件!B7</f>
+        <v>gate_4</v>
+      </c>
+      <c r="C27" s="6" t="str">
+        <f>事件!C7</f>
+        <v>普通强化门</v>
+      </c>
+      <c r="D27" s="15">
+        <f>事件!E7</f>
+        <v>117</v>
+      </c>
+      <c r="E27" s="15">
+        <f>事件!F7</f>
+        <v>117</v>
+      </c>
+      <c r="F27" s="15">
+        <f>事件!G7</f>
+        <v>234</v>
+      </c>
+      <c r="G27" s="15">
+        <f>事件!H7</f>
+        <v>88</v>
+      </c>
+      <c r="H27" s="15">
+        <f>事件!K7</f>
+        <v>351</v>
+      </c>
+      <c r="I27" s="6" t="str">
+        <f>TEXT(事件!M7,"0")&amp;"–"&amp;TEXT(事件!N7,"0")</f>
+        <v>117–234</v>
+      </c>
+      <c r="J27" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="K27" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="L27" s="36"/>
+      <c r="M27" s="36"/>
+      <c r="N27" s="36"/>
+      <c r="O27" s="36"/>
+      <c r="P27" s="36"/>
+      <c r="Q27" s="36"/>
+    </row>
+    <row r="28" spans="1:17" ht="15">
+      <c r="A28" s="12">
+        <f>事件!A8</f>
+        <v>74</v>
+      </c>
+      <c r="B28" s="6" t="str">
+        <f>事件!B8</f>
+        <v>gate_5</v>
+      </c>
+      <c r="C28" s="6" t="str">
+        <f>事件!C8</f>
+        <v>普通强化门</v>
+      </c>
+      <c r="D28" s="15">
+        <f>事件!E8</f>
+        <v>161</v>
+      </c>
+      <c r="E28" s="15">
+        <f>事件!F8</f>
+        <v>161</v>
+      </c>
+      <c r="F28" s="15">
+        <f>事件!G8</f>
+        <v>322</v>
+      </c>
+      <c r="G28" s="15">
+        <f>事件!H8</f>
+        <v>121</v>
+      </c>
+      <c r="H28" s="15">
+        <f>事件!K8</f>
+        <v>483</v>
+      </c>
+      <c r="I28" s="6" t="str">
+        <f>TEXT(事件!M8,"0")&amp;"–"&amp;TEXT(事件!N8,"0")</f>
+        <v>161–322</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" ht="15">
+      <c r="A29" s="12">
+        <f>事件!A9</f>
+        <v>80</v>
+      </c>
+      <c r="B29" s="6" t="str">
+        <f>事件!B9</f>
+        <v>elite</v>
+      </c>
+      <c r="C29" s="6" t="str">
+        <f>事件!C9</f>
+        <v>精英</v>
+      </c>
+      <c r="D29" s="15">
+        <f>事件!E9</f>
+        <v>185</v>
+      </c>
+      <c r="E29" s="15">
+        <f>事件!F9</f>
+        <v>185</v>
+      </c>
+      <c r="F29" s="15">
+        <f>事件!G9</f>
+        <v>370</v>
+      </c>
+      <c r="G29" s="15">
+        <f>事件!H9</f>
+        <v>139</v>
+      </c>
+      <c r="H29" s="15">
+        <f>事件!K9</f>
+        <v>555</v>
+      </c>
+      <c r="I29" s="6" t="str">
+        <f>TEXT(事件!M9,"0")&amp;"–"&amp;TEXT(事件!N9,"0")</f>
+        <v>185–370</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" ht="15">
+      <c r="A30" s="12">
+        <f>事件!A10</f>
+        <v>86</v>
+      </c>
+      <c r="B30" s="6" t="str">
+        <f>事件!B10</f>
+        <v>gate_6</v>
+      </c>
+      <c r="C30" s="6" t="str">
+        <f>事件!C10</f>
+        <v>普通强化门</v>
+      </c>
+      <c r="D30" s="15">
+        <f>事件!E10</f>
+        <v>212</v>
+      </c>
+      <c r="E30" s="15">
+        <f>事件!F10</f>
+        <v>212</v>
+      </c>
+      <c r="F30" s="15">
+        <f>事件!G10</f>
+        <v>424</v>
+      </c>
+      <c r="G30" s="15">
+        <f>事件!H10</f>
+        <v>159</v>
+      </c>
+      <c r="H30" s="15">
+        <f>事件!K10</f>
+        <v>636</v>
+      </c>
+      <c r="I30" s="6" t="str">
+        <f>TEXT(事件!M10,"0")&amp;"–"&amp;TEXT(事件!N10,"0")</f>
+        <v>212–424</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" ht="15">
+      <c r="A31" s="12">
+        <f>事件!A11</f>
+        <v>94</v>
+      </c>
+      <c r="B31" s="6" t="str">
+        <f>事件!B11</f>
+        <v>gate_7</v>
+      </c>
+      <c r="C31" s="6" t="str">
+        <f>事件!C11</f>
+        <v>普通强化门</v>
+      </c>
+      <c r="D31" s="15">
+        <f>事件!E11</f>
+        <v>250</v>
+      </c>
+      <c r="E31" s="15">
+        <f>事件!F11</f>
+        <v>250</v>
+      </c>
+      <c r="F31" s="15">
+        <f>事件!G11</f>
+        <v>500</v>
+      </c>
+      <c r="G31" s="15">
+        <f>事件!H11</f>
+        <v>188</v>
+      </c>
+      <c r="H31" s="15">
+        <f>事件!K11</f>
+        <v>750</v>
+      </c>
+      <c r="I31" s="6" t="str">
+        <f>TEXT(事件!M11,"0")&amp;"–"&amp;TEXT(事件!N11,"0")</f>
+        <v>250–500</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" ht="15">
+      <c r="A32" s="12">
+        <f>事件!A12</f>
+        <v>102</v>
+      </c>
+      <c r="B32" s="6" t="str">
+        <f>事件!B12</f>
+        <v>gate_8</v>
+      </c>
+      <c r="C32" s="6" t="str">
+        <f>事件!C12</f>
+        <v>普通强化门</v>
+      </c>
+      <c r="D32" s="15">
+        <f>事件!E12</f>
+        <v>292</v>
+      </c>
+      <c r="E32" s="15">
+        <f>事件!F12</f>
+        <v>292</v>
+      </c>
+      <c r="F32" s="15">
+        <f>事件!G12</f>
+        <v>584</v>
+      </c>
+      <c r="G32" s="15">
+        <f>事件!H12</f>
+        <v>219</v>
+      </c>
+      <c r="H32" s="15">
+        <f>事件!K12</f>
+        <v>876</v>
+      </c>
+      <c r="I32" s="6" t="str">
+        <f>TEXT(事件!M12,"0")&amp;"–"&amp;TEXT(事件!N12,"0")</f>
+        <v>292–584</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" ht="15">
+      <c r="A33" s="12">
+        <f>事件!A13</f>
+        <v>110</v>
+      </c>
+      <c r="B33" s="6" t="str">
+        <f>事件!B13</f>
+        <v>gate_9</v>
+      </c>
+      <c r="C33" s="6" t="str">
+        <f>事件!C13</f>
+        <v>普通强化门</v>
+      </c>
+      <c r="D33" s="15">
+        <f>事件!E13</f>
+        <v>337</v>
+      </c>
+      <c r="E33" s="15">
+        <f>事件!F13</f>
+        <v>337</v>
+      </c>
+      <c r="F33" s="15">
+        <f>事件!G13</f>
+        <v>674</v>
+      </c>
+      <c r="G33" s="15">
+        <f>事件!H13</f>
+        <v>253</v>
+      </c>
+      <c r="H33" s="15">
+        <f>事件!K13</f>
+        <v>1011</v>
+      </c>
+      <c r="I33" s="6" t="str">
+        <f>TEXT(事件!M13,"0")&amp;"–"&amp;TEXT(事件!N13,"0")</f>
+        <v>337–674</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" ht="15">
+      <c r="A34" s="12">
+        <f>事件!A14</f>
+        <v>118</v>
+      </c>
+      <c r="B34" s="6" t="str">
+        <f>事件!B14</f>
+        <v>gate_10</v>
+      </c>
+      <c r="C34" s="6" t="str">
+        <f>事件!C14</f>
+        <v>普通强化门</v>
+      </c>
+      <c r="D34" s="15">
+        <f>事件!E14</f>
+        <v>386</v>
+      </c>
+      <c r="E34" s="15">
+        <f>事件!F14</f>
+        <v>386</v>
+      </c>
+      <c r="F34" s="15">
+        <f>事件!G14</f>
+        <v>772</v>
+      </c>
+      <c r="G34" s="15">
+        <f>事件!H14</f>
+        <v>290</v>
+      </c>
+      <c r="H34" s="15">
+        <f>事件!K14</f>
+        <v>1158</v>
+      </c>
+      <c r="I34" s="6" t="str">
+        <f>TEXT(事件!M14,"0")&amp;"–"&amp;TEXT(事件!N14,"0")</f>
+        <v>386–772</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" ht="15">
+      <c r="A35" s="12">
+        <f>事件!A15</f>
+        <v>126</v>
+      </c>
+      <c r="B35" s="6" t="str">
+        <f>事件!B15</f>
+        <v>gate_11</v>
+      </c>
+      <c r="C35" s="6" t="str">
+        <f>事件!C15</f>
+        <v>普通强化门</v>
+      </c>
+      <c r="D35" s="15">
+        <f>事件!E15</f>
+        <v>437</v>
+      </c>
+      <c r="E35" s="15">
+        <f>事件!F15</f>
+        <v>437</v>
+      </c>
+      <c r="F35" s="15">
+        <f>事件!G15</f>
+        <v>874</v>
+      </c>
+      <c r="G35" s="15">
+        <f>事件!H15</f>
+        <v>328</v>
+      </c>
+      <c r="H35" s="15">
+        <f>事件!K15</f>
+        <v>1311</v>
+      </c>
+      <c r="I35" s="6" t="str">
+        <f>TEXT(事件!M15,"0")&amp;"–"&amp;TEXT(事件!N15,"0")</f>
+        <v>437–874</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" ht="15">
+      <c r="A36" s="13">
+        <f>事件!A16</f>
         <v>135</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="15">
-      <c r="A7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="9">
-        <v>1.6</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>15</v>
-      </c>
+      <c r="B36" s="7" t="str">
+        <f>事件!B16</f>
+        <v>boss</v>
+      </c>
+      <c r="C36" s="7" t="str">
+        <f>事件!C16</f>
+        <v>Boss</v>
+      </c>
+      <c r="D36" s="16">
+        <f>事件!E16</f>
+        <v>500</v>
+      </c>
+      <c r="E36" s="16">
+        <f>事件!F16</f>
+        <v>500</v>
+      </c>
+      <c r="F36" s="16">
+        <f>事件!G16</f>
+        <v>1000</v>
+      </c>
+      <c r="G36" s="16">
+        <f>事件!H16</f>
+        <v>375</v>
+      </c>
+      <c r="H36" s="16">
+        <f>事件!K16</f>
+        <v>1500</v>
+      </c>
+      <c r="I36" s="7" t="str">
+        <f>TEXT(事件!M16,"0")&amp;"–"&amp;TEXT(事件!N16,"0")</f>
+        <v>500–1000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" ht="28.05" customHeight="1">
+      <c r="A38" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="B38" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="C38" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="D38" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="E38" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="F38" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="G38" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="H38" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="I38" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="J38" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="K38" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="L38" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="M38" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="N38" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="O38" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="P38" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q38" s="37" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" ht="31.95" customHeight="1">
+      <c r="A39" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="B39" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="C39" s="36"/>
+      <c r="D39" s="36"/>
+      <c r="E39" s="36"/>
+      <c r="F39" s="36"/>
+      <c r="G39" s="36"/>
+      <c r="H39" s="36"/>
+      <c r="I39" s="36"/>
+      <c r="J39" s="36"/>
+      <c r="K39" s="36"/>
+      <c r="L39" s="36"/>
+      <c r="M39" s="36"/>
+      <c r="N39" s="36"/>
+      <c r="O39" s="36"/>
+      <c r="P39" s="36"/>
+      <c r="Q39" s="36"/>
+    </row>
+    <row r="40" spans="1:17" ht="31.95" customHeight="1">
+      <c r="A40" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="36" t="s">
+        <v>39</v>
+      </c>
+      <c r="C40" s="36"/>
+      <c r="D40" s="36"/>
+      <c r="E40" s="36"/>
+      <c r="F40" s="36"/>
+      <c r="G40" s="36"/>
+      <c r="H40" s="36"/>
+      <c r="I40" s="36"/>
+      <c r="J40" s="36"/>
+      <c r="K40" s="36"/>
+      <c r="L40" s="36"/>
+      <c r="M40" s="36"/>
+      <c r="N40" s="36"/>
+      <c r="O40" s="36"/>
+      <c r="P40" s="36"/>
+      <c r="Q40" s="36"/>
+    </row>
+    <row r="41" spans="1:17" ht="31.95" customHeight="1">
+      <c r="A41" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="C41" s="36"/>
+      <c r="D41" s="36"/>
+      <c r="E41" s="36"/>
+      <c r="F41" s="36"/>
+      <c r="G41" s="36"/>
+      <c r="H41" s="36"/>
+      <c r="I41" s="36"/>
+      <c r="J41" s="36"/>
+      <c r="K41" s="36"/>
+      <c r="L41" s="36"/>
+      <c r="M41" s="36"/>
+      <c r="N41" s="36"/>
+      <c r="O41" s="36"/>
+      <c r="P41" s="36"/>
+      <c r="Q41" s="36"/>
+    </row>
+    <row r="42" spans="1:17" ht="31.95" customHeight="1">
+      <c r="A42" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="C42" s="36"/>
+      <c r="D42" s="36"/>
+      <c r="E42" s="36"/>
+      <c r="F42" s="36"/>
+      <c r="G42" s="36"/>
+      <c r="H42" s="36"/>
+      <c r="I42" s="36"/>
+      <c r="J42" s="36"/>
+      <c r="K42" s="36"/>
+      <c r="L42" s="36"/>
+      <c r="M42" s="36"/>
+      <c r="N42" s="36"/>
+      <c r="O42" s="36"/>
+      <c r="P42" s="36"/>
+      <c r="Q42" s="36"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <mergeCells count="16">
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A2:Q3"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A20:Q20"/>
+    <mergeCell ref="J21:Q21"/>
+    <mergeCell ref="K22:Q22"/>
+    <mergeCell ref="K23:Q23"/>
+    <mergeCell ref="K24:Q24"/>
+    <mergeCell ref="K25:Q25"/>
+    <mergeCell ref="K26:Q26"/>
+    <mergeCell ref="B42:Q42"/>
+    <mergeCell ref="K27:Q27"/>
+    <mergeCell ref="A38:Q38"/>
+    <mergeCell ref="B39:Q39"/>
+    <mergeCell ref="B40:Q40"/>
+    <mergeCell ref="B41:Q41"/>
+  </mergeCells>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="46" customWidth="1"/>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="36" customWidth="1"/>
+    <col min="4" max="4" width="48" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="30" customHeight="1">
+    <row r="1" spans="1:5" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="34.049999999999997" customHeight="1">
+      <c r="A2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="24" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="34.049999999999997" customHeight="1">
+      <c r="A3" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" s="22">
+        <v>1</v>
+      </c>
+      <c r="C3" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="34.049999999999997" customHeight="1">
+      <c r="A4" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" s="22">
+        <v>15</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="25" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="34.049999999999997" customHeight="1">
+      <c r="A5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="22">
+        <v>500</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" s="25" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="34.049999999999997" customHeight="1">
+      <c r="A6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" s="22">
+        <v>135</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="34.049999999999997" customHeight="1">
+      <c r="A7" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" s="23">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="15">
-      <c r="A2" s="10">
-        <v>2</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" s="2"/>
-    </row>
-    <row r="3" spans="1:4" ht="15">
-      <c r="A3" s="11">
-        <v>18</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="3"/>
-    </row>
-    <row r="4" spans="1:4" ht="15">
-      <c r="A4" s="11">
-        <v>27</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="3"/>
-    </row>
-    <row r="5" spans="1:4" ht="15">
-      <c r="A5" s="11">
-        <v>39</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="3"/>
-    </row>
-    <row r="6" spans="1:4" ht="15">
-      <c r="A6" s="11">
-        <v>50</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="3"/>
-    </row>
-    <row r="7" spans="1:4" ht="15">
-      <c r="A7" s="11">
-        <v>62</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="3"/>
-    </row>
-    <row r="8" spans="1:4" ht="15">
-      <c r="A8" s="11">
-        <v>74</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="3"/>
-    </row>
-    <row r="9" spans="1:4" ht="15">
-      <c r="A9" s="11">
-        <v>80</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="3"/>
-    </row>
-    <row r="10" spans="1:4" ht="15">
-      <c r="A10" s="11">
-        <v>86</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="3"/>
-    </row>
-    <row r="11" spans="1:4" ht="15">
-      <c r="A11" s="11">
-        <v>94</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="3"/>
-    </row>
-    <row r="12" spans="1:4" ht="15">
-      <c r="A12" s="11">
-        <v>102</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="3"/>
-    </row>
-    <row r="13" spans="1:4" ht="15">
-      <c r="A13" s="11">
-        <v>110</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" s="3"/>
-    </row>
-    <row r="14" spans="1:4" ht="15">
-      <c r="A14" s="11">
-        <v>118</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="3"/>
-    </row>
-    <row r="15" spans="1:4" ht="15">
-      <c r="A15" s="11">
-        <v>126</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" s="3"/>
-    </row>
-    <row r="16" spans="1:4" ht="15">
-      <c r="A16" s="12">
-        <v>135</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D16" s="4"/>
+      <c r="C7" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="E7" s="26" t="s">
+        <v>72</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -897,71 +2636,972 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="44" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="11" width="12" customWidth="1"/>
+    <col min="12" max="14" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="30" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="31.95" customHeight="1">
+      <c r="A2" s="30">
+        <v>2</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="D2" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="E2" s="14">
+        <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A2/配置!$B$6,0),1),配置!$B$7),0)</f>
+        <v>15</v>
+      </c>
+      <c r="F2" s="14">
+        <f t="shared" ref="F2:F16" si="0">ROUND(E2,0)</f>
+        <v>15</v>
+      </c>
+      <c r="G2" s="14">
+        <f t="shared" ref="G2:G16" si="1">ROUND(E2*2,0)</f>
+        <v>30</v>
+      </c>
+      <c r="H2" s="14">
+        <f t="shared" ref="H2:H16" si="2">ROUND(E2*0.75,0)</f>
+        <v>11</v>
+      </c>
+      <c r="I2" s="14">
+        <f t="shared" ref="I2:I16" si="3">ROUND(E2*1.5,0)</f>
+        <v>23</v>
+      </c>
+      <c r="J2" s="14">
+        <f t="shared" ref="J2:J16" si="4">ROUND(E2*1.5,0)</f>
+        <v>23</v>
+      </c>
+      <c r="K2" s="14">
+        <f t="shared" ref="K2:K16" si="5">ROUND(E2*3,0)</f>
+        <v>45</v>
+      </c>
+      <c r="L2" s="14">
+        <f t="shared" ref="L2:L16" si="6">ROUND(E2*5.625,0)</f>
+        <v>84</v>
+      </c>
+      <c r="M2" s="14">
+        <f t="shared" ref="M2:M16" si="7">ROUND(E2,0)</f>
+        <v>15</v>
+      </c>
+      <c r="N2" s="14">
+        <f t="shared" ref="N2:N16" si="8">ROUND(E2*2,0)</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="31.95" customHeight="1">
+      <c r="A3" s="31">
+        <v>18</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="D3" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="E3" s="15">
+        <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A3/配置!$B$6,0),1),配置!$B$7),0)</f>
+        <v>24</v>
+      </c>
+      <c r="F3" s="15">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="G3" s="15">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="H3" s="15">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+      <c r="I3" s="15">
+        <f t="shared" si="3"/>
+        <v>36</v>
+      </c>
+      <c r="J3" s="15">
+        <f t="shared" si="4"/>
+        <v>36</v>
+      </c>
+      <c r="K3" s="15">
+        <f t="shared" si="5"/>
+        <v>72</v>
+      </c>
+      <c r="L3" s="15">
+        <f t="shared" si="6"/>
+        <v>135</v>
+      </c>
+      <c r="M3" s="15">
+        <f t="shared" si="7"/>
+        <v>24</v>
+      </c>
+      <c r="N3" s="15">
+        <f t="shared" si="8"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="31.95" customHeight="1">
+      <c r="A4" s="31">
+        <v>27</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="D4" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="E4" s="15">
+        <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A4/配置!$B$6,0),1),配置!$B$7),0)</f>
+        <v>34</v>
+      </c>
+      <c r="F4" s="15">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="G4" s="15">
+        <f t="shared" si="1"/>
+        <v>68</v>
+      </c>
+      <c r="H4" s="15">
+        <f t="shared" si="2"/>
+        <v>26</v>
+      </c>
+      <c r="I4" s="15">
+        <f t="shared" si="3"/>
+        <v>51</v>
+      </c>
+      <c r="J4" s="15">
+        <f t="shared" si="4"/>
+        <v>51</v>
+      </c>
+      <c r="K4" s="15">
+        <f t="shared" si="5"/>
+        <v>102</v>
+      </c>
+      <c r="L4" s="15">
+        <f t="shared" si="6"/>
+        <v>191</v>
+      </c>
+      <c r="M4" s="15">
+        <f t="shared" si="7"/>
+        <v>34</v>
+      </c>
+      <c r="N4" s="15">
+        <f t="shared" si="8"/>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="31.95" customHeight="1">
+      <c r="A5" s="31">
+        <v>39</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="D5" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="E5" s="15">
+        <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A5/配置!$B$6,0),1),配置!$B$7),0)</f>
+        <v>55</v>
+      </c>
+      <c r="F5" s="15">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="G5" s="15">
+        <f t="shared" si="1"/>
+        <v>110</v>
+      </c>
+      <c r="H5" s="15">
+        <f t="shared" si="2"/>
+        <v>41</v>
+      </c>
+      <c r="I5" s="15">
+        <f t="shared" si="3"/>
+        <v>83</v>
+      </c>
+      <c r="J5" s="15">
+        <f t="shared" si="4"/>
+        <v>83</v>
+      </c>
+      <c r="K5" s="15">
+        <f t="shared" si="5"/>
+        <v>165</v>
+      </c>
+      <c r="L5" s="15">
+        <f t="shared" si="6"/>
+        <v>309</v>
+      </c>
+      <c r="M5" s="15">
+        <f t="shared" si="7"/>
+        <v>55</v>
+      </c>
+      <c r="N5" s="15">
+        <f t="shared" si="8"/>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="31.95" customHeight="1">
+      <c r="A6" s="31">
+        <v>50</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="D6" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="E6" s="15">
+        <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A6/配置!$B$6,0),1),配置!$B$7),0)</f>
+        <v>82</v>
+      </c>
+      <c r="F6" s="15">
+        <f t="shared" si="0"/>
+        <v>82</v>
+      </c>
+      <c r="G6" s="15">
+        <f t="shared" si="1"/>
+        <v>164</v>
+      </c>
+      <c r="H6" s="15">
+        <f t="shared" si="2"/>
+        <v>62</v>
+      </c>
+      <c r="I6" s="15">
+        <f t="shared" si="3"/>
+        <v>123</v>
+      </c>
+      <c r="J6" s="15">
+        <f t="shared" si="4"/>
+        <v>123</v>
+      </c>
+      <c r="K6" s="15">
+        <f t="shared" si="5"/>
+        <v>246</v>
+      </c>
+      <c r="L6" s="15">
+        <f t="shared" si="6"/>
+        <v>461</v>
+      </c>
+      <c r="M6" s="15">
+        <f t="shared" si="7"/>
+        <v>82</v>
+      </c>
+      <c r="N6" s="15">
+        <f t="shared" si="8"/>
+        <v>164</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="31.95" customHeight="1">
+      <c r="A7" s="31">
+        <v>62</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="D7" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="E7" s="15">
+        <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A7/配置!$B$6,0),1),配置!$B$7),0)</f>
+        <v>117</v>
+      </c>
+      <c r="F7" s="15">
+        <f t="shared" si="0"/>
+        <v>117</v>
+      </c>
+      <c r="G7" s="15">
+        <f t="shared" si="1"/>
+        <v>234</v>
+      </c>
+      <c r="H7" s="15">
+        <f t="shared" si="2"/>
+        <v>88</v>
+      </c>
+      <c r="I7" s="15">
+        <f t="shared" si="3"/>
+        <v>176</v>
+      </c>
+      <c r="J7" s="15">
+        <f t="shared" si="4"/>
+        <v>176</v>
+      </c>
+      <c r="K7" s="15">
+        <f t="shared" si="5"/>
+        <v>351</v>
+      </c>
+      <c r="L7" s="15">
+        <f t="shared" si="6"/>
+        <v>658</v>
+      </c>
+      <c r="M7" s="15">
+        <f t="shared" si="7"/>
+        <v>117</v>
+      </c>
+      <c r="N7" s="15">
+        <f t="shared" si="8"/>
+        <v>234</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="31.95" customHeight="1">
+      <c r="A8" s="31">
+        <v>74</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="D8" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="E8" s="15">
+        <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A8/配置!$B$6,0),1),配置!$B$7),0)</f>
+        <v>161</v>
+      </c>
+      <c r="F8" s="15">
+        <f t="shared" si="0"/>
+        <v>161</v>
+      </c>
+      <c r="G8" s="15">
+        <f t="shared" si="1"/>
+        <v>322</v>
+      </c>
+      <c r="H8" s="15">
+        <f t="shared" si="2"/>
+        <v>121</v>
+      </c>
+      <c r="I8" s="15">
+        <f t="shared" si="3"/>
+        <v>242</v>
+      </c>
+      <c r="J8" s="15">
+        <f t="shared" si="4"/>
+        <v>242</v>
+      </c>
+      <c r="K8" s="15">
+        <f t="shared" si="5"/>
+        <v>483</v>
+      </c>
+      <c r="L8" s="15">
+        <f t="shared" si="6"/>
+        <v>906</v>
+      </c>
+      <c r="M8" s="15">
+        <f t="shared" si="7"/>
+        <v>161</v>
+      </c>
+      <c r="N8" s="15">
+        <f t="shared" si="8"/>
+        <v>322</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="31.95" customHeight="1">
+      <c r="A9" s="31">
+        <v>80</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="D9" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="E9" s="15">
+        <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A9/配置!$B$6,0),1),配置!$B$7),0)</f>
+        <v>185</v>
+      </c>
+      <c r="F9" s="15">
+        <f t="shared" si="0"/>
+        <v>185</v>
+      </c>
+      <c r="G9" s="15">
+        <f t="shared" si="1"/>
+        <v>370</v>
+      </c>
+      <c r="H9" s="15">
+        <f t="shared" si="2"/>
+        <v>139</v>
+      </c>
+      <c r="I9" s="15">
+        <f t="shared" si="3"/>
+        <v>278</v>
+      </c>
+      <c r="J9" s="15">
+        <f t="shared" si="4"/>
+        <v>278</v>
+      </c>
+      <c r="K9" s="15">
+        <f t="shared" si="5"/>
+        <v>555</v>
+      </c>
+      <c r="L9" s="15">
+        <f t="shared" si="6"/>
+        <v>1041</v>
+      </c>
+      <c r="M9" s="15">
+        <f t="shared" si="7"/>
+        <v>185</v>
+      </c>
+      <c r="N9" s="15">
+        <f t="shared" si="8"/>
+        <v>370</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="31.95" customHeight="1">
+      <c r="A10" s="31">
+        <v>86</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="D10" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="E10" s="15">
+        <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A10/配置!$B$6,0),1),配置!$B$7),0)</f>
+        <v>212</v>
+      </c>
+      <c r="F10" s="15">
+        <f t="shared" si="0"/>
+        <v>212</v>
+      </c>
+      <c r="G10" s="15">
+        <f t="shared" si="1"/>
+        <v>424</v>
+      </c>
+      <c r="H10" s="15">
+        <f t="shared" si="2"/>
+        <v>159</v>
+      </c>
+      <c r="I10" s="15">
+        <f t="shared" si="3"/>
+        <v>318</v>
+      </c>
+      <c r="J10" s="15">
+        <f t="shared" si="4"/>
+        <v>318</v>
+      </c>
+      <c r="K10" s="15">
+        <f t="shared" si="5"/>
+        <v>636</v>
+      </c>
+      <c r="L10" s="15">
+        <f t="shared" si="6"/>
+        <v>1193</v>
+      </c>
+      <c r="M10" s="15">
+        <f t="shared" si="7"/>
+        <v>212</v>
+      </c>
+      <c r="N10" s="15">
+        <f t="shared" si="8"/>
+        <v>424</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="31.95" customHeight="1">
+      <c r="A11" s="31">
+        <v>94</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="D11" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="E11" s="15">
+        <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A11/配置!$B$6,0),1),配置!$B$7),0)</f>
+        <v>250</v>
+      </c>
+      <c r="F11" s="15">
+        <f t="shared" si="0"/>
+        <v>250</v>
+      </c>
+      <c r="G11" s="15">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="H11" s="15">
+        <f t="shared" si="2"/>
+        <v>188</v>
+      </c>
+      <c r="I11" s="15">
+        <f t="shared" si="3"/>
+        <v>375</v>
+      </c>
+      <c r="J11" s="15">
+        <f t="shared" si="4"/>
+        <v>375</v>
+      </c>
+      <c r="K11" s="15">
+        <f t="shared" si="5"/>
+        <v>750</v>
+      </c>
+      <c r="L11" s="15">
+        <f t="shared" si="6"/>
+        <v>1406</v>
+      </c>
+      <c r="M11" s="15">
+        <f t="shared" si="7"/>
+        <v>250</v>
+      </c>
+      <c r="N11" s="15">
+        <f t="shared" si="8"/>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="31.95" customHeight="1">
+      <c r="A12" s="31">
+        <v>102</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="D12" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="E12" s="15">
+        <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A12/配置!$B$6,0),1),配置!$B$7),0)</f>
+        <v>292</v>
+      </c>
+      <c r="F12" s="15">
+        <f t="shared" si="0"/>
+        <v>292</v>
+      </c>
+      <c r="G12" s="15">
+        <f t="shared" si="1"/>
+        <v>584</v>
+      </c>
+      <c r="H12" s="15">
+        <f t="shared" si="2"/>
+        <v>219</v>
+      </c>
+      <c r="I12" s="15">
+        <f t="shared" si="3"/>
+        <v>438</v>
+      </c>
+      <c r="J12" s="15">
+        <f t="shared" si="4"/>
+        <v>438</v>
+      </c>
+      <c r="K12" s="15">
+        <f t="shared" si="5"/>
+        <v>876</v>
+      </c>
+      <c r="L12" s="15">
+        <f t="shared" si="6"/>
+        <v>1643</v>
+      </c>
+      <c r="M12" s="15">
+        <f t="shared" si="7"/>
+        <v>292</v>
+      </c>
+      <c r="N12" s="15">
+        <f t="shared" si="8"/>
+        <v>584</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="31.95" customHeight="1">
+      <c r="A13" s="31">
+        <v>110</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="D13" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="E13" s="15">
+        <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A13/配置!$B$6,0),1),配置!$B$7),0)</f>
+        <v>337</v>
+      </c>
+      <c r="F13" s="15">
+        <f t="shared" si="0"/>
+        <v>337</v>
+      </c>
+      <c r="G13" s="15">
+        <f t="shared" si="1"/>
+        <v>674</v>
+      </c>
+      <c r="H13" s="15">
+        <f t="shared" si="2"/>
+        <v>253</v>
+      </c>
+      <c r="I13" s="15">
+        <f t="shared" si="3"/>
+        <v>506</v>
+      </c>
+      <c r="J13" s="15">
+        <f t="shared" si="4"/>
+        <v>506</v>
+      </c>
+      <c r="K13" s="15">
+        <f t="shared" si="5"/>
+        <v>1011</v>
+      </c>
+      <c r="L13" s="15">
+        <f t="shared" si="6"/>
+        <v>1896</v>
+      </c>
+      <c r="M13" s="15">
+        <f t="shared" si="7"/>
+        <v>337</v>
+      </c>
+      <c r="N13" s="15">
+        <f t="shared" si="8"/>
+        <v>674</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="31.95" customHeight="1">
+      <c r="A14" s="31">
+        <v>118</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="E14" s="15">
+        <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A14/配置!$B$6,0),1),配置!$B$7),0)</f>
+        <v>386</v>
+      </c>
+      <c r="F14" s="15">
+        <f t="shared" si="0"/>
+        <v>386</v>
+      </c>
+      <c r="G14" s="15">
+        <f t="shared" si="1"/>
+        <v>772</v>
+      </c>
+      <c r="H14" s="15">
+        <f t="shared" si="2"/>
+        <v>290</v>
+      </c>
+      <c r="I14" s="15">
+        <f t="shared" si="3"/>
+        <v>579</v>
+      </c>
+      <c r="J14" s="15">
+        <f t="shared" si="4"/>
+        <v>579</v>
+      </c>
+      <c r="K14" s="15">
+        <f t="shared" si="5"/>
+        <v>1158</v>
+      </c>
+      <c r="L14" s="15">
+        <f t="shared" si="6"/>
+        <v>2171</v>
+      </c>
+      <c r="M14" s="15">
+        <f t="shared" si="7"/>
+        <v>386</v>
+      </c>
+      <c r="N14" s="15">
+        <f t="shared" si="8"/>
+        <v>772</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="31.95" customHeight="1">
+      <c r="A15" s="31">
+        <v>126</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="C15" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="E15" s="15">
+        <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A15/配置!$B$6,0),1),配置!$B$7),0)</f>
+        <v>437</v>
+      </c>
+      <c r="F15" s="15">
+        <f t="shared" si="0"/>
+        <v>437</v>
+      </c>
+      <c r="G15" s="15">
+        <f t="shared" si="1"/>
+        <v>874</v>
+      </c>
+      <c r="H15" s="15">
+        <f t="shared" si="2"/>
+        <v>328</v>
+      </c>
+      <c r="I15" s="15">
+        <f t="shared" si="3"/>
+        <v>656</v>
+      </c>
+      <c r="J15" s="15">
+        <f t="shared" si="4"/>
+        <v>656</v>
+      </c>
+      <c r="K15" s="15">
+        <f t="shared" si="5"/>
+        <v>1311</v>
+      </c>
+      <c r="L15" s="15">
+        <f t="shared" si="6"/>
+        <v>2458</v>
+      </c>
+      <c r="M15" s="15">
+        <f t="shared" si="7"/>
+        <v>437</v>
+      </c>
+      <c r="N15" s="15">
+        <f t="shared" si="8"/>
+        <v>874</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="31.95" customHeight="1">
+      <c r="A16" s="32">
+        <v>135</v>
+      </c>
+      <c r="B16" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="C16" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="D16" s="35" t="s">
+        <v>100</v>
+      </c>
+      <c r="E16" s="16">
+        <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A16/配置!$B$6,0),1),配置!$B$7),0)</f>
+        <v>500</v>
+      </c>
+      <c r="F16" s="16">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+      <c r="G16" s="16">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="H16" s="16">
+        <f t="shared" si="2"/>
+        <v>375</v>
+      </c>
+      <c r="I16" s="16">
+        <f t="shared" si="3"/>
+        <v>750</v>
+      </c>
+      <c r="J16" s="16">
+        <f t="shared" si="4"/>
+        <v>750</v>
+      </c>
+      <c r="K16" s="16">
+        <f t="shared" si="5"/>
+        <v>1500</v>
+      </c>
+      <c r="L16" s="16">
+        <f t="shared" si="6"/>
+        <v>2813</v>
+      </c>
+      <c r="M16" s="16">
+        <f t="shared" si="7"/>
+        <v>500</v>
+      </c>
+      <c r="N16" s="16">
+        <f t="shared" si="8"/>
+        <v>1000</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="88" customWidth="1"/>
+    <col min="2" max="2" width="92" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>101</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="42" customHeight="1">
-      <c r="A2" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>40</v>
+      <c r="A2" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="42" customHeight="1">
-      <c r="A3" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>42</v>
+      <c r="A3" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" s="25" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="42" customHeight="1">
-      <c r="A4" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>44</v>
+      <c r="A4" s="28" t="s">
+        <v>106</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="42" customHeight="1">
-      <c r="A5" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>46</v>
+      <c r="A5" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="42" customHeight="1">
-      <c r="A6" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>48</v>
+      <c r="A6" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="42" customHeight="1">
-      <c r="A7" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>50</v>
+      <c r="A7" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="42" customHeight="1">
+      <c r="A8" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="42" customHeight="1">
+      <c r="A9" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="42" customHeight="1">
+      <c r="A10" s="29" t="s">
+        <v>118</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">

--- a/balance_tables/时间轴.xlsx
+++ b/balance_tables/时间轴.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gameproduct\小厨西\balance_tables\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38E2EF53-B82D-49AA-97CC-6433C784A553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="24750" windowHeight="12080" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="时间轴预览" sheetId="1" r:id="rId1"/>
@@ -27,10 +21,9 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -402,28 +395,38 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.0"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF243238"/>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="18"/>
       <color rgb="FFFFFFFF"/>
       <name val="Microsoft YaHei"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF243238"/>
-      <name val="Microsoft YaHei"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -431,22 +434,6 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Microsoft YaHei"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Microsoft YaHei"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF243238"/>
-      <name val="Microsoft YaHei"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -454,21 +441,161 @@
       <sz val="10"/>
       <color rgb="FF243238"/>
       <name val="Microsoft YaHei"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Carlito"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -478,40 +605,233 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF243238"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F3EC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF3CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F0F8"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF5F7F6"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2D6F6A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7F0F8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE8F3EC"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9A441"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF3CD"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -548,168 +868,470 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="4" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="5" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="4" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="5" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="4" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="5" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="4" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="4" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="5" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="5" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="5" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="8" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="8" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="8" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="8" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal" xfId="49"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
   <c:lang val="zh-CN"/>
   <c:roundedCorners val="0"/>
-  <c:style val="2"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr/>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
+            <a:pPr>
+              <a:defRPr lang="zh-CN" sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
             <a:r>
               <a:rPr lang="zh-CN" altLang="en-US"/>
               <a:t>基准胃口随时间增长</a:t>
             </a:r>
+            <a:endParaRPr lang="zh-CN" altLang="en-US"/>
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="1"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -722,45 +1344,126 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>基准胃口</c:v>
+            <c:strRef>
+              <c:f>"基准胃口"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>基准胃口</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:marker>
+              <c:symbol val="none"/>
+            </c:marker>
+            <c:bubble3D val="0"/>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:marker>
+              <c:symbol val="none"/>
+            </c:marker>
+            <c:bubble3D val="0"/>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:marker>
+              <c:symbol val="none"/>
+            </c:marker>
+            <c:bubble3D val="0"/>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:marker>
+              <c:symbol val="none"/>
+            </c:marker>
+            <c:bubble3D val="0"/>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:marker>
+              <c:symbol val="none"/>
+            </c:marker>
+            <c:bubble3D val="0"/>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:marker>
+              <c:symbol val="none"/>
+            </c:marker>
+            <c:bubble3D val="0"/>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="6"/>
+            <c:marker>
+              <c:symbol val="none"/>
+            </c:marker>
+            <c:bubble3D val="0"/>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="7"/>
+            <c:marker>
+              <c:symbol val="none"/>
+            </c:marker>
+            <c:bubble3D val="0"/>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="8"/>
+            <c:marker>
+              <c:symbol val="none"/>
+            </c:marker>
+            <c:bubble3D val="0"/>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="9"/>
+            <c:marker>
+              <c:symbol val="none"/>
+            </c:marker>
+            <c:bubble3D val="0"/>
+          </c:dPt>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
           <c:cat>
             <c:numRef>
               <c:f>时间轴预览!$H$6:$H$15</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="10"/>
-                <c:pt idx="0">
+                <c:pt idx="0" c:formatCode="0.0">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="1" c:formatCode="0.0">
                   <c:v>15</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="2" c:formatCode="0.0">
                   <c:v>30</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="3" c:formatCode="0.0">
                   <c:v>45</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="4" c:formatCode="0.0">
                   <c:v>60</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="5" c:formatCode="0.0">
                   <c:v>75</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="6" c:formatCode="0.0">
                   <c:v>90</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="7" c:formatCode="0.0">
                   <c:v>105</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="8" c:formatCode="0.0">
                   <c:v>120</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="9" c:formatCode="0.0">
                   <c:v>135</c:v>
                 </c:pt>
               </c:numCache>
@@ -776,41 +1479,36 @@
                   <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>21</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>39</c:v>
+                  <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>69</c:v>
+                  <c:v>58</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>111</c:v>
+                  <c:v>91</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>165</c:v>
+                  <c:v>134</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>231</c:v>
+                  <c:v>186</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>308</c:v>
+                  <c:v>248</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>398</c:v>
+                  <c:v>319</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>500</c:v>
+                  <c:v>400</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-32EF-401A-818A-8948F3A7D2AC}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -820,7 +1518,8 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:smooth val="0"/>
+        <c:marker val="0"/>
+        <c:smooth val="1"/>
         <c:axId val="48650112"/>
         <c:axId val="48672768"/>
       </c:lineChart>
@@ -838,28 +1537,57 @@
                 <a:srgbClr val="CCCCCC"/>
               </a:solidFill>
               <a:prstDash val="dash"/>
+              <a:round/>
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr/>
+              <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
+                <a:pPr>
+                  <a:defRPr lang="zh-CN" sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
                 <a:r>
                   <a:rPr lang="zh-CN" altLang="en-US"/>
                   <a:t>时间（秒）</a:t>
                 </a:r>
+                <a:endParaRPr lang="zh-CN" altLang="en-US"/>
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="1"/>
         </c:title>
         <c:numFmt formatCode="0.0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="zh-CN" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
         <c:crossAx val="48672768"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
@@ -882,28 +1610,57 @@
                 <a:srgbClr val="CCCCCC"/>
               </a:solidFill>
               <a:prstDash val="dash"/>
+              <a:round/>
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr/>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
+                <a:pPr>
+                  <a:defRPr lang="zh-CN" sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
                 <a:r>
                   <a:rPr lang="zh-CN" altLang="en-US"/>
                   <a:t>基准胃口</a:t>
                 </a:r>
+                <a:endParaRPr lang="zh-CN" altLang="en-US"/>
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="1"/>
         </c:title>
         <c:numFmt formatCode="0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="zh-CN" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
         <c:crossAx val="48650112"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
@@ -912,6 +1669,11 @@
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="zero"/>
     <c:showDLblsOverMax val="1"/>
+    <c:extLst>
+      <c:ext uri="{0b15fc19-7d7d-44ad-8c2d-2c3a37ce22c3}">
+        <chartProps xmlns="https://web.wps.cn/et/2018/main" chartId="{820bf882-ab9c-443d-ad3c-c572de86ced5}"/>
+      </c:ext>
+    </c:extLst>
   </c:chart>
   <c:spPr>
     <a:ln w="9525">
@@ -919,8 +1681,18 @@
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
       <a:prstDash val="solid"/>
+      <a:round/>
     </a:ln>
   </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="zh-CN"/>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
@@ -930,7 +1702,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
@@ -944,20 +1716,14 @@
       <xdr:row>18</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame macro="">
+    <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2" name="Chart"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
+        <a:off x="12115800" y="1269365"/>
+        <a:ext cx="6934200" cy="2952750"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -971,45 +1737,45 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TimelineConfigTable" displayName="TimelineConfigTable" ref="A1:E7" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TimelineConfigTable" displayName="TimelineConfigTable" ref="A1:E7" totalsRowShown="0">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="参数ID"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="数值"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="说明"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="对游戏的影响"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="修改建议"/>
+    <tableColumn id="1" name="参数ID"/>
+    <tableColumn id="2" name="数值"/>
+    <tableColumn id="3" name="说明"/>
+    <tableColumn id="4" name="对游戏的影响"/>
+    <tableColumn id="5" name="修改建议"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="TimelineEventsTable" displayName="TimelineEventsTable" ref="A1:N16" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TimelineEventsTable" displayName="TimelineEventsTable" ref="A1:N16" totalsRowShown="0">
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="请求时间(s)"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="事件ID"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="类型"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="说明"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="基准胃口"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="普通p0"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="普通p1"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="快速p0"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="快速p1"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="远程p0"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="远程p1"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="精英胃口"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="门基础最低"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="门基础最高"/>
+    <tableColumn id="1" name="请求时间(s)"/>
+    <tableColumn id="2" name="事件ID"/>
+    <tableColumn id="3" name="类型"/>
+    <tableColumn id="4" name="说明"/>
+    <tableColumn id="5" name="基准胃口"/>
+    <tableColumn id="6" name="普通p0"/>
+    <tableColumn id="7" name="普通p1"/>
+    <tableColumn id="8" name="快速p0"/>
+    <tableColumn id="9" name="快速p1"/>
+    <tableColumn id="10" name="远程p0"/>
+    <tableColumn id="11" name="远程p1"/>
+    <tableColumn id="12" name="精英胃口"/>
+    <tableColumn id="13" name="门基础最低"/>
+    <tableColumn id="14" name="门基础最高"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="TimelineNotesTable" displayName="TimelineNotesTable" ref="A1:B10" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="TimelineNotesTable" displayName="TimelineNotesTable" ref="A1:B10" totalsRowShown="0">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="项目"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="说明"/>
+    <tableColumn id="1" name="项目"/>
+    <tableColumn id="2" name="说明"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1204,14 +1970,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:Q42"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>
@@ -1223,182 +1989,182 @@
     <col min="11" max="17" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="37.950000000000003" customHeight="1">
-      <c r="A1" s="38" t="s">
+    <row r="1" ht="37.95" customHeight="1" spans="1:17">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="38" t="s">
+      <c r="B1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="38" t="s">
+      <c r="C1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="38" t="s">
+      <c r="D1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="38" t="s">
+      <c r="E1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="38" t="s">
+      <c r="F1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="38" t="s">
+      <c r="G1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="38" t="s">
+      <c r="H1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="38" t="s">
+      <c r="I1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="J1" s="38" t="s">
+      <c r="J1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="K1" s="38" t="s">
+      <c r="K1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="L1" s="38" t="s">
+      <c r="L1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="M1" s="38" t="s">
+      <c r="M1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="N1" s="38" t="s">
+      <c r="N1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="O1" s="38" t="s">
+      <c r="O1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="P1" s="38" t="s">
+      <c r="P1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="Q1" s="38" t="s">
+      <c r="Q1" s="25" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="24" customHeight="1">
-      <c r="A2" s="36" t="s">
+    <row r="2" ht="24" customHeight="1" spans="1:17">
+      <c r="A2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="36" t="s">
+      <c r="C2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="36" t="s">
+      <c r="D2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="36" t="s">
+      <c r="E2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="36" t="s">
+      <c r="F2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="36" t="s">
+      <c r="G2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="36" t="s">
+      <c r="H2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="I2" s="36" t="s">
+      <c r="I2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="36" t="s">
+      <c r="J2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="K2" s="36" t="s">
+      <c r="K2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="L2" s="36" t="s">
+      <c r="L2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="M2" s="36" t="s">
+      <c r="M2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="N2" s="36" t="s">
+      <c r="N2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="36" t="s">
+      <c r="O2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="P2" s="36" t="s">
+      <c r="P2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="Q2" s="36" t="s">
+      <c r="Q2" s="26" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="24" customHeight="1">
-      <c r="A3" s="36" t="s">
+    <row r="3" ht="24" customHeight="1" spans="1:17">
+      <c r="A3" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="36" t="s">
+      <c r="B3" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="36" t="s">
+      <c r="C3" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="36" t="s">
+      <c r="D3" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="36" t="s">
+      <c r="E3" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="36" t="s">
+      <c r="F3" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="36" t="s">
+      <c r="G3" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="H3" s="36" t="s">
+      <c r="H3" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="I3" s="36" t="s">
+      <c r="I3" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="J3" s="36" t="s">
+      <c r="J3" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="K3" s="36" t="s">
+      <c r="K3" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="L3" s="36" t="s">
+      <c r="L3" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="M3" s="36" t="s">
+      <c r="M3" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="N3" s="36" t="s">
+      <c r="N3" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="O3" s="36" t="s">
+      <c r="O3" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="P3" s="36" t="s">
+      <c r="P3" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="Q3" s="36" t="s">
+      <c r="Q3" s="26" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="30" customHeight="1">
-      <c r="A5" s="37" t="s">
+    <row r="5" ht="30" customHeight="1" spans="1:17">
+      <c r="A5" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="37" t="s">
+      <c r="B5" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="37" t="s">
+      <c r="C5" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="37" t="s">
+      <c r="D5" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="37" t="s">
+      <c r="E5" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="37" t="s">
+      <c r="F5" s="27" t="s">
         <v>2</v>
       </c>
       <c r="H5" s="1" t="s">
@@ -1408,7 +2174,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="30" customHeight="1">
+    <row r="6" ht="30" customHeight="1" spans="1:17">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -1421,215 +2187,215 @@
       <c r="E6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H6" s="11">
+      <c r="H6" s="28">
         <f>配置!$B$6*0/9</f>
         <v>0</v>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="11">
         <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(H6/配置!$B$6,0),1),配置!$B$7),0)</f>
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15">
-      <c r="A7" s="2" t="s">
+    <row r="7" ht="14.5" spans="1:17">
+      <c r="A7" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="29">
         <f>配置!B4</f>
         <v>15</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="28">
         <f>COUNTA(事件!B2:B100)</f>
         <v>15</v>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="30">
         <f>配置!$B$6*1/9</f>
         <v>15</v>
       </c>
       <c r="I7" s="15">
         <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(H7/配置!$B$6,0),1),配置!$B$7),0)</f>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" ht="15">
-      <c r="A8" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" ht="14.5" spans="1:17">
+      <c r="A8" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="31">
         <f>配置!B5</f>
-        <v>500</v>
-      </c>
-      <c r="D8" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="D8" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="30">
         <f>COUNTIF(事件!C2:C100,"普通强化门")</f>
         <v>12</v>
       </c>
-      <c r="H8" s="12">
+      <c r="H8" s="30">
         <f>配置!$B$6*2/9</f>
         <v>30</v>
       </c>
       <c r="I8" s="15">
         <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(H8/配置!$B$6,0),1),配置!$B$7),0)</f>
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" ht="15">
-      <c r="A9" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" ht="14.5" spans="1:17">
+      <c r="A9" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="31">
         <f>配置!B6</f>
         <v>135</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="30">
         <f>SUMIF(事件!B2:B100,"elite",事件!A2:A100)</f>
         <v>80</v>
       </c>
-      <c r="H9" s="12">
+      <c r="H9" s="30">
         <f>配置!$B$6*3/9</f>
         <v>45</v>
       </c>
       <c r="I9" s="15">
         <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(H9/配置!$B$6,0),1),配置!$B$7),0)</f>
-        <v>69</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" ht="15">
-      <c r="A10" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" ht="14.5" spans="1:17">
+      <c r="A10" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="32">
         <f>配置!B7</f>
         <v>2</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="33">
         <f>SUMIF(事件!B2:B100,"boss",事件!A2:A100)</f>
         <v>135</v>
       </c>
-      <c r="H10" s="12">
+      <c r="H10" s="30">
         <f>配置!$B$6*4/9</f>
         <v>60</v>
       </c>
       <c r="I10" s="15">
         <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(H10/配置!$B$6,0),1),配置!$B$7),0)</f>
-        <v>111</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" ht="15">
-      <c r="H11" s="12">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" ht="14.5" spans="1:17">
+      <c r="H11" s="30">
         <f>配置!$B$6*5/9</f>
         <v>75</v>
       </c>
       <c r="I11" s="15">
         <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(H11/配置!$B$6,0),1),配置!$B$7),0)</f>
-        <v>165</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" ht="15">
-      <c r="H12" s="12">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="12" ht="14.5" spans="1:17">
+      <c r="H12" s="30">
         <f>配置!$B$6*6/9</f>
         <v>90</v>
       </c>
       <c r="I12" s="15">
         <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(H12/配置!$B$6,0),1),配置!$B$7),0)</f>
-        <v>231</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" ht="15">
-      <c r="H13" s="12">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="13" ht="14.5" spans="1:17">
+      <c r="H13" s="30">
         <f>配置!$B$6*7/9</f>
         <v>105</v>
       </c>
       <c r="I13" s="15">
         <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(H13/配置!$B$6,0),1),配置!$B$7),0)</f>
-        <v>308</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" ht="15">
-      <c r="H14" s="12">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="14" ht="14.5" spans="1:17">
+      <c r="H14" s="30">
         <f>配置!$B$6*8/9</f>
         <v>120</v>
       </c>
       <c r="I14" s="15">
         <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(H14/配置!$B$6,0),1),配置!$B$7),0)</f>
-        <v>398</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" ht="15">
-      <c r="H15" s="13">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="15" ht="14.5" spans="1:17">
+      <c r="H15" s="33">
         <f>配置!$B$6*9/9</f>
         <v>135</v>
       </c>
-      <c r="I15" s="16">
+      <c r="I15" s="19">
         <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(H15/配置!$B$6,0),1),配置!$B$7),0)</f>
-        <v>500</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" ht="28.05" customHeight="1">
-      <c r="A20" s="37" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="20" ht="28.05" customHeight="1" spans="1:17">
+      <c r="A20" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="B20" s="37" t="s">
+      <c r="B20" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="C20" s="37" t="s">
+      <c r="C20" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="D20" s="37" t="s">
+      <c r="D20" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="E20" s="37" t="s">
+      <c r="E20" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="F20" s="37" t="s">
+      <c r="F20" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="G20" s="37" t="s">
+      <c r="G20" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="H20" s="37" t="s">
+      <c r="H20" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="I20" s="37" t="s">
+      <c r="I20" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="J20" s="37" t="s">
+      <c r="J20" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="K20" s="37" t="s">
+      <c r="K20" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="L20" s="37" t="s">
+      <c r="L20" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="M20" s="37" t="s">
+      <c r="M20" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="N20" s="37" t="s">
+      <c r="N20" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="O20" s="37" t="s">
+      <c r="O20" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="P20" s="37" t="s">
+      <c r="P20" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="Q20" s="37" t="s">
+      <c r="Q20" s="27" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="30" customHeight="1">
+    <row r="21" ht="30" customHeight="1" spans="1:17">
       <c r="A21" s="1" t="s">
         <v>17</v>
       </c>
@@ -1657,822 +2423,821 @@
       <c r="I21" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J21" s="39" t="s">
+      <c r="J21" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K21" s="39" t="s">
+      <c r="K21" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="L21" s="39" t="s">
+      <c r="L21" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M21" s="39" t="s">
+      <c r="M21" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="N21" s="39" t="s">
+      <c r="N21" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="O21" s="39" t="s">
+      <c r="O21" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="P21" s="39" t="s">
+      <c r="P21" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="Q21" s="39" t="s">
+      <c r="Q21" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="34.049999999999997" customHeight="1">
-      <c r="A22" s="11">
+    <row r="22" ht="34.05" customHeight="1" spans="1:17">
+      <c r="A22" s="28">
         <f>事件!A2</f>
         <v>2</v>
       </c>
-      <c r="B22" s="5" t="str">
+      <c r="B22" s="34" t="str">
         <f>事件!B2</f>
         <v>start_gate</v>
       </c>
-      <c r="C22" s="5" t="str">
+      <c r="C22" s="34" t="str">
         <f>事件!C2</f>
         <v>开局食材门</v>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="11">
         <f>事件!E2</f>
         <v>15</v>
       </c>
-      <c r="E22" s="14">
+      <c r="E22" s="11">
         <f>事件!F2</f>
         <v>15</v>
       </c>
-      <c r="F22" s="14">
+      <c r="F22" s="11">
         <f>事件!G2</f>
         <v>30</v>
       </c>
-      <c r="G22" s="14">
+      <c r="G22" s="11">
         <f>事件!H2</f>
         <v>11</v>
       </c>
-      <c r="H22" s="14">
+      <c r="H22" s="11">
         <f>事件!K2</f>
         <v>45</v>
       </c>
-      <c r="I22" s="5" t="str">
+      <c r="I22" s="34" t="str">
         <f>TEXT(事件!M2,"0")&amp;"–"&amp;TEXT(事件!N2,"0")</f>
         <v>15–30</v>
       </c>
-      <c r="J22" s="17" t="s">
+      <c r="J22" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="K22" s="36" t="s">
+      <c r="K22" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="L22" s="36"/>
-      <c r="M22" s="36"/>
-      <c r="N22" s="36"/>
-      <c r="O22" s="36"/>
-      <c r="P22" s="36"/>
-      <c r="Q22" s="36"/>
-    </row>
-    <row r="23" spans="1:17" ht="34.049999999999997" customHeight="1">
-      <c r="A23" s="12">
+      <c r="L22" s="26"/>
+      <c r="M22" s="26"/>
+      <c r="N22" s="26"/>
+      <c r="O22" s="26"/>
+      <c r="P22" s="26"/>
+      <c r="Q22" s="26"/>
+    </row>
+    <row r="23" ht="34.05" customHeight="1" spans="1:17">
+      <c r="A23" s="30">
         <f>事件!A3</f>
         <v>18</v>
       </c>
-      <c r="B23" s="6" t="str">
+      <c r="B23" s="36" t="str">
         <f>事件!B3</f>
         <v>gate_0</v>
       </c>
-      <c r="C23" s="6" t="str">
+      <c r="C23" s="36" t="str">
         <f>事件!C3</f>
         <v>普通强化门</v>
       </c>
       <c r="D23" s="15">
         <f>事件!E3</f>
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E23" s="15">
         <f>事件!F3</f>
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F23" s="15">
         <f>事件!G3</f>
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G23" s="15">
         <f>事件!H3</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H23" s="15">
         <f>事件!K3</f>
-        <v>72</v>
-      </c>
-      <c r="I23" s="6" t="str">
+        <v>66</v>
+      </c>
+      <c r="I23" s="36" t="str">
         <f>TEXT(事件!M3,"0")&amp;"–"&amp;TEXT(事件!N3,"0")</f>
-        <v>24–48</v>
-      </c>
-      <c r="J23" s="17" t="s">
+        <v>22–44</v>
+      </c>
+      <c r="J23" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="K23" s="36" t="s">
+      <c r="K23" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="L23" s="36"/>
-      <c r="M23" s="36"/>
-      <c r="N23" s="36"/>
-      <c r="O23" s="36"/>
-      <c r="P23" s="36"/>
-      <c r="Q23" s="36"/>
-    </row>
-    <row r="24" spans="1:17" ht="34.049999999999997" customHeight="1">
-      <c r="A24" s="12">
+      <c r="L23" s="26"/>
+      <c r="M23" s="26"/>
+      <c r="N23" s="26"/>
+      <c r="O23" s="26"/>
+      <c r="P23" s="26"/>
+      <c r="Q23" s="26"/>
+    </row>
+    <row r="24" ht="34.05" customHeight="1" spans="1:17">
+      <c r="A24" s="30">
         <f>事件!A4</f>
         <v>27</v>
       </c>
-      <c r="B24" s="6" t="str">
+      <c r="B24" s="36" t="str">
         <f>事件!B4</f>
         <v>gate_1</v>
       </c>
-      <c r="C24" s="6" t="str">
+      <c r="C24" s="36" t="str">
         <f>事件!C4</f>
         <v>普通强化门</v>
       </c>
       <c r="D24" s="15">
         <f>事件!E4</f>
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E24" s="15">
         <f>事件!F4</f>
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F24" s="15">
         <f>事件!G4</f>
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="G24" s="15">
         <f>事件!H4</f>
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H24" s="15">
         <f>事件!K4</f>
-        <v>102</v>
-      </c>
-      <c r="I24" s="6" t="str">
+        <v>90</v>
+      </c>
+      <c r="I24" s="36" t="str">
         <f>TEXT(事件!M4,"0")&amp;"–"&amp;TEXT(事件!N4,"0")</f>
-        <v>34–68</v>
-      </c>
-      <c r="J24" s="17" t="s">
+        <v>30–60</v>
+      </c>
+      <c r="J24" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="K24" s="36" t="s">
+      <c r="K24" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="L24" s="36"/>
-      <c r="M24" s="36"/>
-      <c r="N24" s="36"/>
-      <c r="O24" s="36"/>
-      <c r="P24" s="36"/>
-      <c r="Q24" s="36"/>
-    </row>
-    <row r="25" spans="1:17" ht="34.049999999999997" customHeight="1">
-      <c r="A25" s="12">
+      <c r="L24" s="26"/>
+      <c r="M24" s="26"/>
+      <c r="N24" s="26"/>
+      <c r="O24" s="26"/>
+      <c r="P24" s="26"/>
+      <c r="Q24" s="26"/>
+    </row>
+    <row r="25" ht="34.05" customHeight="1" spans="1:17">
+      <c r="A25" s="30">
         <f>事件!A5</f>
         <v>39</v>
       </c>
-      <c r="B25" s="6" t="str">
+      <c r="B25" s="36" t="str">
         <f>事件!B5</f>
         <v>gate_2</v>
       </c>
-      <c r="C25" s="6" t="str">
+      <c r="C25" s="36" t="str">
         <f>事件!C5</f>
         <v>普通强化门</v>
       </c>
       <c r="D25" s="15">
         <f>事件!E5</f>
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="E25" s="15">
         <f>事件!F5</f>
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F25" s="15">
         <f>事件!G5</f>
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="G25" s="15">
         <f>事件!H5</f>
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="H25" s="15">
         <f>事件!K5</f>
-        <v>165</v>
-      </c>
-      <c r="I25" s="6" t="str">
+        <v>141</v>
+      </c>
+      <c r="I25" s="36" t="str">
         <f>TEXT(事件!M5,"0")&amp;"–"&amp;TEXT(事件!N5,"0")</f>
-        <v>55–110</v>
-      </c>
-      <c r="J25" s="17" t="s">
+        <v>47–94</v>
+      </c>
+      <c r="J25" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="K25" s="36" t="s">
+      <c r="K25" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="L25" s="36"/>
-      <c r="M25" s="36"/>
-      <c r="N25" s="36"/>
-      <c r="O25" s="36"/>
-      <c r="P25" s="36"/>
-      <c r="Q25" s="36"/>
-    </row>
-    <row r="26" spans="1:17" ht="34.049999999999997" customHeight="1">
-      <c r="A26" s="12">
+      <c r="L25" s="26"/>
+      <c r="M25" s="26"/>
+      <c r="N25" s="26"/>
+      <c r="O25" s="26"/>
+      <c r="P25" s="26"/>
+      <c r="Q25" s="26"/>
+    </row>
+    <row r="26" ht="34.05" customHeight="1" spans="1:17">
+      <c r="A26" s="30">
         <f>事件!A6</f>
         <v>50</v>
       </c>
-      <c r="B26" s="6" t="str">
+      <c r="B26" s="36" t="str">
         <f>事件!B6</f>
         <v>gate_3</v>
       </c>
-      <c r="C26" s="6" t="str">
+      <c r="C26" s="36" t="str">
         <f>事件!C6</f>
         <v>普通强化门</v>
       </c>
       <c r="D26" s="15">
         <f>事件!E6</f>
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="E26" s="15">
         <f>事件!F6</f>
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="F26" s="15">
         <f>事件!G6</f>
-        <v>164</v>
+        <v>136</v>
       </c>
       <c r="G26" s="15">
         <f>事件!H6</f>
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="H26" s="15">
         <f>事件!K6</f>
-        <v>246</v>
-      </c>
-      <c r="I26" s="6" t="str">
+        <v>204</v>
+      </c>
+      <c r="I26" s="36" t="str">
         <f>TEXT(事件!M6,"0")&amp;"–"&amp;TEXT(事件!N6,"0")</f>
-        <v>82–164</v>
-      </c>
-      <c r="J26" s="17" t="s">
+        <v>68–136</v>
+      </c>
+      <c r="J26" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="K26" s="36" t="s">
+      <c r="K26" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="L26" s="36"/>
-      <c r="M26" s="36"/>
-      <c r="N26" s="36"/>
-      <c r="O26" s="36"/>
-      <c r="P26" s="36"/>
-      <c r="Q26" s="36"/>
-    </row>
-    <row r="27" spans="1:17" ht="34.049999999999997" customHeight="1">
-      <c r="A27" s="12">
+      <c r="L26" s="26"/>
+      <c r="M26" s="26"/>
+      <c r="N26" s="26"/>
+      <c r="O26" s="26"/>
+      <c r="P26" s="26"/>
+      <c r="Q26" s="26"/>
+    </row>
+    <row r="27" ht="34.05" customHeight="1" spans="1:17">
+      <c r="A27" s="30">
         <f>事件!A7</f>
         <v>62</v>
       </c>
-      <c r="B27" s="6" t="str">
+      <c r="B27" s="36" t="str">
         <f>事件!B7</f>
         <v>gate_4</v>
       </c>
-      <c r="C27" s="6" t="str">
+      <c r="C27" s="36" t="str">
         <f>事件!C7</f>
         <v>普通强化门</v>
       </c>
       <c r="D27" s="15">
         <f>事件!E7</f>
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="E27" s="15">
         <f>事件!F7</f>
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="F27" s="15">
         <f>事件!G7</f>
-        <v>234</v>
+        <v>192</v>
       </c>
       <c r="G27" s="15">
         <f>事件!H7</f>
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="H27" s="15">
         <f>事件!K7</f>
-        <v>351</v>
-      </c>
-      <c r="I27" s="6" t="str">
+        <v>288</v>
+      </c>
+      <c r="I27" s="36" t="str">
         <f>TEXT(事件!M7,"0")&amp;"–"&amp;TEXT(事件!N7,"0")</f>
-        <v>117–234</v>
-      </c>
-      <c r="J27" s="17" t="s">
+        <v>96–192</v>
+      </c>
+      <c r="J27" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="K27" s="36" t="s">
+      <c r="K27" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="L27" s="36"/>
-      <c r="M27" s="36"/>
-      <c r="N27" s="36"/>
-      <c r="O27" s="36"/>
-      <c r="P27" s="36"/>
-      <c r="Q27" s="36"/>
-    </row>
-    <row r="28" spans="1:17" ht="15">
-      <c r="A28" s="12">
+      <c r="L27" s="26"/>
+      <c r="M27" s="26"/>
+      <c r="N27" s="26"/>
+      <c r="O27" s="26"/>
+      <c r="P27" s="26"/>
+      <c r="Q27" s="26"/>
+    </row>
+    <row r="28" ht="14.5" spans="1:17">
+      <c r="A28" s="30">
         <f>事件!A8</f>
         <v>74</v>
       </c>
-      <c r="B28" s="6" t="str">
+      <c r="B28" s="36" t="str">
         <f>事件!B8</f>
         <v>gate_5</v>
       </c>
-      <c r="C28" s="6" t="str">
+      <c r="C28" s="36" t="str">
         <f>事件!C8</f>
         <v>普通强化门</v>
       </c>
       <c r="D28" s="15">
         <f>事件!E8</f>
-        <v>161</v>
+        <v>131</v>
       </c>
       <c r="E28" s="15">
         <f>事件!F8</f>
-        <v>161</v>
+        <v>131</v>
       </c>
       <c r="F28" s="15">
         <f>事件!G8</f>
-        <v>322</v>
+        <v>262</v>
       </c>
       <c r="G28" s="15">
         <f>事件!H8</f>
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="H28" s="15">
         <f>事件!K8</f>
-        <v>483</v>
-      </c>
-      <c r="I28" s="6" t="str">
+        <v>393</v>
+      </c>
+      <c r="I28" s="36" t="str">
         <f>TEXT(事件!M8,"0")&amp;"–"&amp;TEXT(事件!N8,"0")</f>
-        <v>161–322</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" ht="15">
-      <c r="A29" s="12">
+        <v>131–262</v>
+      </c>
+    </row>
+    <row r="29" ht="14.5" spans="1:17">
+      <c r="A29" s="30">
         <f>事件!A9</f>
         <v>80</v>
       </c>
-      <c r="B29" s="6" t="str">
+      <c r="B29" s="36" t="str">
         <f>事件!B9</f>
         <v>elite</v>
       </c>
-      <c r="C29" s="6" t="str">
+      <c r="C29" s="36" t="str">
         <f>事件!C9</f>
         <v>精英</v>
       </c>
       <c r="D29" s="15">
         <f>事件!E9</f>
-        <v>185</v>
+        <v>150</v>
       </c>
       <c r="E29" s="15">
         <f>事件!F9</f>
-        <v>185</v>
+        <v>150</v>
       </c>
       <c r="F29" s="15">
         <f>事件!G9</f>
-        <v>370</v>
+        <v>300</v>
       </c>
       <c r="G29" s="15">
         <f>事件!H9</f>
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="H29" s="15">
         <f>事件!K9</f>
-        <v>555</v>
-      </c>
-      <c r="I29" s="6" t="str">
+        <v>450</v>
+      </c>
+      <c r="I29" s="36" t="str">
         <f>TEXT(事件!M9,"0")&amp;"–"&amp;TEXT(事件!N9,"0")</f>
-        <v>185–370</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" ht="15">
-      <c r="A30" s="12">
+        <v>150–300</v>
+      </c>
+    </row>
+    <row r="30" ht="14.5" spans="1:17">
+      <c r="A30" s="30">
         <f>事件!A10</f>
         <v>86</v>
       </c>
-      <c r="B30" s="6" t="str">
+      <c r="B30" s="36" t="str">
         <f>事件!B10</f>
         <v>gate_6</v>
       </c>
-      <c r="C30" s="6" t="str">
+      <c r="C30" s="36" t="str">
         <f>事件!C10</f>
         <v>普通强化门</v>
       </c>
       <c r="D30" s="15">
         <f>事件!E10</f>
-        <v>212</v>
+        <v>171</v>
       </c>
       <c r="E30" s="15">
         <f>事件!F10</f>
-        <v>212</v>
+        <v>171</v>
       </c>
       <c r="F30" s="15">
         <f>事件!G10</f>
-        <v>424</v>
+        <v>342</v>
       </c>
       <c r="G30" s="15">
         <f>事件!H10</f>
-        <v>159</v>
+        <v>128</v>
       </c>
       <c r="H30" s="15">
         <f>事件!K10</f>
-        <v>636</v>
-      </c>
-      <c r="I30" s="6" t="str">
+        <v>513</v>
+      </c>
+      <c r="I30" s="36" t="str">
         <f>TEXT(事件!M10,"0")&amp;"–"&amp;TEXT(事件!N10,"0")</f>
-        <v>212–424</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" ht="15">
-      <c r="A31" s="12">
+        <v>171–342</v>
+      </c>
+    </row>
+    <row r="31" ht="14.5" spans="1:17">
+      <c r="A31" s="30">
         <f>事件!A11</f>
         <v>94</v>
       </c>
-      <c r="B31" s="6" t="str">
+      <c r="B31" s="36" t="str">
         <f>事件!B11</f>
         <v>gate_7</v>
       </c>
-      <c r="C31" s="6" t="str">
+      <c r="C31" s="36" t="str">
         <f>事件!C11</f>
         <v>普通强化门</v>
       </c>
       <c r="D31" s="15">
         <f>事件!E11</f>
-        <v>250</v>
+        <v>202</v>
       </c>
       <c r="E31" s="15">
         <f>事件!F11</f>
-        <v>250</v>
+        <v>202</v>
       </c>
       <c r="F31" s="15">
         <f>事件!G11</f>
-        <v>500</v>
+        <v>404</v>
       </c>
       <c r="G31" s="15">
         <f>事件!H11</f>
-        <v>188</v>
+        <v>152</v>
       </c>
       <c r="H31" s="15">
         <f>事件!K11</f>
-        <v>750</v>
-      </c>
-      <c r="I31" s="6" t="str">
+        <v>606</v>
+      </c>
+      <c r="I31" s="36" t="str">
         <f>TEXT(事件!M11,"0")&amp;"–"&amp;TEXT(事件!N11,"0")</f>
-        <v>250–500</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" ht="15">
-      <c r="A32" s="12">
+        <v>202–404</v>
+      </c>
+    </row>
+    <row r="32" ht="14.5" spans="1:17">
+      <c r="A32" s="30">
         <f>事件!A12</f>
         <v>102</v>
       </c>
-      <c r="B32" s="6" t="str">
+      <c r="B32" s="36" t="str">
         <f>事件!B12</f>
         <v>gate_8</v>
       </c>
-      <c r="C32" s="6" t="str">
+      <c r="C32" s="36" t="str">
         <f>事件!C12</f>
         <v>普通强化门</v>
       </c>
       <c r="D32" s="15">
         <f>事件!E12</f>
-        <v>292</v>
+        <v>235</v>
       </c>
       <c r="E32" s="15">
         <f>事件!F12</f>
-        <v>292</v>
+        <v>235</v>
       </c>
       <c r="F32" s="15">
         <f>事件!G12</f>
-        <v>584</v>
+        <v>470</v>
       </c>
       <c r="G32" s="15">
         <f>事件!H12</f>
-        <v>219</v>
+        <v>176</v>
       </c>
       <c r="H32" s="15">
         <f>事件!K12</f>
-        <v>876</v>
-      </c>
-      <c r="I32" s="6" t="str">
+        <v>705</v>
+      </c>
+      <c r="I32" s="36" t="str">
         <f>TEXT(事件!M12,"0")&amp;"–"&amp;TEXT(事件!N12,"0")</f>
-        <v>292–584</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" ht="15">
-      <c r="A33" s="12">
+        <v>235–470</v>
+      </c>
+    </row>
+    <row r="33" ht="14.5" spans="1:17">
+      <c r="A33" s="30">
         <f>事件!A13</f>
         <v>110</v>
       </c>
-      <c r="B33" s="6" t="str">
+      <c r="B33" s="36" t="str">
         <f>事件!B13</f>
         <v>gate_9</v>
       </c>
-      <c r="C33" s="6" t="str">
+      <c r="C33" s="36" t="str">
         <f>事件!C13</f>
         <v>普通强化门</v>
       </c>
       <c r="D33" s="15">
         <f>事件!E13</f>
-        <v>337</v>
+        <v>271</v>
       </c>
       <c r="E33" s="15">
         <f>事件!F13</f>
-        <v>337</v>
+        <v>271</v>
       </c>
       <c r="F33" s="15">
         <f>事件!G13</f>
-        <v>674</v>
+        <v>542</v>
       </c>
       <c r="G33" s="15">
         <f>事件!H13</f>
-        <v>253</v>
+        <v>203</v>
       </c>
       <c r="H33" s="15">
         <f>事件!K13</f>
-        <v>1011</v>
-      </c>
-      <c r="I33" s="6" t="str">
+        <v>813</v>
+      </c>
+      <c r="I33" s="36" t="str">
         <f>TEXT(事件!M13,"0")&amp;"–"&amp;TEXT(事件!N13,"0")</f>
-        <v>337–674</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" ht="15">
-      <c r="A34" s="12">
+        <v>271–542</v>
+      </c>
+    </row>
+    <row r="34" ht="14.5" spans="1:17">
+      <c r="A34" s="30">
         <f>事件!A14</f>
         <v>118</v>
       </c>
-      <c r="B34" s="6" t="str">
+      <c r="B34" s="36" t="str">
         <f>事件!B14</f>
         <v>gate_10</v>
       </c>
-      <c r="C34" s="6" t="str">
+      <c r="C34" s="36" t="str">
         <f>事件!C14</f>
         <v>普通强化门</v>
       </c>
       <c r="D34" s="15">
         <f>事件!E14</f>
-        <v>386</v>
+        <v>309</v>
       </c>
       <c r="E34" s="15">
         <f>事件!F14</f>
-        <v>386</v>
+        <v>309</v>
       </c>
       <c r="F34" s="15">
         <f>事件!G14</f>
-        <v>772</v>
+        <v>618</v>
       </c>
       <c r="G34" s="15">
         <f>事件!H14</f>
-        <v>290</v>
+        <v>232</v>
       </c>
       <c r="H34" s="15">
         <f>事件!K14</f>
-        <v>1158</v>
-      </c>
-      <c r="I34" s="6" t="str">
+        <v>927</v>
+      </c>
+      <c r="I34" s="36" t="str">
         <f>TEXT(事件!M14,"0")&amp;"–"&amp;TEXT(事件!N14,"0")</f>
-        <v>386–772</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" ht="15">
-      <c r="A35" s="12">
+        <v>309–618</v>
+      </c>
+    </row>
+    <row r="35" ht="14.5" spans="1:17">
+      <c r="A35" s="30">
         <f>事件!A15</f>
         <v>126</v>
       </c>
-      <c r="B35" s="6" t="str">
+      <c r="B35" s="36" t="str">
         <f>事件!B15</f>
         <v>gate_11</v>
       </c>
-      <c r="C35" s="6" t="str">
+      <c r="C35" s="36" t="str">
         <f>事件!C15</f>
         <v>普通强化门</v>
       </c>
       <c r="D35" s="15">
         <f>事件!E15</f>
-        <v>437</v>
+        <v>350</v>
       </c>
       <c r="E35" s="15">
         <f>事件!F15</f>
-        <v>437</v>
+        <v>350</v>
       </c>
       <c r="F35" s="15">
         <f>事件!G15</f>
-        <v>874</v>
+        <v>700</v>
       </c>
       <c r="G35" s="15">
         <f>事件!H15</f>
-        <v>328</v>
+        <v>263</v>
       </c>
       <c r="H35" s="15">
         <f>事件!K15</f>
-        <v>1311</v>
-      </c>
-      <c r="I35" s="6" t="str">
+        <v>1050</v>
+      </c>
+      <c r="I35" s="36" t="str">
         <f>TEXT(事件!M15,"0")&amp;"–"&amp;TEXT(事件!N15,"0")</f>
-        <v>437–874</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" ht="15">
-      <c r="A36" s="13">
+        <v>350–700</v>
+      </c>
+    </row>
+    <row r="36" ht="14.5" spans="1:17">
+      <c r="A36" s="33">
         <f>事件!A16</f>
         <v>135</v>
       </c>
-      <c r="B36" s="7" t="str">
+      <c r="B36" s="37" t="str">
         <f>事件!B16</f>
         <v>boss</v>
       </c>
-      <c r="C36" s="7" t="str">
+      <c r="C36" s="37" t="str">
         <f>事件!C16</f>
         <v>Boss</v>
       </c>
-      <c r="D36" s="16">
+      <c r="D36" s="19">
         <f>事件!E16</f>
-        <v>500</v>
-      </c>
-      <c r="E36" s="16">
+        <v>400</v>
+      </c>
+      <c r="E36" s="19">
         <f>事件!F16</f>
-        <v>500</v>
-      </c>
-      <c r="F36" s="16">
+        <v>400</v>
+      </c>
+      <c r="F36" s="19">
         <f>事件!G16</f>
-        <v>1000</v>
-      </c>
-      <c r="G36" s="16">
+        <v>800</v>
+      </c>
+      <c r="G36" s="19">
         <f>事件!H16</f>
-        <v>375</v>
-      </c>
-      <c r="H36" s="16">
+        <v>300</v>
+      </c>
+      <c r="H36" s="19">
         <f>事件!K16</f>
-        <v>1500</v>
-      </c>
-      <c r="I36" s="7" t="str">
+        <v>1200</v>
+      </c>
+      <c r="I36" s="37" t="str">
         <f>TEXT(事件!M16,"0")&amp;"–"&amp;TEXT(事件!N16,"0")</f>
-        <v>500–1000</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" ht="28.05" customHeight="1">
-      <c r="A38" s="37" t="s">
+        <v>400–800</v>
+      </c>
+    </row>
+    <row r="38" ht="28.05" customHeight="1" spans="1:17">
+      <c r="A38" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="B38" s="37" t="s">
+      <c r="B38" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="C38" s="37" t="s">
+      <c r="C38" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="D38" s="37" t="s">
+      <c r="D38" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="E38" s="37" t="s">
+      <c r="E38" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="F38" s="37" t="s">
+      <c r="F38" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="G38" s="37" t="s">
+      <c r="G38" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="H38" s="37" t="s">
+      <c r="H38" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="I38" s="37" t="s">
+      <c r="I38" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="J38" s="37" t="s">
+      <c r="J38" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="K38" s="37" t="s">
+      <c r="K38" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="L38" s="37" t="s">
+      <c r="L38" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="M38" s="37" t="s">
+      <c r="M38" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="N38" s="37" t="s">
+      <c r="N38" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="O38" s="37" t="s">
+      <c r="O38" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="P38" s="37" t="s">
+      <c r="P38" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="Q38" s="37" t="s">
+      <c r="Q38" s="27" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="31.95" customHeight="1">
-      <c r="A39" s="18" t="s">
+    <row r="39" ht="31.95" customHeight="1" spans="1:17">
+      <c r="A39" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="B39" s="36" t="s">
+      <c r="B39" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="C39" s="36"/>
-      <c r="D39" s="36"/>
-      <c r="E39" s="36"/>
-      <c r="F39" s="36"/>
-      <c r="G39" s="36"/>
-      <c r="H39" s="36"/>
-      <c r="I39" s="36"/>
-      <c r="J39" s="36"/>
-      <c r="K39" s="36"/>
-      <c r="L39" s="36"/>
-      <c r="M39" s="36"/>
-      <c r="N39" s="36"/>
-      <c r="O39" s="36"/>
-      <c r="P39" s="36"/>
-      <c r="Q39" s="36"/>
-    </row>
-    <row r="40" spans="1:17" ht="31.95" customHeight="1">
-      <c r="A40" s="18" t="s">
+      <c r="C39" s="26"/>
+      <c r="D39" s="26"/>
+      <c r="E39" s="26"/>
+      <c r="F39" s="26"/>
+      <c r="G39" s="26"/>
+      <c r="H39" s="26"/>
+      <c r="I39" s="26"/>
+      <c r="J39" s="26"/>
+      <c r="K39" s="26"/>
+      <c r="L39" s="26"/>
+      <c r="M39" s="26"/>
+      <c r="N39" s="26"/>
+      <c r="O39" s="26"/>
+      <c r="P39" s="26"/>
+      <c r="Q39" s="26"/>
+    </row>
+    <row r="40" ht="31.95" customHeight="1" spans="1:17">
+      <c r="A40" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="36" t="s">
+      <c r="B40" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="C40" s="36"/>
-      <c r="D40" s="36"/>
-      <c r="E40" s="36"/>
-      <c r="F40" s="36"/>
-      <c r="G40" s="36"/>
-      <c r="H40" s="36"/>
-      <c r="I40" s="36"/>
-      <c r="J40" s="36"/>
-      <c r="K40" s="36"/>
-      <c r="L40" s="36"/>
-      <c r="M40" s="36"/>
-      <c r="N40" s="36"/>
-      <c r="O40" s="36"/>
-      <c r="P40" s="36"/>
-      <c r="Q40" s="36"/>
-    </row>
-    <row r="41" spans="1:17" ht="31.95" customHeight="1">
-      <c r="A41" s="18" t="s">
+      <c r="C40" s="26"/>
+      <c r="D40" s="26"/>
+      <c r="E40" s="26"/>
+      <c r="F40" s="26"/>
+      <c r="G40" s="26"/>
+      <c r="H40" s="26"/>
+      <c r="I40" s="26"/>
+      <c r="J40" s="26"/>
+      <c r="K40" s="26"/>
+      <c r="L40" s="26"/>
+      <c r="M40" s="26"/>
+      <c r="N40" s="26"/>
+      <c r="O40" s="26"/>
+      <c r="P40" s="26"/>
+      <c r="Q40" s="26"/>
+    </row>
+    <row r="41" ht="31.95" customHeight="1" spans="1:17">
+      <c r="A41" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="B41" s="36" t="s">
+      <c r="B41" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="C41" s="36"/>
-      <c r="D41" s="36"/>
-      <c r="E41" s="36"/>
-      <c r="F41" s="36"/>
-      <c r="G41" s="36"/>
-      <c r="H41" s="36"/>
-      <c r="I41" s="36"/>
-      <c r="J41" s="36"/>
-      <c r="K41" s="36"/>
-      <c r="L41" s="36"/>
-      <c r="M41" s="36"/>
-      <c r="N41" s="36"/>
-      <c r="O41" s="36"/>
-      <c r="P41" s="36"/>
-      <c r="Q41" s="36"/>
-    </row>
-    <row r="42" spans="1:17" ht="31.95" customHeight="1">
-      <c r="A42" s="18" t="s">
+      <c r="C41" s="26"/>
+      <c r="D41" s="26"/>
+      <c r="E41" s="26"/>
+      <c r="F41" s="26"/>
+      <c r="G41" s="26"/>
+      <c r="H41" s="26"/>
+      <c r="I41" s="26"/>
+      <c r="J41" s="26"/>
+      <c r="K41" s="26"/>
+      <c r="L41" s="26"/>
+      <c r="M41" s="26"/>
+      <c r="N41" s="26"/>
+      <c r="O41" s="26"/>
+      <c r="P41" s="26"/>
+      <c r="Q41" s="26"/>
+    </row>
+    <row r="42" ht="31.95" customHeight="1" spans="1:17">
+      <c r="A42" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="B42" s="36" t="s">
+      <c r="B42" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="C42" s="36"/>
-      <c r="D42" s="36"/>
-      <c r="E42" s="36"/>
-      <c r="F42" s="36"/>
-      <c r="G42" s="36"/>
-      <c r="H42" s="36"/>
-      <c r="I42" s="36"/>
-      <c r="J42" s="36"/>
-      <c r="K42" s="36"/>
-      <c r="L42" s="36"/>
-      <c r="M42" s="36"/>
-      <c r="N42" s="36"/>
-      <c r="O42" s="36"/>
-      <c r="P42" s="36"/>
-      <c r="Q42" s="36"/>
+      <c r="C42" s="26"/>
+      <c r="D42" s="26"/>
+      <c r="E42" s="26"/>
+      <c r="F42" s="26"/>
+      <c r="G42" s="26"/>
+      <c r="H42" s="26"/>
+      <c r="I42" s="26"/>
+      <c r="J42" s="26"/>
+      <c r="K42" s="26"/>
+      <c r="L42" s="26"/>
+      <c r="M42" s="26"/>
+      <c r="N42" s="26"/>
+      <c r="O42" s="26"/>
+      <c r="P42" s="26"/>
+      <c r="Q42" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="16">
     <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="A2:Q3"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A20:Q20"/>
     <mergeCell ref="J21:Q21"/>
@@ -2481,23 +3246,25 @@
     <mergeCell ref="K24:Q24"/>
     <mergeCell ref="K25:Q25"/>
     <mergeCell ref="K26:Q26"/>
-    <mergeCell ref="B42:Q42"/>
     <mergeCell ref="K27:Q27"/>
     <mergeCell ref="A38:Q38"/>
     <mergeCell ref="B39:Q39"/>
     <mergeCell ref="B40:Q40"/>
     <mergeCell ref="B41:Q41"/>
+    <mergeCell ref="B42:Q42"/>
+    <mergeCell ref="A2:Q3"/>
   </mergeCells>
-  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -2506,7 +3273,7 @@
     <col min="5" max="5" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30" customHeight="1">
+    <row r="1" ht="30" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2523,111 +3290,111 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="34.049999999999997" customHeight="1">
-      <c r="A2" s="2" t="s">
+    <row r="2" ht="34.05" customHeight="1" spans="1:5">
+      <c r="A2" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="24" t="s">
+      <c r="D2" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E2" s="24" t="s">
+      <c r="E2" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="34.049999999999997" customHeight="1">
-      <c r="A3" s="3" t="s">
+    <row r="3" ht="34.05" customHeight="1" spans="1:5">
+      <c r="A3" s="21" t="s">
         <v>54</v>
       </c>
       <c r="B3" s="22">
         <v>1</v>
       </c>
-      <c r="C3" s="25" t="s">
+      <c r="C3" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D3" s="25" t="s">
+      <c r="D3" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="E3" s="25" t="s">
+      <c r="E3" s="5" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="34.049999999999997" customHeight="1">
-      <c r="A4" s="3" t="s">
+    <row r="4" ht="34.05" customHeight="1" spans="1:5">
+      <c r="A4" s="21" t="s">
         <v>57</v>
       </c>
       <c r="B4" s="22">
         <v>15</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="C4" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="D4" s="25" t="s">
+      <c r="D4" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E4" s="25" t="s">
+      <c r="E4" s="5" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="34.049999999999997" customHeight="1">
-      <c r="A5" s="3" t="s">
+    <row r="5" ht="34.05" customHeight="1" spans="1:5">
+      <c r="A5" s="21" t="s">
         <v>61</v>
       </c>
       <c r="B5" s="22">
-        <v>500</v>
-      </c>
-      <c r="C5" s="25" t="s">
+        <v>400</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="D5" s="25" t="s">
+      <c r="D5" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E5" s="25" t="s">
+      <c r="E5" s="5" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="34.049999999999997" customHeight="1">
-      <c r="A6" s="3" t="s">
+    <row r="6" ht="34.05" customHeight="1" spans="1:5">
+      <c r="A6" s="21" t="s">
         <v>65</v>
       </c>
       <c r="B6" s="22">
         <v>135</v>
       </c>
-      <c r="C6" s="25" t="s">
+      <c r="C6" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D6" s="25" t="s">
+      <c r="D6" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E6" s="25" t="s">
+      <c r="E6" s="5" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="34.049999999999997" customHeight="1">
-      <c r="A7" s="4" t="s">
+    <row r="7" ht="34.05" customHeight="1" spans="1:5">
+      <c r="A7" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="B7" s="23">
+      <c r="B7" s="24">
         <v>2</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="D7" s="26" t="s">
+      <c r="D7" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="E7" s="26" t="s">
+      <c r="E7" s="7" t="s">
         <v>72</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -2635,9 +3402,10 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:N16"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -2648,7 +3416,7 @@
     <col min="12" max="14" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="30" customHeight="1">
+    <row r="1" ht="30" customHeight="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
@@ -2692,819 +3460,819 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="31.95" customHeight="1">
-      <c r="A2" s="30">
+    <row r="2" ht="31.95" customHeight="1" spans="1:14">
+      <c r="A2" s="8">
         <v>2</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D2" s="33" t="s">
+      <c r="D2" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="E2" s="14">
+      <c r="E2" s="11">
         <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A2/配置!$B$6,0),1),配置!$B$7),0)</f>
         <v>15</v>
       </c>
-      <c r="F2" s="14">
+      <c r="F2" s="11">
         <f t="shared" ref="F2:F16" si="0">ROUND(E2,0)</f>
         <v>15</v>
       </c>
-      <c r="G2" s="14">
+      <c r="G2" s="11">
         <f t="shared" ref="G2:G16" si="1">ROUND(E2*2,0)</f>
         <v>30</v>
       </c>
-      <c r="H2" s="14">
+      <c r="H2" s="11">
         <f t="shared" ref="H2:H16" si="2">ROUND(E2*0.75,0)</f>
         <v>11</v>
       </c>
-      <c r="I2" s="14">
+      <c r="I2" s="11">
         <f t="shared" ref="I2:I16" si="3">ROUND(E2*1.5,0)</f>
         <v>23</v>
       </c>
-      <c r="J2" s="14">
+      <c r="J2" s="11">
         <f t="shared" ref="J2:J16" si="4">ROUND(E2*1.5,0)</f>
         <v>23</v>
       </c>
-      <c r="K2" s="14">
+      <c r="K2" s="11">
         <f t="shared" ref="K2:K16" si="5">ROUND(E2*3,0)</f>
         <v>45</v>
       </c>
-      <c r="L2" s="14">
+      <c r="L2" s="11">
         <f t="shared" ref="L2:L16" si="6">ROUND(E2*5.625,0)</f>
         <v>84</v>
       </c>
-      <c r="M2" s="14">
+      <c r="M2" s="11">
         <f t="shared" ref="M2:M16" si="7">ROUND(E2,0)</f>
         <v>15</v>
       </c>
-      <c r="N2" s="14">
+      <c r="N2" s="11">
         <f t="shared" ref="N2:N16" si="8">ROUND(E2*2,0)</f>
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="31.95" customHeight="1">
-      <c r="A3" s="31">
+    <row r="3" ht="31.95" customHeight="1" spans="1:14">
+      <c r="A3" s="12">
         <v>18</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="C3" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="D3" s="34" t="s">
+      <c r="D3" s="14" t="s">
         <v>83</v>
       </c>
       <c r="E3" s="15">
         <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A3/配置!$B$6,0),1),配置!$B$7),0)</f>
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F3" s="15">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G3" s="15">
         <f t="shared" si="1"/>
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H3" s="15">
         <f t="shared" si="2"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I3" s="15">
         <f t="shared" si="3"/>
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="J3" s="15">
         <f t="shared" si="4"/>
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K3" s="15">
         <f t="shared" si="5"/>
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="L3" s="15">
         <f t="shared" si="6"/>
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="M3" s="15">
         <f t="shared" si="7"/>
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="N3" s="15">
         <f t="shared" si="8"/>
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="31.95" customHeight="1">
-      <c r="A4" s="31">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" ht="31.95" customHeight="1" spans="1:14">
+      <c r="A4" s="12">
         <v>27</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="D4" s="34" t="s">
+      <c r="D4" s="14" t="s">
         <v>83</v>
       </c>
       <c r="E4" s="15">
         <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A4/配置!$B$6,0),1),配置!$B$7),0)</f>
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F4" s="15">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G4" s="15">
         <f t="shared" si="1"/>
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H4" s="15">
         <f t="shared" si="2"/>
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="I4" s="15">
         <f t="shared" si="3"/>
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="J4" s="15">
         <f t="shared" si="4"/>
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="K4" s="15">
         <f t="shared" si="5"/>
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="L4" s="15">
         <f t="shared" si="6"/>
-        <v>191</v>
+        <v>169</v>
       </c>
       <c r="M4" s="15">
         <f t="shared" si="7"/>
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="N4" s="15">
         <f t="shared" si="8"/>
-        <v>68</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="31.95" customHeight="1">
-      <c r="A5" s="31">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" ht="31.95" customHeight="1" spans="1:14">
+      <c r="A5" s="12">
         <v>39</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="C5" s="28" t="s">
+      <c r="C5" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="D5" s="34" t="s">
+      <c r="D5" s="14" t="s">
         <v>83</v>
       </c>
       <c r="E5" s="15">
         <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A5/配置!$B$6,0),1),配置!$B$7),0)</f>
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F5" s="15">
         <f t="shared" si="0"/>
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="G5" s="15">
         <f t="shared" si="1"/>
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="H5" s="15">
         <f t="shared" si="2"/>
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="I5" s="15">
         <f t="shared" si="3"/>
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="J5" s="15">
         <f t="shared" si="4"/>
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="K5" s="15">
         <f t="shared" si="5"/>
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="L5" s="15">
         <f t="shared" si="6"/>
-        <v>309</v>
+        <v>264</v>
       </c>
       <c r="M5" s="15">
         <f t="shared" si="7"/>
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="N5" s="15">
         <f t="shared" si="8"/>
-        <v>110</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="31.95" customHeight="1">
-      <c r="A6" s="31">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" ht="31.95" customHeight="1" spans="1:14">
+      <c r="A6" s="12">
         <v>50</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="C6" s="28" t="s">
+      <c r="C6" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="D6" s="34" t="s">
+      <c r="D6" s="14" t="s">
         <v>83</v>
       </c>
       <c r="E6" s="15">
         <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A6/配置!$B$6,0),1),配置!$B$7),0)</f>
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="F6" s="15">
         <f t="shared" si="0"/>
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="G6" s="15">
         <f t="shared" si="1"/>
-        <v>164</v>
+        <v>136</v>
       </c>
       <c r="H6" s="15">
         <f t="shared" si="2"/>
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="I6" s="15">
         <f t="shared" si="3"/>
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="J6" s="15">
         <f t="shared" si="4"/>
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="K6" s="15">
         <f t="shared" si="5"/>
-        <v>246</v>
+        <v>204</v>
       </c>
       <c r="L6" s="15">
         <f t="shared" si="6"/>
-        <v>461</v>
+        <v>383</v>
       </c>
       <c r="M6" s="15">
         <f t="shared" si="7"/>
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="N6" s="15">
         <f t="shared" si="8"/>
-        <v>164</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="31.95" customHeight="1">
-      <c r="A7" s="31">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="7" ht="31.95" customHeight="1" spans="1:14">
+      <c r="A7" s="12">
         <v>62</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="C7" s="28" t="s">
+      <c r="C7" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="D7" s="34" t="s">
+      <c r="D7" s="14" t="s">
         <v>83</v>
       </c>
       <c r="E7" s="15">
         <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A7/配置!$B$6,0),1),配置!$B$7),0)</f>
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="F7" s="15">
         <f t="shared" si="0"/>
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="G7" s="15">
         <f t="shared" si="1"/>
-        <v>234</v>
+        <v>192</v>
       </c>
       <c r="H7" s="15">
         <f t="shared" si="2"/>
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="I7" s="15">
         <f t="shared" si="3"/>
-        <v>176</v>
+        <v>144</v>
       </c>
       <c r="J7" s="15">
         <f t="shared" si="4"/>
-        <v>176</v>
+        <v>144</v>
       </c>
       <c r="K7" s="15">
         <f t="shared" si="5"/>
-        <v>351</v>
+        <v>288</v>
       </c>
       <c r="L7" s="15">
         <f t="shared" si="6"/>
-        <v>658</v>
+        <v>540</v>
       </c>
       <c r="M7" s="15">
         <f t="shared" si="7"/>
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="N7" s="15">
         <f t="shared" si="8"/>
-        <v>234</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="31.95" customHeight="1">
-      <c r="A8" s="31">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="8" ht="31.95" customHeight="1" spans="1:14">
+      <c r="A8" s="12">
         <v>74</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="C8" s="28" t="s">
+      <c r="C8" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="D8" s="34" t="s">
+      <c r="D8" s="14" t="s">
         <v>83</v>
       </c>
       <c r="E8" s="15">
         <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A8/配置!$B$6,0),1),配置!$B$7),0)</f>
-        <v>161</v>
+        <v>131</v>
       </c>
       <c r="F8" s="15">
         <f t="shared" si="0"/>
-        <v>161</v>
+        <v>131</v>
       </c>
       <c r="G8" s="15">
         <f t="shared" si="1"/>
-        <v>322</v>
+        <v>262</v>
       </c>
       <c r="H8" s="15">
         <f t="shared" si="2"/>
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="I8" s="15">
         <f t="shared" si="3"/>
-        <v>242</v>
+        <v>197</v>
       </c>
       <c r="J8" s="15">
         <f t="shared" si="4"/>
-        <v>242</v>
+        <v>197</v>
       </c>
       <c r="K8" s="15">
         <f t="shared" si="5"/>
-        <v>483</v>
+        <v>393</v>
       </c>
       <c r="L8" s="15">
         <f t="shared" si="6"/>
-        <v>906</v>
+        <v>737</v>
       </c>
       <c r="M8" s="15">
         <f t="shared" si="7"/>
-        <v>161</v>
+        <v>131</v>
       </c>
       <c r="N8" s="15">
         <f t="shared" si="8"/>
-        <v>322</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="31.95" customHeight="1">
-      <c r="A9" s="31">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="9" ht="31.95" customHeight="1" spans="1:14">
+      <c r="A9" s="12">
         <v>80</v>
       </c>
-      <c r="B9" s="20" t="s">
+      <c r="B9" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="C9" s="28" t="s">
+      <c r="C9" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="D9" s="34" t="s">
+      <c r="D9" s="14" t="s">
         <v>91</v>
       </c>
       <c r="E9" s="15">
         <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A9/配置!$B$6,0),1),配置!$B$7),0)</f>
-        <v>185</v>
+        <v>150</v>
       </c>
       <c r="F9" s="15">
         <f t="shared" si="0"/>
-        <v>185</v>
+        <v>150</v>
       </c>
       <c r="G9" s="15">
         <f t="shared" si="1"/>
-        <v>370</v>
+        <v>300</v>
       </c>
       <c r="H9" s="15">
         <f t="shared" si="2"/>
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="I9" s="15">
         <f t="shared" si="3"/>
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="J9" s="15">
         <f t="shared" si="4"/>
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="K9" s="15">
         <f t="shared" si="5"/>
-        <v>555</v>
+        <v>450</v>
       </c>
       <c r="L9" s="15">
         <f t="shared" si="6"/>
-        <v>1041</v>
+        <v>844</v>
       </c>
       <c r="M9" s="15">
         <f t="shared" si="7"/>
-        <v>185</v>
+        <v>150</v>
       </c>
       <c r="N9" s="15">
         <f t="shared" si="8"/>
-        <v>370</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="31.95" customHeight="1">
-      <c r="A10" s="31">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="10" ht="31.95" customHeight="1" spans="1:14">
+      <c r="A10" s="12">
         <v>86</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="C10" s="28" t="s">
+      <c r="C10" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="D10" s="34" t="s">
+      <c r="D10" s="14" t="s">
         <v>83</v>
       </c>
       <c r="E10" s="15">
         <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A10/配置!$B$6,0),1),配置!$B$7),0)</f>
-        <v>212</v>
+        <v>171</v>
       </c>
       <c r="F10" s="15">
         <f t="shared" si="0"/>
-        <v>212</v>
+        <v>171</v>
       </c>
       <c r="G10" s="15">
         <f t="shared" si="1"/>
-        <v>424</v>
+        <v>342</v>
       </c>
       <c r="H10" s="15">
         <f t="shared" si="2"/>
-        <v>159</v>
+        <v>128</v>
       </c>
       <c r="I10" s="15">
         <f t="shared" si="3"/>
-        <v>318</v>
+        <v>257</v>
       </c>
       <c r="J10" s="15">
         <f t="shared" si="4"/>
-        <v>318</v>
+        <v>257</v>
       </c>
       <c r="K10" s="15">
         <f t="shared" si="5"/>
-        <v>636</v>
+        <v>513</v>
       </c>
       <c r="L10" s="15">
         <f t="shared" si="6"/>
-        <v>1193</v>
+        <v>962</v>
       </c>
       <c r="M10" s="15">
         <f t="shared" si="7"/>
-        <v>212</v>
+        <v>171</v>
       </c>
       <c r="N10" s="15">
         <f t="shared" si="8"/>
-        <v>424</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="31.95" customHeight="1">
-      <c r="A11" s="31">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="11" ht="31.95" customHeight="1" spans="1:14">
+      <c r="A11" s="12">
         <v>94</v>
       </c>
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="C11" s="28" t="s">
+      <c r="C11" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="D11" s="34" t="s">
+      <c r="D11" s="14" t="s">
         <v>83</v>
       </c>
       <c r="E11" s="15">
         <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A11/配置!$B$6,0),1),配置!$B$7),0)</f>
-        <v>250</v>
+        <v>202</v>
       </c>
       <c r="F11" s="15">
         <f t="shared" si="0"/>
-        <v>250</v>
+        <v>202</v>
       </c>
       <c r="G11" s="15">
         <f t="shared" si="1"/>
-        <v>500</v>
+        <v>404</v>
       </c>
       <c r="H11" s="15">
         <f t="shared" si="2"/>
-        <v>188</v>
+        <v>152</v>
       </c>
       <c r="I11" s="15">
         <f t="shared" si="3"/>
-        <v>375</v>
+        <v>303</v>
       </c>
       <c r="J11" s="15">
         <f t="shared" si="4"/>
-        <v>375</v>
+        <v>303</v>
       </c>
       <c r="K11" s="15">
         <f t="shared" si="5"/>
-        <v>750</v>
+        <v>606</v>
       </c>
       <c r="L11" s="15">
         <f t="shared" si="6"/>
-        <v>1406</v>
+        <v>1136</v>
       </c>
       <c r="M11" s="15">
         <f t="shared" si="7"/>
-        <v>250</v>
+        <v>202</v>
       </c>
       <c r="N11" s="15">
         <f t="shared" si="8"/>
-        <v>500</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="31.95" customHeight="1">
-      <c r="A12" s="31">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="12" ht="31.95" customHeight="1" spans="1:14">
+      <c r="A12" s="12">
         <v>102</v>
       </c>
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="C12" s="28" t="s">
+      <c r="C12" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="D12" s="34" t="s">
+      <c r="D12" s="14" t="s">
         <v>83</v>
       </c>
       <c r="E12" s="15">
         <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A12/配置!$B$6,0),1),配置!$B$7),0)</f>
-        <v>292</v>
+        <v>235</v>
       </c>
       <c r="F12" s="15">
         <f t="shared" si="0"/>
-        <v>292</v>
+        <v>235</v>
       </c>
       <c r="G12" s="15">
         <f t="shared" si="1"/>
-        <v>584</v>
+        <v>470</v>
       </c>
       <c r="H12" s="15">
         <f t="shared" si="2"/>
-        <v>219</v>
+        <v>176</v>
       </c>
       <c r="I12" s="15">
         <f t="shared" si="3"/>
-        <v>438</v>
+        <v>353</v>
       </c>
       <c r="J12" s="15">
         <f t="shared" si="4"/>
-        <v>438</v>
+        <v>353</v>
       </c>
       <c r="K12" s="15">
         <f t="shared" si="5"/>
-        <v>876</v>
+        <v>705</v>
       </c>
       <c r="L12" s="15">
         <f t="shared" si="6"/>
-        <v>1643</v>
+        <v>1322</v>
       </c>
       <c r="M12" s="15">
         <f t="shared" si="7"/>
-        <v>292</v>
+        <v>235</v>
       </c>
       <c r="N12" s="15">
         <f t="shared" si="8"/>
-        <v>584</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="31.95" customHeight="1">
-      <c r="A13" s="31">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="13" ht="31.95" customHeight="1" spans="1:14">
+      <c r="A13" s="12">
         <v>110</v>
       </c>
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="C13" s="28" t="s">
+      <c r="C13" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="D13" s="34" t="s">
+      <c r="D13" s="14" t="s">
         <v>83</v>
       </c>
       <c r="E13" s="15">
         <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A13/配置!$B$6,0),1),配置!$B$7),0)</f>
-        <v>337</v>
+        <v>271</v>
       </c>
       <c r="F13" s="15">
         <f t="shared" si="0"/>
-        <v>337</v>
+        <v>271</v>
       </c>
       <c r="G13" s="15">
         <f t="shared" si="1"/>
-        <v>674</v>
+        <v>542</v>
       </c>
       <c r="H13" s="15">
         <f t="shared" si="2"/>
-        <v>253</v>
+        <v>203</v>
       </c>
       <c r="I13" s="15">
         <f t="shared" si="3"/>
-        <v>506</v>
+        <v>407</v>
       </c>
       <c r="J13" s="15">
         <f t="shared" si="4"/>
-        <v>506</v>
+        <v>407</v>
       </c>
       <c r="K13" s="15">
         <f t="shared" si="5"/>
-        <v>1011</v>
+        <v>813</v>
       </c>
       <c r="L13" s="15">
         <f t="shared" si="6"/>
-        <v>1896</v>
+        <v>1524</v>
       </c>
       <c r="M13" s="15">
         <f t="shared" si="7"/>
-        <v>337</v>
+        <v>271</v>
       </c>
       <c r="N13" s="15">
         <f t="shared" si="8"/>
-        <v>674</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="31.95" customHeight="1">
-      <c r="A14" s="31">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="14" ht="31.95" customHeight="1" spans="1:14">
+      <c r="A14" s="12">
         <v>118</v>
       </c>
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="C14" s="28" t="s">
+      <c r="C14" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="D14" s="34" t="s">
+      <c r="D14" s="14" t="s">
         <v>83</v>
       </c>
       <c r="E14" s="15">
         <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A14/配置!$B$6,0),1),配置!$B$7),0)</f>
-        <v>386</v>
+        <v>309</v>
       </c>
       <c r="F14" s="15">
         <f t="shared" si="0"/>
-        <v>386</v>
+        <v>309</v>
       </c>
       <c r="G14" s="15">
         <f t="shared" si="1"/>
-        <v>772</v>
+        <v>618</v>
       </c>
       <c r="H14" s="15">
         <f t="shared" si="2"/>
-        <v>290</v>
+        <v>232</v>
       </c>
       <c r="I14" s="15">
         <f t="shared" si="3"/>
-        <v>579</v>
+        <v>464</v>
       </c>
       <c r="J14" s="15">
         <f t="shared" si="4"/>
-        <v>579</v>
+        <v>464</v>
       </c>
       <c r="K14" s="15">
         <f t="shared" si="5"/>
-        <v>1158</v>
+        <v>927</v>
       </c>
       <c r="L14" s="15">
         <f t="shared" si="6"/>
-        <v>2171</v>
+        <v>1738</v>
       </c>
       <c r="M14" s="15">
         <f t="shared" si="7"/>
-        <v>386</v>
+        <v>309</v>
       </c>
       <c r="N14" s="15">
         <f t="shared" si="8"/>
-        <v>772</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="31.95" customHeight="1">
-      <c r="A15" s="31">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="15" ht="31.95" customHeight="1" spans="1:14">
+      <c r="A15" s="12">
         <v>126</v>
       </c>
-      <c r="B15" s="20" t="s">
+      <c r="B15" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="C15" s="28" t="s">
+      <c r="C15" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="D15" s="34" t="s">
+      <c r="D15" s="14" t="s">
         <v>83</v>
       </c>
       <c r="E15" s="15">
         <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A15/配置!$B$6,0),1),配置!$B$7),0)</f>
-        <v>437</v>
+        <v>350</v>
       </c>
       <c r="F15" s="15">
         <f t="shared" si="0"/>
-        <v>437</v>
+        <v>350</v>
       </c>
       <c r="G15" s="15">
         <f t="shared" si="1"/>
-        <v>874</v>
+        <v>700</v>
       </c>
       <c r="H15" s="15">
         <f t="shared" si="2"/>
-        <v>328</v>
+        <v>263</v>
       </c>
       <c r="I15" s="15">
         <f t="shared" si="3"/>
-        <v>656</v>
+        <v>525</v>
       </c>
       <c r="J15" s="15">
         <f t="shared" si="4"/>
-        <v>656</v>
+        <v>525</v>
       </c>
       <c r="K15" s="15">
         <f t="shared" si="5"/>
-        <v>1311</v>
+        <v>1050</v>
       </c>
       <c r="L15" s="15">
         <f t="shared" si="6"/>
-        <v>2458</v>
+        <v>1969</v>
       </c>
       <c r="M15" s="15">
         <f t="shared" si="7"/>
-        <v>437</v>
+        <v>350</v>
       </c>
       <c r="N15" s="15">
         <f t="shared" si="8"/>
-        <v>874</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="31.95" customHeight="1">
-      <c r="A16" s="32">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="16" ht="31.95" customHeight="1" spans="1:14">
+      <c r="A16" s="16">
         <v>135</v>
       </c>
-      <c r="B16" s="21" t="s">
+      <c r="B16" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="C16" s="29" t="s">
+      <c r="C16" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="D16" s="35" t="s">
+      <c r="D16" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="E16" s="16">
+      <c r="E16" s="19">
         <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A16/配置!$B$6,0),1),配置!$B$7),0)</f>
-        <v>500</v>
-      </c>
-      <c r="F16" s="16">
+        <v>400</v>
+      </c>
+      <c r="F16" s="19">
         <f t="shared" si="0"/>
-        <v>500</v>
-      </c>
-      <c r="G16" s="16">
+        <v>400</v>
+      </c>
+      <c r="G16" s="19">
         <f t="shared" si="1"/>
-        <v>1000</v>
-      </c>
-      <c r="H16" s="16">
+        <v>800</v>
+      </c>
+      <c r="H16" s="19">
         <f t="shared" si="2"/>
-        <v>375</v>
-      </c>
-      <c r="I16" s="16">
+        <v>300</v>
+      </c>
+      <c r="I16" s="19">
         <f t="shared" si="3"/>
-        <v>750</v>
-      </c>
-      <c r="J16" s="16">
+        <v>600</v>
+      </c>
+      <c r="J16" s="19">
         <f t="shared" si="4"/>
-        <v>750</v>
-      </c>
-      <c r="K16" s="16">
+        <v>600</v>
+      </c>
+      <c r="K16" s="19">
         <f t="shared" si="5"/>
-        <v>1500</v>
-      </c>
-      <c r="L16" s="16">
+        <v>1200</v>
+      </c>
+      <c r="L16" s="19">
         <f t="shared" si="6"/>
-        <v>2813</v>
-      </c>
-      <c r="M16" s="16">
+        <v>2250</v>
+      </c>
+      <c r="M16" s="19">
         <f t="shared" si="7"/>
-        <v>500</v>
-      </c>
-      <c r="N16" s="16">
+        <v>400</v>
+      </c>
+      <c r="N16" s="19">
         <f t="shared" si="8"/>
-        <v>1000</v>
+        <v>800</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -3512,15 +4280,16 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="92" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="30" customHeight="1">
+    <row r="1" ht="30" customHeight="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>101</v>
       </c>
@@ -3528,84 +4297,84 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="42" customHeight="1">
-      <c r="A2" s="27" t="s">
+    <row r="2" ht="42" customHeight="1" spans="1:2">
+      <c r="A2" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="3" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="42" customHeight="1">
-      <c r="A3" s="28" t="s">
+    <row r="3" ht="42" customHeight="1" spans="1:2">
+      <c r="A3" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="5" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="42" customHeight="1">
-      <c r="A4" s="28" t="s">
+    <row r="4" ht="42" customHeight="1" spans="1:2">
+      <c r="A4" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="5" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="42" customHeight="1">
-      <c r="A5" s="28" t="s">
+    <row r="5" ht="42" customHeight="1" spans="1:2">
+      <c r="A5" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="5" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="42" customHeight="1">
-      <c r="A6" s="28" t="s">
+    <row r="6" ht="42" customHeight="1" spans="1:2">
+      <c r="A6" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="5" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="42" customHeight="1">
-      <c r="A7" s="28" t="s">
+    <row r="7" ht="42" customHeight="1" spans="1:2">
+      <c r="A7" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="5" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="42" customHeight="1">
-      <c r="A8" s="28" t="s">
+    <row r="8" ht="42" customHeight="1" spans="1:2">
+      <c r="A8" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="5" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="42" customHeight="1">
-      <c r="A9" s="28" t="s">
+    <row r="9" ht="42" customHeight="1" spans="1:2">
+      <c r="A9" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="5" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="42" customHeight="1">
-      <c r="A10" s="29" t="s">
+    <row r="10" ht="42" customHeight="1" spans="1:2">
+      <c r="A10" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="B10" s="26" t="s">
+      <c r="B10" s="7" t="s">
         <v>119</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
--- a/balance_tables/时间轴.xlsx
+++ b/balance_tables/时间轴.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gameproduct\小厨西\balance_tables\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E78CCDBD-B3BC-4A8C-ACD7-CB4BD6A936E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080" activeTab="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="时间轴预览" sheetId="1" r:id="rId1"/>
@@ -21,9 +27,10 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -395,15 +402,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0.0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="178" formatCode="0.0"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -445,157 +448,16 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Carlito"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
+      <sz val="9"/>
+      <name val="Carlito"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="40">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -644,194 +506,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="12">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -868,433 +544,150 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="40">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="2" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="2" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="2" fontId="2" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="2" fontId="2" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="2" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="2" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="2" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </cellStyleXfs>
-  <cellXfs count="39">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="4" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="5" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="4" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="5" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="4" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="5" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="4" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="4" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="5" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="5" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="5" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="2">
+    <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="Normal" xfId="49"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="zh-CN"/>
   <c:roundedCorners val="0"/>
@@ -1327,11 +720,9 @@
               <a:rPr lang="zh-CN" altLang="en-US"/>
               <a:t>基准胃口随时间增长</a:t>
             </a:r>
-            <a:endParaRPr lang="zh-CN" altLang="en-US"/>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="1"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -1344,126 +735,135 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:strRef>
-              <c:f>"基准胃口"</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>基准胃口</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>基准胃口</c:v>
           </c:tx>
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
           <c:dPt>
             <c:idx val="0"/>
-            <c:marker>
-              <c:symbol val="none"/>
-            </c:marker>
             <c:bubble3D val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000000-D578-4AAB-A341-8C627FDEA8FB}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
-            <c:marker>
-              <c:symbol val="none"/>
-            </c:marker>
             <c:bubble3D val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-D578-4AAB-A341-8C627FDEA8FB}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
-            <c:marker>
-              <c:symbol val="none"/>
-            </c:marker>
             <c:bubble3D val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-D578-4AAB-A341-8C627FDEA8FB}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
-            <c:marker>
-              <c:symbol val="none"/>
-            </c:marker>
             <c:bubble3D val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-D578-4AAB-A341-8C627FDEA8FB}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
-            <c:marker>
-              <c:symbol val="none"/>
-            </c:marker>
             <c:bubble3D val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000004-D578-4AAB-A341-8C627FDEA8FB}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="5"/>
-            <c:marker>
-              <c:symbol val="none"/>
-            </c:marker>
             <c:bubble3D val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-D578-4AAB-A341-8C627FDEA8FB}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="6"/>
-            <c:marker>
-              <c:symbol val="none"/>
-            </c:marker>
             <c:bubble3D val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000006-D578-4AAB-A341-8C627FDEA8FB}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="7"/>
-            <c:marker>
-              <c:symbol val="none"/>
-            </c:marker>
             <c:bubble3D val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-D578-4AAB-A341-8C627FDEA8FB}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="8"/>
-            <c:marker>
-              <c:symbol val="none"/>
-            </c:marker>
             <c:bubble3D val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000008-D578-4AAB-A341-8C627FDEA8FB}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="9"/>
-            <c:marker>
-              <c:symbol val="none"/>
-            </c:marker>
             <c:bubble3D val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-D578-4AAB-A341-8C627FDEA8FB}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
-          <c:dLbls>
-            <c:delete val="1"/>
-          </c:dLbls>
           <c:cat>
             <c:numRef>
               <c:f>时间轴预览!$H$6:$H$15</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="10"/>
-                <c:pt idx="0" c:formatCode="0.0">
+                <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="1" c:formatCode="0.0">
+                <c:pt idx="1">
                   <c:v>15</c:v>
                 </c:pt>
-                <c:pt idx="2" c:formatCode="0.0">
+                <c:pt idx="2">
                   <c:v>30</c:v>
                 </c:pt>
-                <c:pt idx="3" c:formatCode="0.0">
+                <c:pt idx="3">
                   <c:v>45</c:v>
                 </c:pt>
-                <c:pt idx="4" c:formatCode="0.0">
+                <c:pt idx="4">
                   <c:v>60</c:v>
                 </c:pt>
-                <c:pt idx="5" c:formatCode="0.0">
+                <c:pt idx="5">
                   <c:v>75</c:v>
                 </c:pt>
-                <c:pt idx="6" c:formatCode="0.0">
+                <c:pt idx="6">
                   <c:v>90</c:v>
                 </c:pt>
-                <c:pt idx="7" c:formatCode="0.0">
+                <c:pt idx="7">
                   <c:v>105</c:v>
                 </c:pt>
-                <c:pt idx="8" c:formatCode="0.0">
+                <c:pt idx="8">
                   <c:v>120</c:v>
                 </c:pt>
-                <c:pt idx="9" c:formatCode="0.0">
+                <c:pt idx="9">
                   <c:v>135</c:v>
                 </c:pt>
               </c:numCache>
@@ -1479,36 +879,41 @@
                   <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>20</c:v>
+                  <c:v>18</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>34</c:v>
+                  <c:v>29</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>58</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>91</c:v>
+                  <c:v>76</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>134</c:v>
+                  <c:v>112</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>186</c:v>
+                  <c:v>158</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>248</c:v>
+                  <c:v>213</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>319</c:v>
+                  <c:v>277</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>400</c:v>
+                  <c:v>350</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000A-D578-4AAB-A341-8C627FDEA8FB}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -1518,8 +923,7 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:marker val="0"/>
-        <c:smooth val="1"/>
+        <c:smooth val="0"/>
         <c:axId val="48650112"/>
         <c:axId val="48672768"/>
       </c:lineChart>
@@ -1561,11 +965,9 @@
                   <a:rPr lang="zh-CN" altLang="en-US"/>
                   <a:t>时间（秒）</a:t>
                 </a:r>
-                <a:endParaRPr lang="zh-CN" altLang="en-US"/>
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="1"/>
         </c:title>
         <c:numFmt formatCode="0.0" sourceLinked="1"/>
@@ -1586,6 +988,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="48672768"/>
@@ -1634,11 +1037,9 @@
                   <a:rPr lang="zh-CN" altLang="en-US"/>
                   <a:t>基准胃口</a:t>
                 </a:r>
-                <a:endParaRPr lang="zh-CN" altLang="en-US"/>
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="1"/>
         </c:title>
         <c:numFmt formatCode="0" sourceLinked="1"/>
@@ -1659,6 +1060,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="48650112"/>
@@ -1691,6 +1093,7 @@
       <a:pPr>
         <a:defRPr lang="zh-CN"/>
       </a:pPr>
+      <a:endParaRPr lang="zh-CN"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -1702,7 +1105,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
@@ -1716,14 +1119,20 @@
       <xdr:row>18</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart"/>
+        <xdr:cNvPr id="2" name="Chart">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="12115800" y="1269365"/>
-        <a:ext cx="6934200" cy="2952750"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1737,45 +1146,65 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TimelineConfigTable" displayName="TimelineConfigTable" ref="A1:E7" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TimelineConfigTable" displayName="TimelineConfigTable" ref="A1:E7" totalsRowShown="0">
   <tableColumns count="5">
-    <tableColumn id="1" name="参数ID"/>
-    <tableColumn id="2" name="数值"/>
-    <tableColumn id="3" name="说明"/>
-    <tableColumn id="4" name="对游戏的影响"/>
-    <tableColumn id="5" name="修改建议"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="参数ID"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="数值"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="说明"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="对游戏的影响"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="修改建议"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TimelineEventsTable" displayName="TimelineEventsTable" ref="A1:N16" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="TimelineEventsTable" displayName="TimelineEventsTable" ref="A1:N16" totalsRowShown="0">
   <tableColumns count="14">
-    <tableColumn id="1" name="请求时间(s)"/>
-    <tableColumn id="2" name="事件ID"/>
-    <tableColumn id="3" name="类型"/>
-    <tableColumn id="4" name="说明"/>
-    <tableColumn id="5" name="基准胃口"/>
-    <tableColumn id="6" name="普通p0"/>
-    <tableColumn id="7" name="普通p1"/>
-    <tableColumn id="8" name="快速p0"/>
-    <tableColumn id="9" name="快速p1"/>
-    <tableColumn id="10" name="远程p0"/>
-    <tableColumn id="11" name="远程p1"/>
-    <tableColumn id="12" name="精英胃口"/>
-    <tableColumn id="13" name="门基础最低"/>
-    <tableColumn id="14" name="门基础最高"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="请求时间(s)"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="事件ID"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="类型"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="说明"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="基准胃口">
+      <calculatedColumnFormula>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A2/配置!$B$6,0),1),配置!$B$7),0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="普通p0">
+      <calculatedColumnFormula>ROUND(E2,0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="普通p1">
+      <calculatedColumnFormula>ROUND(E2*2,0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="快速p0">
+      <calculatedColumnFormula>ROUND(E2*0.75,0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="快速p1">
+      <calculatedColumnFormula>ROUND(E2*1.5,0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="远程p0">
+      <calculatedColumnFormula>ROUND(E2*1.5,0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="远程p1">
+      <calculatedColumnFormula>ROUND(E2*3,0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="精英胃口">
+      <calculatedColumnFormula>ROUND(E2*5.625,0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="门基础最低">
+      <calculatedColumnFormula>ROUND(E2,0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="门基础最高">
+      <calculatedColumnFormula>ROUND(E2*2,0)</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="TimelineNotesTable" displayName="TimelineNotesTable" ref="A1:B10" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="TimelineNotesTable" displayName="TimelineNotesTable" ref="A1:B10" totalsRowShown="0">
   <tableColumns count="2">
-    <tableColumn id="1" name="项目"/>
-    <tableColumn id="2" name="说明"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="项目"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="说明"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1970,14 +1399,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q42"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>
@@ -1989,182 +1418,182 @@
     <col min="11" max="17" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="37.95" customHeight="1" spans="1:17">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:17" ht="37.950000000000003" customHeight="1">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="D1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="E1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="F1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="25" t="s">
+      <c r="G1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="25" t="s">
+      <c r="H1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="25" t="s">
+      <c r="I1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="J1" s="25" t="s">
+      <c r="J1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="K1" s="25" t="s">
+      <c r="K1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="L1" s="25" t="s">
+      <c r="L1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="M1" s="25" t="s">
+      <c r="M1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="N1" s="25" t="s">
+      <c r="N1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="O1" s="25" t="s">
+      <c r="O1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="P1" s="25" t="s">
+      <c r="P1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="Q1" s="25" t="s">
+      <c r="Q1" s="36" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" ht="24" customHeight="1" spans="1:17">
-      <c r="A2" s="26" t="s">
+    <row r="2" spans="1:17" ht="24" customHeight="1">
+      <c r="A2" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="C2" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="D2" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="26" t="s">
+      <c r="E2" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="26" t="s">
+      <c r="F2" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="26" t="s">
+      <c r="G2" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="26" t="s">
+      <c r="H2" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="I2" s="26" t="s">
+      <c r="I2" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="26" t="s">
+      <c r="J2" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="K2" s="26" t="s">
+      <c r="K2" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="L2" s="26" t="s">
+      <c r="L2" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="M2" s="26" t="s">
+      <c r="M2" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="N2" s="26" t="s">
+      <c r="N2" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="26" t="s">
+      <c r="O2" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="P2" s="26" t="s">
+      <c r="P2" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="Q2" s="26" t="s">
+      <c r="Q2" s="39" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1" spans="1:17">
-      <c r="A3" s="26" t="s">
+    <row r="3" spans="1:17" ht="24" customHeight="1">
+      <c r="A3" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="C3" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="D3" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="E3" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="F3" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="G3" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="H3" s="26" t="s">
+      <c r="H3" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="I3" s="26" t="s">
+      <c r="I3" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="J3" s="26" t="s">
+      <c r="J3" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="K3" s="26" t="s">
+      <c r="K3" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="L3" s="26" t="s">
+      <c r="L3" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="M3" s="26" t="s">
+      <c r="M3" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="N3" s="26" t="s">
+      <c r="N3" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="O3" s="26" t="s">
+      <c r="O3" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="P3" s="26" t="s">
+      <c r="P3" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="Q3" s="26" t="s">
+      <c r="Q3" s="39" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1" spans="1:17">
-      <c r="A5" s="27" t="s">
+    <row r="5" spans="1:17" ht="30" customHeight="1">
+      <c r="A5" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="27" t="s">
+      <c r="C5" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="27" t="s">
+      <c r="E5" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="27" t="s">
+      <c r="F5" s="37" t="s">
         <v>2</v>
       </c>
       <c r="H5" s="1" t="s">
@@ -2174,7 +1603,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1" spans="1:17">
+    <row r="6" spans="1:17" ht="30" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -2187,7 +1616,7 @@
       <c r="E6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H6" s="28">
+      <c r="H6" s="25">
         <f>配置!$B$6*0/9</f>
         <v>0</v>
       </c>
@@ -2196,206 +1625,206 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" ht="14.5" spans="1:17">
+    <row r="7" spans="1:17" ht="15">
       <c r="A7" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="29">
+      <c r="B7" s="26">
         <f>配置!B4</f>
         <v>15</v>
       </c>
       <c r="D7" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="28">
+      <c r="E7" s="25">
         <f>COUNTA(事件!B2:B100)</f>
         <v>15</v>
       </c>
-      <c r="H7" s="30">
+      <c r="H7" s="27">
         <f>配置!$B$6*1/9</f>
         <v>15</v>
       </c>
       <c r="I7" s="15">
         <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(H7/配置!$B$6,0),1),配置!$B$7),0)</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" ht="14.5" spans="1:17">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="15">
       <c r="A8" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="31">
+      <c r="B8" s="28">
         <f>配置!B5</f>
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="D8" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="27">
         <f>COUNTIF(事件!C2:C100,"普通强化门")</f>
         <v>12</v>
       </c>
-      <c r="H8" s="30">
+      <c r="H8" s="27">
         <f>配置!$B$6*2/9</f>
         <v>30</v>
       </c>
       <c r="I8" s="15">
         <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(H8/配置!$B$6,0),1),配置!$B$7),0)</f>
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" ht="14.5" spans="1:17">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="15">
       <c r="A9" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="31">
+      <c r="B9" s="28">
         <f>配置!B6</f>
         <v>135</v>
       </c>
       <c r="D9" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="27">
         <f>SUMIF(事件!B2:B100,"elite",事件!A2:A100)</f>
         <v>80</v>
       </c>
-      <c r="H9" s="30">
+      <c r="H9" s="27">
         <f>配置!$B$6*3/9</f>
         <v>45</v>
       </c>
       <c r="I9" s="15">
         <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(H9/配置!$B$6,0),1),配置!$B$7),0)</f>
-        <v>58</v>
-      </c>
-    </row>
-    <row r="10" ht="14.5" spans="1:17">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" ht="15">
       <c r="A10" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="32">
+      <c r="B10" s="29">
         <f>配置!B7</f>
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="D10" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="33">
+      <c r="E10" s="30">
         <f>SUMIF(事件!B2:B100,"boss",事件!A2:A100)</f>
         <v>135</v>
       </c>
-      <c r="H10" s="30">
+      <c r="H10" s="27">
         <f>配置!$B$6*4/9</f>
         <v>60</v>
       </c>
       <c r="I10" s="15">
         <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(H10/配置!$B$6,0),1),配置!$B$7),0)</f>
-        <v>91</v>
-      </c>
-    </row>
-    <row r="11" ht="14.5" spans="1:17">
-      <c r="H11" s="30">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="15">
+      <c r="H11" s="27">
         <f>配置!$B$6*5/9</f>
         <v>75</v>
       </c>
       <c r="I11" s="15">
         <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(H11/配置!$B$6,0),1),配置!$B$7),0)</f>
-        <v>134</v>
-      </c>
-    </row>
-    <row r="12" ht="14.5" spans="1:17">
-      <c r="H12" s="30">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="15">
+      <c r="H12" s="27">
         <f>配置!$B$6*6/9</f>
         <v>90</v>
       </c>
       <c r="I12" s="15">
         <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(H12/配置!$B$6,0),1),配置!$B$7),0)</f>
-        <v>186</v>
-      </c>
-    </row>
-    <row r="13" ht="14.5" spans="1:17">
-      <c r="H13" s="30">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="15">
+      <c r="H13" s="27">
         <f>配置!$B$6*7/9</f>
         <v>105</v>
       </c>
       <c r="I13" s="15">
         <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(H13/配置!$B$6,0),1),配置!$B$7),0)</f>
-        <v>248</v>
-      </c>
-    </row>
-    <row r="14" ht="14.5" spans="1:17">
-      <c r="H14" s="30">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="15">
+      <c r="H14" s="27">
         <f>配置!$B$6*8/9</f>
         <v>120</v>
       </c>
       <c r="I14" s="15">
         <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(H14/配置!$B$6,0),1),配置!$B$7),0)</f>
-        <v>319</v>
-      </c>
-    </row>
-    <row r="15" ht="14.5" spans="1:17">
-      <c r="H15" s="33">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" ht="15">
+      <c r="H15" s="30">
         <f>配置!$B$6*9/9</f>
         <v>135</v>
       </c>
       <c r="I15" s="19">
         <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(H15/配置!$B$6,0),1),配置!$B$7),0)</f>
-        <v>400</v>
-      </c>
-    </row>
-    <row r="20" ht="28.05" customHeight="1" spans="1:17">
-      <c r="A20" s="27" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="28.05" customHeight="1">
+      <c r="A20" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="B20" s="27" t="s">
+      <c r="B20" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="C20" s="27" t="s">
+      <c r="C20" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="D20" s="27" t="s">
+      <c r="D20" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="E20" s="27" t="s">
+      <c r="E20" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="F20" s="27" t="s">
+      <c r="F20" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="G20" s="27" t="s">
+      <c r="G20" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="H20" s="27" t="s">
+      <c r="H20" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="I20" s="27" t="s">
+      <c r="I20" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="J20" s="27" t="s">
+      <c r="J20" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="K20" s="27" t="s">
+      <c r="K20" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="L20" s="27" t="s">
+      <c r="L20" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="M20" s="27" t="s">
+      <c r="M20" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="N20" s="27" t="s">
+      <c r="N20" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="O20" s="27" t="s">
+      <c r="O20" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="P20" s="27" t="s">
+      <c r="P20" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="Q20" s="27" t="s">
+      <c r="Q20" s="37" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="21" ht="30" customHeight="1" spans="1:17">
+    <row r="21" spans="1:17" ht="30" customHeight="1">
       <c r="A21" s="1" t="s">
         <v>17</v>
       </c>
@@ -2423,41 +1852,41 @@
       <c r="I21" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J21" s="1" t="s">
+      <c r="J21" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="K21" s="1" t="s">
+      <c r="K21" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="L21" s="1" t="s">
+      <c r="L21" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="M21" s="1" t="s">
+      <c r="M21" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="N21" s="1" t="s">
+      <c r="N21" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="O21" s="1" t="s">
+      <c r="O21" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="P21" s="1" t="s">
+      <c r="P21" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="Q21" s="1" t="s">
+      <c r="Q21" s="38" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="22" ht="34.05" customHeight="1" spans="1:17">
-      <c r="A22" s="28">
+    <row r="22" spans="1:17" ht="34.049999999999997" customHeight="1">
+      <c r="A22" s="25">
         <f>事件!A2</f>
         <v>2</v>
       </c>
-      <c r="B22" s="34" t="str">
+      <c r="B22" s="31" t="str">
         <f>事件!B2</f>
         <v>start_gate</v>
       </c>
-      <c r="C22" s="34" t="str">
+      <c r="C22" s="31" t="str">
         <f>事件!C2</f>
         <v>开局食材门</v>
       </c>
@@ -2481,790 +1910,789 @@
         <f>事件!K2</f>
         <v>45</v>
       </c>
-      <c r="I22" s="34" t="str">
+      <c r="I22" s="31" t="str">
         <f>TEXT(事件!M2,"0")&amp;"–"&amp;TEXT(事件!N2,"0")</f>
         <v>15–30</v>
       </c>
-      <c r="J22" s="35" t="s">
+      <c r="J22" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="K22" s="26" t="s">
+      <c r="K22" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="L22" s="26"/>
-      <c r="M22" s="26"/>
-      <c r="N22" s="26"/>
-      <c r="O22" s="26"/>
-      <c r="P22" s="26"/>
-      <c r="Q22" s="26"/>
-    </row>
-    <row r="23" ht="34.05" customHeight="1" spans="1:17">
-      <c r="A23" s="30">
+      <c r="L22" s="39"/>
+      <c r="M22" s="39"/>
+      <c r="N22" s="39"/>
+      <c r="O22" s="39"/>
+      <c r="P22" s="39"/>
+      <c r="Q22" s="39"/>
+    </row>
+    <row r="23" spans="1:17" ht="34.049999999999997" customHeight="1">
+      <c r="A23" s="27">
         <f>事件!A3</f>
         <v>18</v>
       </c>
-      <c r="B23" s="36" t="str">
+      <c r="B23" s="33" t="str">
         <f>事件!B3</f>
         <v>gate_0</v>
       </c>
-      <c r="C23" s="36" t="str">
+      <c r="C23" s="33" t="str">
         <f>事件!C3</f>
         <v>普通强化门</v>
       </c>
       <c r="D23" s="15">
         <f>事件!E3</f>
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E23" s="15">
         <f>事件!F3</f>
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F23" s="15">
         <f>事件!G3</f>
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G23" s="15">
         <f>事件!H3</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H23" s="15">
         <f>事件!K3</f>
-        <v>66</v>
-      </c>
-      <c r="I23" s="36" t="str">
+        <v>60</v>
+      </c>
+      <c r="I23" s="33" t="str">
         <f>TEXT(事件!M3,"0")&amp;"–"&amp;TEXT(事件!N3,"0")</f>
-        <v>22–44</v>
-      </c>
-      <c r="J23" s="35" t="s">
+        <v>20–40</v>
+      </c>
+      <c r="J23" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="K23" s="26" t="s">
+      <c r="K23" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="L23" s="26"/>
-      <c r="M23" s="26"/>
-      <c r="N23" s="26"/>
-      <c r="O23" s="26"/>
-      <c r="P23" s="26"/>
-      <c r="Q23" s="26"/>
-    </row>
-    <row r="24" ht="34.05" customHeight="1" spans="1:17">
-      <c r="A24" s="30">
+      <c r="L23" s="39"/>
+      <c r="M23" s="39"/>
+      <c r="N23" s="39"/>
+      <c r="O23" s="39"/>
+      <c r="P23" s="39"/>
+      <c r="Q23" s="39"/>
+    </row>
+    <row r="24" spans="1:17" ht="34.049999999999997" customHeight="1">
+      <c r="A24" s="27">
         <f>事件!A4</f>
         <v>27</v>
       </c>
-      <c r="B24" s="36" t="str">
+      <c r="B24" s="33" t="str">
         <f>事件!B4</f>
         <v>gate_1</v>
       </c>
-      <c r="C24" s="36" t="str">
+      <c r="C24" s="33" t="str">
         <f>事件!C4</f>
         <v>普通强化门</v>
       </c>
       <c r="D24" s="15">
         <f>事件!E4</f>
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E24" s="15">
         <f>事件!F4</f>
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F24" s="15">
         <f>事件!G4</f>
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="G24" s="15">
         <f>事件!H4</f>
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H24" s="15">
         <f>事件!K4</f>
-        <v>90</v>
-      </c>
-      <c r="I24" s="36" t="str">
+        <v>78</v>
+      </c>
+      <c r="I24" s="33" t="str">
         <f>TEXT(事件!M4,"0")&amp;"–"&amp;TEXT(事件!N4,"0")</f>
-        <v>30–60</v>
-      </c>
-      <c r="J24" s="35" t="s">
+        <v>26–52</v>
+      </c>
+      <c r="J24" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="K24" s="26" t="s">
+      <c r="K24" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="L24" s="26"/>
-      <c r="M24" s="26"/>
-      <c r="N24" s="26"/>
-      <c r="O24" s="26"/>
-      <c r="P24" s="26"/>
-      <c r="Q24" s="26"/>
-    </row>
-    <row r="25" ht="34.05" customHeight="1" spans="1:17">
-      <c r="A25" s="30">
+      <c r="L24" s="39"/>
+      <c r="M24" s="39"/>
+      <c r="N24" s="39"/>
+      <c r="O24" s="39"/>
+      <c r="P24" s="39"/>
+      <c r="Q24" s="39"/>
+    </row>
+    <row r="25" spans="1:17" ht="34.049999999999997" customHeight="1">
+      <c r="A25" s="27">
         <f>事件!A5</f>
         <v>39</v>
       </c>
-      <c r="B25" s="36" t="str">
+      <c r="B25" s="33" t="str">
         <f>事件!B5</f>
         <v>gate_2</v>
       </c>
-      <c r="C25" s="36" t="str">
+      <c r="C25" s="33" t="str">
         <f>事件!C5</f>
         <v>普通强化门</v>
       </c>
       <c r="D25" s="15">
         <f>事件!E5</f>
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="E25" s="15">
         <f>事件!F5</f>
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F25" s="15">
         <f>事件!G5</f>
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="G25" s="15">
         <f>事件!H5</f>
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="H25" s="15">
         <f>事件!K5</f>
-        <v>141</v>
-      </c>
-      <c r="I25" s="36" t="str">
+        <v>120</v>
+      </c>
+      <c r="I25" s="33" t="str">
         <f>TEXT(事件!M5,"0")&amp;"–"&amp;TEXT(事件!N5,"0")</f>
-        <v>47–94</v>
-      </c>
-      <c r="J25" s="35" t="s">
+        <v>40–80</v>
+      </c>
+      <c r="J25" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="K25" s="26" t="s">
+      <c r="K25" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="L25" s="26"/>
-      <c r="M25" s="26"/>
-      <c r="N25" s="26"/>
-      <c r="O25" s="26"/>
-      <c r="P25" s="26"/>
-      <c r="Q25" s="26"/>
-    </row>
-    <row r="26" ht="34.05" customHeight="1" spans="1:17">
-      <c r="A26" s="30">
+      <c r="L25" s="39"/>
+      <c r="M25" s="39"/>
+      <c r="N25" s="39"/>
+      <c r="O25" s="39"/>
+      <c r="P25" s="39"/>
+      <c r="Q25" s="39"/>
+    </row>
+    <row r="26" spans="1:17" ht="34.049999999999997" customHeight="1">
+      <c r="A26" s="27">
         <f>事件!A6</f>
         <v>50</v>
       </c>
-      <c r="B26" s="36" t="str">
+      <c r="B26" s="33" t="str">
         <f>事件!B6</f>
         <v>gate_3</v>
       </c>
-      <c r="C26" s="36" t="str">
+      <c r="C26" s="33" t="str">
         <f>事件!C6</f>
         <v>普通强化门</v>
       </c>
       <c r="D26" s="15">
         <f>事件!E6</f>
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="E26" s="15">
         <f>事件!F6</f>
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="F26" s="15">
         <f>事件!G6</f>
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="G26" s="15">
         <f>事件!H6</f>
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="H26" s="15">
         <f>事件!K6</f>
-        <v>204</v>
-      </c>
-      <c r="I26" s="36" t="str">
+        <v>171</v>
+      </c>
+      <c r="I26" s="33" t="str">
         <f>TEXT(事件!M6,"0")&amp;"–"&amp;TEXT(事件!N6,"0")</f>
-        <v>68–136</v>
-      </c>
-      <c r="J26" s="35" t="s">
+        <v>57–114</v>
+      </c>
+      <c r="J26" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="K26" s="26" t="s">
+      <c r="K26" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="L26" s="26"/>
-      <c r="M26" s="26"/>
-      <c r="N26" s="26"/>
-      <c r="O26" s="26"/>
-      <c r="P26" s="26"/>
-      <c r="Q26" s="26"/>
-    </row>
-    <row r="27" ht="34.05" customHeight="1" spans="1:17">
-      <c r="A27" s="30">
+      <c r="L26" s="39"/>
+      <c r="M26" s="39"/>
+      <c r="N26" s="39"/>
+      <c r="O26" s="39"/>
+      <c r="P26" s="39"/>
+      <c r="Q26" s="39"/>
+    </row>
+    <row r="27" spans="1:17" ht="34.049999999999997" customHeight="1">
+      <c r="A27" s="27">
         <f>事件!A7</f>
         <v>62</v>
       </c>
-      <c r="B27" s="36" t="str">
+      <c r="B27" s="33" t="str">
         <f>事件!B7</f>
         <v>gate_4</v>
       </c>
-      <c r="C27" s="36" t="str">
+      <c r="C27" s="33" t="str">
         <f>事件!C7</f>
         <v>普通强化门</v>
       </c>
       <c r="D27" s="15">
         <f>事件!E7</f>
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="E27" s="15">
         <f>事件!F7</f>
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="F27" s="15">
         <f>事件!G7</f>
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="G27" s="15">
         <f>事件!H7</f>
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="H27" s="15">
         <f>事件!K7</f>
-        <v>288</v>
-      </c>
-      <c r="I27" s="36" t="str">
+        <v>240</v>
+      </c>
+      <c r="I27" s="33" t="str">
         <f>TEXT(事件!M7,"0")&amp;"–"&amp;TEXT(事件!N7,"0")</f>
-        <v>96–192</v>
-      </c>
-      <c r="J27" s="35" t="s">
+        <v>80–160</v>
+      </c>
+      <c r="J27" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="K27" s="26" t="s">
+      <c r="K27" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="L27" s="26"/>
-      <c r="M27" s="26"/>
-      <c r="N27" s="26"/>
-      <c r="O27" s="26"/>
-      <c r="P27" s="26"/>
-      <c r="Q27" s="26"/>
-    </row>
-    <row r="28" ht="14.5" spans="1:17">
-      <c r="A28" s="30">
+      <c r="L27" s="39"/>
+      <c r="M27" s="39"/>
+      <c r="N27" s="39"/>
+      <c r="O27" s="39"/>
+      <c r="P27" s="39"/>
+      <c r="Q27" s="39"/>
+    </row>
+    <row r="28" spans="1:17" ht="15">
+      <c r="A28" s="27">
         <f>事件!A8</f>
         <v>74</v>
       </c>
-      <c r="B28" s="36" t="str">
+      <c r="B28" s="33" t="str">
         <f>事件!B8</f>
         <v>gate_5</v>
       </c>
-      <c r="C28" s="36" t="str">
+      <c r="C28" s="33" t="str">
         <f>事件!C8</f>
         <v>普通强化门</v>
       </c>
       <c r="D28" s="15">
         <f>事件!E8</f>
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="E28" s="15">
         <f>事件!F8</f>
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="F28" s="15">
         <f>事件!G8</f>
-        <v>262</v>
+        <v>220</v>
       </c>
       <c r="G28" s="15">
         <f>事件!H8</f>
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="H28" s="15">
         <f>事件!K8</f>
-        <v>393</v>
-      </c>
-      <c r="I28" s="36" t="str">
+        <v>330</v>
+      </c>
+      <c r="I28" s="33" t="str">
         <f>TEXT(事件!M8,"0")&amp;"–"&amp;TEXT(事件!N8,"0")</f>
-        <v>131–262</v>
-      </c>
-    </row>
-    <row r="29" ht="14.5" spans="1:17">
-      <c r="A29" s="30">
+        <v>110–220</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" ht="15">
+      <c r="A29" s="27">
         <f>事件!A9</f>
         <v>80</v>
       </c>
-      <c r="B29" s="36" t="str">
+      <c r="B29" s="33" t="str">
         <f>事件!B9</f>
         <v>elite</v>
       </c>
-      <c r="C29" s="36" t="str">
+      <c r="C29" s="33" t="str">
         <f>事件!C9</f>
         <v>精英</v>
       </c>
       <c r="D29" s="15">
         <f>事件!E9</f>
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="E29" s="15">
         <f>事件!F9</f>
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="F29" s="15">
         <f>事件!G9</f>
-        <v>300</v>
+        <v>254</v>
       </c>
       <c r="G29" s="15">
         <f>事件!H9</f>
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="H29" s="15">
         <f>事件!K9</f>
-        <v>450</v>
-      </c>
-      <c r="I29" s="36" t="str">
+        <v>381</v>
+      </c>
+      <c r="I29" s="33" t="str">
         <f>TEXT(事件!M9,"0")&amp;"–"&amp;TEXT(事件!N9,"0")</f>
-        <v>150–300</v>
-      </c>
-    </row>
-    <row r="30" ht="14.5" spans="1:17">
-      <c r="A30" s="30">
+        <v>127–254</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" ht="15">
+      <c r="A30" s="27">
         <f>事件!A10</f>
         <v>86</v>
       </c>
-      <c r="B30" s="36" t="str">
+      <c r="B30" s="33" t="str">
         <f>事件!B10</f>
         <v>gate_6</v>
       </c>
-      <c r="C30" s="36" t="str">
+      <c r="C30" s="33" t="str">
         <f>事件!C10</f>
         <v>普通强化门</v>
       </c>
       <c r="D30" s="15">
         <f>事件!E10</f>
-        <v>171</v>
+        <v>145</v>
       </c>
       <c r="E30" s="15">
         <f>事件!F10</f>
-        <v>171</v>
+        <v>145</v>
       </c>
       <c r="F30" s="15">
         <f>事件!G10</f>
-        <v>342</v>
+        <v>290</v>
       </c>
       <c r="G30" s="15">
         <f>事件!H10</f>
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="H30" s="15">
         <f>事件!K10</f>
-        <v>513</v>
-      </c>
-      <c r="I30" s="36" t="str">
+        <v>435</v>
+      </c>
+      <c r="I30" s="33" t="str">
         <f>TEXT(事件!M10,"0")&amp;"–"&amp;TEXT(事件!N10,"0")</f>
-        <v>171–342</v>
-      </c>
-    </row>
-    <row r="31" ht="14.5" spans="1:17">
-      <c r="A31" s="30">
+        <v>145–290</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" ht="15">
+      <c r="A31" s="27">
         <f>事件!A11</f>
         <v>94</v>
       </c>
-      <c r="B31" s="36" t="str">
+      <c r="B31" s="33" t="str">
         <f>事件!B11</f>
         <v>gate_7</v>
       </c>
-      <c r="C31" s="36" t="str">
+      <c r="C31" s="33" t="str">
         <f>事件!C11</f>
         <v>普通强化门</v>
       </c>
       <c r="D31" s="15">
         <f>事件!E11</f>
-        <v>202</v>
+        <v>172</v>
       </c>
       <c r="E31" s="15">
         <f>事件!F11</f>
-        <v>202</v>
+        <v>172</v>
       </c>
       <c r="F31" s="15">
         <f>事件!G11</f>
-        <v>404</v>
+        <v>344</v>
       </c>
       <c r="G31" s="15">
         <f>事件!H11</f>
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="H31" s="15">
         <f>事件!K11</f>
-        <v>606</v>
-      </c>
-      <c r="I31" s="36" t="str">
+        <v>516</v>
+      </c>
+      <c r="I31" s="33" t="str">
         <f>TEXT(事件!M11,"0")&amp;"–"&amp;TEXT(事件!N11,"0")</f>
-        <v>202–404</v>
-      </c>
-    </row>
-    <row r="32" ht="14.5" spans="1:17">
-      <c r="A32" s="30">
+        <v>172–344</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" ht="15">
+      <c r="A32" s="27">
         <f>事件!A12</f>
         <v>102</v>
       </c>
-      <c r="B32" s="36" t="str">
+      <c r="B32" s="33" t="str">
         <f>事件!B12</f>
         <v>gate_8</v>
       </c>
-      <c r="C32" s="36" t="str">
+      <c r="C32" s="33" t="str">
         <f>事件!C12</f>
         <v>普通强化门</v>
       </c>
       <c r="D32" s="15">
         <f>事件!E12</f>
-        <v>235</v>
+        <v>201</v>
       </c>
       <c r="E32" s="15">
         <f>事件!F12</f>
-        <v>235</v>
+        <v>201</v>
       </c>
       <c r="F32" s="15">
         <f>事件!G12</f>
-        <v>470</v>
+        <v>402</v>
       </c>
       <c r="G32" s="15">
         <f>事件!H12</f>
-        <v>176</v>
+        <v>151</v>
       </c>
       <c r="H32" s="15">
         <f>事件!K12</f>
-        <v>705</v>
-      </c>
-      <c r="I32" s="36" t="str">
+        <v>603</v>
+      </c>
+      <c r="I32" s="33" t="str">
         <f>TEXT(事件!M12,"0")&amp;"–"&amp;TEXT(事件!N12,"0")</f>
-        <v>235–470</v>
-      </c>
-    </row>
-    <row r="33" ht="14.5" spans="1:17">
-      <c r="A33" s="30">
+        <v>201–402</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" ht="15">
+      <c r="A33" s="27">
         <f>事件!A13</f>
         <v>110</v>
       </c>
-      <c r="B33" s="36" t="str">
+      <c r="B33" s="33" t="str">
         <f>事件!B13</f>
         <v>gate_9</v>
       </c>
-      <c r="C33" s="36" t="str">
+      <c r="C33" s="33" t="str">
         <f>事件!C13</f>
         <v>普通强化门</v>
       </c>
       <c r="D33" s="15">
         <f>事件!E13</f>
-        <v>271</v>
+        <v>233</v>
       </c>
       <c r="E33" s="15">
         <f>事件!F13</f>
-        <v>271</v>
+        <v>233</v>
       </c>
       <c r="F33" s="15">
         <f>事件!G13</f>
-        <v>542</v>
+        <v>466</v>
       </c>
       <c r="G33" s="15">
         <f>事件!H13</f>
-        <v>203</v>
+        <v>175</v>
       </c>
       <c r="H33" s="15">
         <f>事件!K13</f>
-        <v>813</v>
-      </c>
-      <c r="I33" s="36" t="str">
+        <v>699</v>
+      </c>
+      <c r="I33" s="33" t="str">
         <f>TEXT(事件!M13,"0")&amp;"–"&amp;TEXT(事件!N13,"0")</f>
-        <v>271–542</v>
-      </c>
-    </row>
-    <row r="34" ht="14.5" spans="1:17">
-      <c r="A34" s="30">
+        <v>233–466</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" ht="15">
+      <c r="A34" s="27">
         <f>事件!A14</f>
         <v>118</v>
       </c>
-      <c r="B34" s="36" t="str">
+      <c r="B34" s="33" t="str">
         <f>事件!B14</f>
         <v>gate_10</v>
       </c>
-      <c r="C34" s="36" t="str">
+      <c r="C34" s="33" t="str">
         <f>事件!C14</f>
         <v>普通强化门</v>
       </c>
       <c r="D34" s="15">
         <f>事件!E14</f>
-        <v>309</v>
+        <v>268</v>
       </c>
       <c r="E34" s="15">
         <f>事件!F14</f>
-        <v>309</v>
+        <v>268</v>
       </c>
       <c r="F34" s="15">
         <f>事件!G14</f>
-        <v>618</v>
+        <v>536</v>
       </c>
       <c r="G34" s="15">
         <f>事件!H14</f>
-        <v>232</v>
+        <v>201</v>
       </c>
       <c r="H34" s="15">
         <f>事件!K14</f>
-        <v>927</v>
-      </c>
-      <c r="I34" s="36" t="str">
+        <v>804</v>
+      </c>
+      <c r="I34" s="33" t="str">
         <f>TEXT(事件!M14,"0")&amp;"–"&amp;TEXT(事件!N14,"0")</f>
-        <v>309–618</v>
-      </c>
-    </row>
-    <row r="35" ht="14.5" spans="1:17">
-      <c r="A35" s="30">
+        <v>268–536</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" ht="15">
+      <c r="A35" s="27">
         <f>事件!A15</f>
         <v>126</v>
       </c>
-      <c r="B35" s="36" t="str">
+      <c r="B35" s="33" t="str">
         <f>事件!B15</f>
         <v>gate_11</v>
       </c>
-      <c r="C35" s="36" t="str">
+      <c r="C35" s="33" t="str">
         <f>事件!C15</f>
         <v>普通强化门</v>
       </c>
       <c r="D35" s="15">
         <f>事件!E15</f>
-        <v>350</v>
+        <v>305</v>
       </c>
       <c r="E35" s="15">
         <f>事件!F15</f>
-        <v>350</v>
+        <v>305</v>
       </c>
       <c r="F35" s="15">
         <f>事件!G15</f>
-        <v>700</v>
+        <v>610</v>
       </c>
       <c r="G35" s="15">
         <f>事件!H15</f>
-        <v>263</v>
+        <v>229</v>
       </c>
       <c r="H35" s="15">
         <f>事件!K15</f>
-        <v>1050</v>
-      </c>
-      <c r="I35" s="36" t="str">
+        <v>915</v>
+      </c>
+      <c r="I35" s="33" t="str">
         <f>TEXT(事件!M15,"0")&amp;"–"&amp;TEXT(事件!N15,"0")</f>
-        <v>350–700</v>
-      </c>
-    </row>
-    <row r="36" ht="14.5" spans="1:17">
-      <c r="A36" s="33">
+        <v>305–610</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" ht="15">
+      <c r="A36" s="30">
         <f>事件!A16</f>
         <v>135</v>
       </c>
-      <c r="B36" s="37" t="str">
+      <c r="B36" s="34" t="str">
         <f>事件!B16</f>
         <v>boss</v>
       </c>
-      <c r="C36" s="37" t="str">
+      <c r="C36" s="34" t="str">
         <f>事件!C16</f>
         <v>Boss</v>
       </c>
       <c r="D36" s="19">
         <f>事件!E16</f>
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="E36" s="19">
         <f>事件!F16</f>
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="F36" s="19">
         <f>事件!G16</f>
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="G36" s="19">
         <f>事件!H16</f>
-        <v>300</v>
+        <v>263</v>
       </c>
       <c r="H36" s="19">
         <f>事件!K16</f>
-        <v>1200</v>
-      </c>
-      <c r="I36" s="37" t="str">
+        <v>1050</v>
+      </c>
+      <c r="I36" s="34" t="str">
         <f>TEXT(事件!M16,"0")&amp;"–"&amp;TEXT(事件!N16,"0")</f>
-        <v>400–800</v>
-      </c>
-    </row>
-    <row r="38" ht="28.05" customHeight="1" spans="1:17">
-      <c r="A38" s="27" t="s">
+        <v>350–700</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" ht="28.05" customHeight="1">
+      <c r="A38" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="B38" s="27" t="s">
+      <c r="B38" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="C38" s="27" t="s">
+      <c r="C38" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="D38" s="27" t="s">
+      <c r="D38" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="E38" s="27" t="s">
+      <c r="E38" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="F38" s="27" t="s">
+      <c r="F38" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="G38" s="27" t="s">
+      <c r="G38" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="H38" s="27" t="s">
+      <c r="H38" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="I38" s="27" t="s">
+      <c r="I38" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="J38" s="27" t="s">
+      <c r="J38" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="K38" s="27" t="s">
+      <c r="K38" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="L38" s="27" t="s">
+      <c r="L38" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="M38" s="27" t="s">
+      <c r="M38" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="N38" s="27" t="s">
+      <c r="N38" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="O38" s="27" t="s">
+      <c r="O38" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="P38" s="27" t="s">
+      <c r="P38" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="Q38" s="27" t="s">
+      <c r="Q38" s="37" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="39" ht="31.95" customHeight="1" spans="1:17">
-      <c r="A39" s="38" t="s">
+    <row r="39" spans="1:17" ht="31.95" customHeight="1">
+      <c r="A39" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="B39" s="26" t="s">
+      <c r="B39" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="C39" s="26"/>
-      <c r="D39" s="26"/>
-      <c r="E39" s="26"/>
-      <c r="F39" s="26"/>
-      <c r="G39" s="26"/>
-      <c r="H39" s="26"/>
-      <c r="I39" s="26"/>
-      <c r="J39" s="26"/>
-      <c r="K39" s="26"/>
-      <c r="L39" s="26"/>
-      <c r="M39" s="26"/>
-      <c r="N39" s="26"/>
-      <c r="O39" s="26"/>
-      <c r="P39" s="26"/>
-      <c r="Q39" s="26"/>
-    </row>
-    <row r="40" ht="31.95" customHeight="1" spans="1:17">
-      <c r="A40" s="38" t="s">
+      <c r="C39" s="39"/>
+      <c r="D39" s="39"/>
+      <c r="E39" s="39"/>
+      <c r="F39" s="39"/>
+      <c r="G39" s="39"/>
+      <c r="H39" s="39"/>
+      <c r="I39" s="39"/>
+      <c r="J39" s="39"/>
+      <c r="K39" s="39"/>
+      <c r="L39" s="39"/>
+      <c r="M39" s="39"/>
+      <c r="N39" s="39"/>
+      <c r="O39" s="39"/>
+      <c r="P39" s="39"/>
+      <c r="Q39" s="39"/>
+    </row>
+    <row r="40" spans="1:17" ht="31.95" customHeight="1">
+      <c r="A40" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="26" t="s">
+      <c r="B40" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="C40" s="26"/>
-      <c r="D40" s="26"/>
-      <c r="E40" s="26"/>
-      <c r="F40" s="26"/>
-      <c r="G40" s="26"/>
-      <c r="H40" s="26"/>
-      <c r="I40" s="26"/>
-      <c r="J40" s="26"/>
-      <c r="K40" s="26"/>
-      <c r="L40" s="26"/>
-      <c r="M40" s="26"/>
-      <c r="N40" s="26"/>
-      <c r="O40" s="26"/>
-      <c r="P40" s="26"/>
-      <c r="Q40" s="26"/>
-    </row>
-    <row r="41" ht="31.95" customHeight="1" spans="1:17">
-      <c r="A41" s="38" t="s">
+      <c r="C40" s="39"/>
+      <c r="D40" s="39"/>
+      <c r="E40" s="39"/>
+      <c r="F40" s="39"/>
+      <c r="G40" s="39"/>
+      <c r="H40" s="39"/>
+      <c r="I40" s="39"/>
+      <c r="J40" s="39"/>
+      <c r="K40" s="39"/>
+      <c r="L40" s="39"/>
+      <c r="M40" s="39"/>
+      <c r="N40" s="39"/>
+      <c r="O40" s="39"/>
+      <c r="P40" s="39"/>
+      <c r="Q40" s="39"/>
+    </row>
+    <row r="41" spans="1:17" ht="31.95" customHeight="1">
+      <c r="A41" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="B41" s="26" t="s">
+      <c r="B41" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="C41" s="26"/>
-      <c r="D41" s="26"/>
-      <c r="E41" s="26"/>
-      <c r="F41" s="26"/>
-      <c r="G41" s="26"/>
-      <c r="H41" s="26"/>
-      <c r="I41" s="26"/>
-      <c r="J41" s="26"/>
-      <c r="K41" s="26"/>
-      <c r="L41" s="26"/>
-      <c r="M41" s="26"/>
-      <c r="N41" s="26"/>
-      <c r="O41" s="26"/>
-      <c r="P41" s="26"/>
-      <c r="Q41" s="26"/>
-    </row>
-    <row r="42" ht="31.95" customHeight="1" spans="1:17">
-      <c r="A42" s="38" t="s">
+      <c r="C41" s="39"/>
+      <c r="D41" s="39"/>
+      <c r="E41" s="39"/>
+      <c r="F41" s="39"/>
+      <c r="G41" s="39"/>
+      <c r="H41" s="39"/>
+      <c r="I41" s="39"/>
+      <c r="J41" s="39"/>
+      <c r="K41" s="39"/>
+      <c r="L41" s="39"/>
+      <c r="M41" s="39"/>
+      <c r="N41" s="39"/>
+      <c r="O41" s="39"/>
+      <c r="P41" s="39"/>
+      <c r="Q41" s="39"/>
+    </row>
+    <row r="42" spans="1:17" ht="31.95" customHeight="1">
+      <c r="A42" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="B42" s="26" t="s">
+      <c r="B42" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="C42" s="26"/>
-      <c r="D42" s="26"/>
-      <c r="E42" s="26"/>
-      <c r="F42" s="26"/>
-      <c r="G42" s="26"/>
-      <c r="H42" s="26"/>
-      <c r="I42" s="26"/>
-      <c r="J42" s="26"/>
-      <c r="K42" s="26"/>
-      <c r="L42" s="26"/>
-      <c r="M42" s="26"/>
-      <c r="N42" s="26"/>
-      <c r="O42" s="26"/>
-      <c r="P42" s="26"/>
-      <c r="Q42" s="26"/>
+      <c r="C42" s="39"/>
+      <c r="D42" s="39"/>
+      <c r="E42" s="39"/>
+      <c r="F42" s="39"/>
+      <c r="G42" s="39"/>
+      <c r="H42" s="39"/>
+      <c r="I42" s="39"/>
+      <c r="J42" s="39"/>
+      <c r="K42" s="39"/>
+      <c r="L42" s="39"/>
+      <c r="M42" s="39"/>
+      <c r="N42" s="39"/>
+      <c r="O42" s="39"/>
+      <c r="P42" s="39"/>
+      <c r="Q42" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A38:Q38"/>
+    <mergeCell ref="B39:Q39"/>
+    <mergeCell ref="B40:Q40"/>
+    <mergeCell ref="B41:Q41"/>
+    <mergeCell ref="B42:Q42"/>
+    <mergeCell ref="K23:Q23"/>
+    <mergeCell ref="K24:Q24"/>
+    <mergeCell ref="K25:Q25"/>
+    <mergeCell ref="K26:Q26"/>
+    <mergeCell ref="K27:Q27"/>
     <mergeCell ref="A1:Q1"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A20:Q20"/>
     <mergeCell ref="J21:Q21"/>
     <mergeCell ref="K22:Q22"/>
-    <mergeCell ref="K23:Q23"/>
-    <mergeCell ref="K24:Q24"/>
-    <mergeCell ref="K25:Q25"/>
-    <mergeCell ref="K26:Q26"/>
-    <mergeCell ref="K27:Q27"/>
-    <mergeCell ref="A38:Q38"/>
-    <mergeCell ref="B39:Q39"/>
-    <mergeCell ref="B40:Q40"/>
-    <mergeCell ref="B41:Q41"/>
-    <mergeCell ref="B42:Q42"/>
     <mergeCell ref="A2:Q3"/>
   </mergeCells>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -3273,7 +2701,7 @@
     <col min="5" max="5" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:5">
+    <row r="1" spans="1:5" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3290,7 +2718,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" ht="34.05" customHeight="1" spans="1:5">
+    <row r="2" spans="1:5" ht="34.049999999999997" customHeight="1">
       <c r="A2" s="20" t="s">
         <v>49</v>
       </c>
@@ -3307,7 +2735,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" ht="34.05" customHeight="1" spans="1:5">
+    <row r="3" spans="1:5" ht="34.049999999999997" customHeight="1">
       <c r="A3" s="21" t="s">
         <v>54</v>
       </c>
@@ -3324,7 +2752,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" ht="34.05" customHeight="1" spans="1:5">
+    <row r="4" spans="1:5" ht="34.049999999999997" customHeight="1">
       <c r="A4" s="21" t="s">
         <v>57</v>
       </c>
@@ -3341,12 +2769,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" ht="34.05" customHeight="1" spans="1:5">
+    <row r="5" spans="1:5" ht="34.049999999999997" customHeight="1">
       <c r="A5" s="21" t="s">
         <v>61</v>
       </c>
       <c r="B5" s="22">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>62</v>
@@ -3358,7 +2786,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="6" ht="34.05" customHeight="1" spans="1:5">
+    <row r="6" spans="1:5" ht="34.049999999999997" customHeight="1">
       <c r="A6" s="21" t="s">
         <v>65</v>
       </c>
@@ -3375,12 +2803,12 @@
         <v>68</v>
       </c>
     </row>
-    <row r="7" ht="34.05" customHeight="1" spans="1:5">
+    <row r="7" spans="1:5" ht="34.049999999999997" customHeight="1">
       <c r="A7" s="23" t="s">
         <v>69</v>
       </c>
       <c r="B7" s="24">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>70</v>
@@ -3393,8 +2821,8 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -3402,10 +2830,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:N16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -3416,7 +2843,7 @@
     <col min="12" max="14" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:14">
+    <row r="1" spans="1:14" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
@@ -3460,7 +2887,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" ht="31.95" customHeight="1" spans="1:14">
+    <row r="2" spans="1:14" ht="31.95" customHeight="1">
       <c r="A2" s="8">
         <v>2</v>
       </c>
@@ -3514,7 +2941,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" ht="31.95" customHeight="1" spans="1:14">
+    <row r="3" spans="1:14" ht="31.95" customHeight="1">
       <c r="A3" s="12">
         <v>18</v>
       </c>
@@ -3529,46 +2956,46 @@
       </c>
       <c r="E3" s="15">
         <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A3/配置!$B$6,0),1),配置!$B$7),0)</f>
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F3" s="15">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G3" s="15">
         <f t="shared" si="1"/>
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="H3" s="15">
         <f t="shared" si="2"/>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I3" s="15">
         <f t="shared" si="3"/>
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="J3" s="15">
         <f t="shared" si="4"/>
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="K3" s="15">
         <f t="shared" si="5"/>
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="L3" s="15">
         <f t="shared" si="6"/>
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="M3" s="15">
         <f t="shared" si="7"/>
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N3" s="15">
         <f t="shared" si="8"/>
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" ht="31.95" customHeight="1" spans="1:14">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="31.95" customHeight="1">
       <c r="A4" s="12">
         <v>27</v>
       </c>
@@ -3583,46 +3010,46 @@
       </c>
       <c r="E4" s="15">
         <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A4/配置!$B$6,0),1),配置!$B$7),0)</f>
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F4" s="15">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G4" s="15">
         <f t="shared" si="1"/>
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="H4" s="15">
         <f t="shared" si="2"/>
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I4" s="15">
         <f t="shared" si="3"/>
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="J4" s="15">
         <f t="shared" si="4"/>
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="K4" s="15">
         <f t="shared" si="5"/>
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="L4" s="15">
         <f t="shared" si="6"/>
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="M4" s="15">
         <f t="shared" si="7"/>
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="N4" s="15">
         <f t="shared" si="8"/>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" ht="31.95" customHeight="1" spans="1:14">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="31.95" customHeight="1">
       <c r="A5" s="12">
         <v>39</v>
       </c>
@@ -3637,46 +3064,46 @@
       </c>
       <c r="E5" s="15">
         <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A5/配置!$B$6,0),1),配置!$B$7),0)</f>
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F5" s="15">
         <f t="shared" si="0"/>
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G5" s="15">
         <f t="shared" si="1"/>
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="H5" s="15">
         <f t="shared" si="2"/>
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I5" s="15">
         <f t="shared" si="3"/>
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="J5" s="15">
         <f t="shared" si="4"/>
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="K5" s="15">
         <f t="shared" si="5"/>
-        <v>141</v>
+        <v>120</v>
       </c>
       <c r="L5" s="15">
         <f t="shared" si="6"/>
-        <v>264</v>
+        <v>225</v>
       </c>
       <c r="M5" s="15">
         <f t="shared" si="7"/>
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="N5" s="15">
         <f t="shared" si="8"/>
-        <v>94</v>
-      </c>
-    </row>
-    <row r="6" ht="31.95" customHeight="1" spans="1:14">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="31.95" customHeight="1">
       <c r="A6" s="12">
         <v>50</v>
       </c>
@@ -3691,46 +3118,46 @@
       </c>
       <c r="E6" s="15">
         <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A6/配置!$B$6,0),1),配置!$B$7),0)</f>
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="F6" s="15">
         <f t="shared" si="0"/>
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="G6" s="15">
         <f t="shared" si="1"/>
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="H6" s="15">
         <f t="shared" si="2"/>
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="I6" s="15">
         <f t="shared" si="3"/>
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="J6" s="15">
         <f t="shared" si="4"/>
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="K6" s="15">
         <f t="shared" si="5"/>
-        <v>204</v>
+        <v>171</v>
       </c>
       <c r="L6" s="15">
         <f t="shared" si="6"/>
-        <v>383</v>
+        <v>321</v>
       </c>
       <c r="M6" s="15">
         <f t="shared" si="7"/>
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="N6" s="15">
         <f t="shared" si="8"/>
-        <v>136</v>
-      </c>
-    </row>
-    <row r="7" ht="31.95" customHeight="1" spans="1:14">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="31.95" customHeight="1">
       <c r="A7" s="12">
         <v>62</v>
       </c>
@@ -3745,46 +3172,46 @@
       </c>
       <c r="E7" s="15">
         <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A7/配置!$B$6,0),1),配置!$B$7),0)</f>
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="F7" s="15">
         <f t="shared" si="0"/>
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="G7" s="15">
         <f t="shared" si="1"/>
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="H7" s="15">
         <f t="shared" si="2"/>
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="I7" s="15">
         <f t="shared" si="3"/>
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="J7" s="15">
         <f t="shared" si="4"/>
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="K7" s="15">
         <f t="shared" si="5"/>
-        <v>288</v>
+        <v>240</v>
       </c>
       <c r="L7" s="15">
         <f t="shared" si="6"/>
-        <v>540</v>
+        <v>450</v>
       </c>
       <c r="M7" s="15">
         <f t="shared" si="7"/>
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="N7" s="15">
         <f t="shared" si="8"/>
-        <v>192</v>
-      </c>
-    </row>
-    <row r="8" ht="31.95" customHeight="1" spans="1:14">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="31.95" customHeight="1">
       <c r="A8" s="12">
         <v>74</v>
       </c>
@@ -3799,46 +3226,46 @@
       </c>
       <c r="E8" s="15">
         <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A8/配置!$B$6,0),1),配置!$B$7),0)</f>
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="F8" s="15">
         <f t="shared" si="0"/>
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="G8" s="15">
         <f t="shared" si="1"/>
-        <v>262</v>
+        <v>220</v>
       </c>
       <c r="H8" s="15">
         <f t="shared" si="2"/>
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="I8" s="15">
         <f t="shared" si="3"/>
-        <v>197</v>
+        <v>165</v>
       </c>
       <c r="J8" s="15">
         <f t="shared" si="4"/>
-        <v>197</v>
+        <v>165</v>
       </c>
       <c r="K8" s="15">
         <f t="shared" si="5"/>
-        <v>393</v>
+        <v>330</v>
       </c>
       <c r="L8" s="15">
         <f t="shared" si="6"/>
-        <v>737</v>
+        <v>619</v>
       </c>
       <c r="M8" s="15">
         <f t="shared" si="7"/>
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="N8" s="15">
         <f t="shared" si="8"/>
-        <v>262</v>
-      </c>
-    </row>
-    <row r="9" ht="31.95" customHeight="1" spans="1:14">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="31.95" customHeight="1">
       <c r="A9" s="12">
         <v>80</v>
       </c>
@@ -3853,46 +3280,46 @@
       </c>
       <c r="E9" s="15">
         <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A9/配置!$B$6,0),1),配置!$B$7),0)</f>
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="F9" s="15">
         <f t="shared" si="0"/>
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="G9" s="15">
         <f t="shared" si="1"/>
-        <v>300</v>
+        <v>254</v>
       </c>
       <c r="H9" s="15">
         <f t="shared" si="2"/>
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="I9" s="15">
         <f t="shared" si="3"/>
-        <v>225</v>
+        <v>191</v>
       </c>
       <c r="J9" s="15">
         <f t="shared" si="4"/>
-        <v>225</v>
+        <v>191</v>
       </c>
       <c r="K9" s="15">
         <f t="shared" si="5"/>
-        <v>450</v>
+        <v>381</v>
       </c>
       <c r="L9" s="15">
         <f t="shared" si="6"/>
-        <v>844</v>
+        <v>714</v>
       </c>
       <c r="M9" s="15">
         <f t="shared" si="7"/>
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="N9" s="15">
         <f t="shared" si="8"/>
-        <v>300</v>
-      </c>
-    </row>
-    <row r="10" ht="31.95" customHeight="1" spans="1:14">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="31.95" customHeight="1">
       <c r="A10" s="12">
         <v>86</v>
       </c>
@@ -3907,46 +3334,46 @@
       </c>
       <c r="E10" s="15">
         <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A10/配置!$B$6,0),1),配置!$B$7),0)</f>
-        <v>171</v>
+        <v>145</v>
       </c>
       <c r="F10" s="15">
         <f t="shared" si="0"/>
-        <v>171</v>
+        <v>145</v>
       </c>
       <c r="G10" s="15">
         <f t="shared" si="1"/>
-        <v>342</v>
+        <v>290</v>
       </c>
       <c r="H10" s="15">
         <f t="shared" si="2"/>
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="I10" s="15">
         <f t="shared" si="3"/>
-        <v>257</v>
+        <v>218</v>
       </c>
       <c r="J10" s="15">
         <f t="shared" si="4"/>
-        <v>257</v>
+        <v>218</v>
       </c>
       <c r="K10" s="15">
         <f t="shared" si="5"/>
-        <v>513</v>
+        <v>435</v>
       </c>
       <c r="L10" s="15">
         <f t="shared" si="6"/>
-        <v>962</v>
+        <v>816</v>
       </c>
       <c r="M10" s="15">
         <f t="shared" si="7"/>
-        <v>171</v>
+        <v>145</v>
       </c>
       <c r="N10" s="15">
         <f t="shared" si="8"/>
-        <v>342</v>
-      </c>
-    </row>
-    <row r="11" ht="31.95" customHeight="1" spans="1:14">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="31.95" customHeight="1">
       <c r="A11" s="12">
         <v>94</v>
       </c>
@@ -3961,46 +3388,46 @@
       </c>
       <c r="E11" s="15">
         <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A11/配置!$B$6,0),1),配置!$B$7),0)</f>
-        <v>202</v>
+        <v>172</v>
       </c>
       <c r="F11" s="15">
         <f t="shared" si="0"/>
-        <v>202</v>
+        <v>172</v>
       </c>
       <c r="G11" s="15">
         <f t="shared" si="1"/>
-        <v>404</v>
+        <v>344</v>
       </c>
       <c r="H11" s="15">
         <f t="shared" si="2"/>
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="I11" s="15">
         <f t="shared" si="3"/>
-        <v>303</v>
+        <v>258</v>
       </c>
       <c r="J11" s="15">
         <f t="shared" si="4"/>
-        <v>303</v>
+        <v>258</v>
       </c>
       <c r="K11" s="15">
         <f t="shared" si="5"/>
-        <v>606</v>
+        <v>516</v>
       </c>
       <c r="L11" s="15">
         <f t="shared" si="6"/>
-        <v>1136</v>
+        <v>968</v>
       </c>
       <c r="M11" s="15">
         <f t="shared" si="7"/>
-        <v>202</v>
+        <v>172</v>
       </c>
       <c r="N11" s="15">
         <f t="shared" si="8"/>
-        <v>404</v>
-      </c>
-    </row>
-    <row r="12" ht="31.95" customHeight="1" spans="1:14">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="31.95" customHeight="1">
       <c r="A12" s="12">
         <v>102</v>
       </c>
@@ -4015,46 +3442,46 @@
       </c>
       <c r="E12" s="15">
         <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A12/配置!$B$6,0),1),配置!$B$7),0)</f>
-        <v>235</v>
+        <v>201</v>
       </c>
       <c r="F12" s="15">
         <f t="shared" si="0"/>
-        <v>235</v>
+        <v>201</v>
       </c>
       <c r="G12" s="15">
         <f t="shared" si="1"/>
-        <v>470</v>
+        <v>402</v>
       </c>
       <c r="H12" s="15">
         <f t="shared" si="2"/>
-        <v>176</v>
+        <v>151</v>
       </c>
       <c r="I12" s="15">
         <f t="shared" si="3"/>
-        <v>353</v>
+        <v>302</v>
       </c>
       <c r="J12" s="15">
         <f t="shared" si="4"/>
-        <v>353</v>
+        <v>302</v>
       </c>
       <c r="K12" s="15">
         <f t="shared" si="5"/>
-        <v>705</v>
+        <v>603</v>
       </c>
       <c r="L12" s="15">
         <f t="shared" si="6"/>
-        <v>1322</v>
+        <v>1131</v>
       </c>
       <c r="M12" s="15">
         <f t="shared" si="7"/>
-        <v>235</v>
+        <v>201</v>
       </c>
       <c r="N12" s="15">
         <f t="shared" si="8"/>
-        <v>470</v>
-      </c>
-    </row>
-    <row r="13" ht="31.95" customHeight="1" spans="1:14">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="31.95" customHeight="1">
       <c r="A13" s="12">
         <v>110</v>
       </c>
@@ -4069,46 +3496,46 @@
       </c>
       <c r="E13" s="15">
         <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A13/配置!$B$6,0),1),配置!$B$7),0)</f>
-        <v>271</v>
+        <v>233</v>
       </c>
       <c r="F13" s="15">
         <f t="shared" si="0"/>
-        <v>271</v>
+        <v>233</v>
       </c>
       <c r="G13" s="15">
         <f t="shared" si="1"/>
-        <v>542</v>
+        <v>466</v>
       </c>
       <c r="H13" s="15">
         <f t="shared" si="2"/>
-        <v>203</v>
+        <v>175</v>
       </c>
       <c r="I13" s="15">
         <f t="shared" si="3"/>
-        <v>407</v>
+        <v>350</v>
       </c>
       <c r="J13" s="15">
         <f t="shared" si="4"/>
-        <v>407</v>
+        <v>350</v>
       </c>
       <c r="K13" s="15">
         <f t="shared" si="5"/>
-        <v>813</v>
+        <v>699</v>
       </c>
       <c r="L13" s="15">
         <f t="shared" si="6"/>
-        <v>1524</v>
+        <v>1311</v>
       </c>
       <c r="M13" s="15">
         <f t="shared" si="7"/>
-        <v>271</v>
+        <v>233</v>
       </c>
       <c r="N13" s="15">
         <f t="shared" si="8"/>
-        <v>542</v>
-      </c>
-    </row>
-    <row r="14" ht="31.95" customHeight="1" spans="1:14">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="31.95" customHeight="1">
       <c r="A14" s="12">
         <v>118</v>
       </c>
@@ -4123,46 +3550,46 @@
       </c>
       <c r="E14" s="15">
         <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A14/配置!$B$6,0),1),配置!$B$7),0)</f>
-        <v>309</v>
+        <v>268</v>
       </c>
       <c r="F14" s="15">
         <f t="shared" si="0"/>
-        <v>309</v>
+        <v>268</v>
       </c>
       <c r="G14" s="15">
         <f t="shared" si="1"/>
-        <v>618</v>
+        <v>536</v>
       </c>
       <c r="H14" s="15">
         <f t="shared" si="2"/>
-        <v>232</v>
+        <v>201</v>
       </c>
       <c r="I14" s="15">
         <f t="shared" si="3"/>
-        <v>464</v>
+        <v>402</v>
       </c>
       <c r="J14" s="15">
         <f t="shared" si="4"/>
-        <v>464</v>
+        <v>402</v>
       </c>
       <c r="K14" s="15">
         <f t="shared" si="5"/>
-        <v>927</v>
+        <v>804</v>
       </c>
       <c r="L14" s="15">
         <f t="shared" si="6"/>
-        <v>1738</v>
+        <v>1508</v>
       </c>
       <c r="M14" s="15">
         <f t="shared" si="7"/>
-        <v>309</v>
+        <v>268</v>
       </c>
       <c r="N14" s="15">
         <f t="shared" si="8"/>
-        <v>618</v>
-      </c>
-    </row>
-    <row r="15" ht="31.95" customHeight="1" spans="1:14">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="31.95" customHeight="1">
       <c r="A15" s="12">
         <v>126</v>
       </c>
@@ -4177,46 +3604,46 @@
       </c>
       <c r="E15" s="15">
         <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A15/配置!$B$6,0),1),配置!$B$7),0)</f>
-        <v>350</v>
+        <v>305</v>
       </c>
       <c r="F15" s="15">
         <f t="shared" si="0"/>
-        <v>350</v>
+        <v>305</v>
       </c>
       <c r="G15" s="15">
         <f t="shared" si="1"/>
-        <v>700</v>
+        <v>610</v>
       </c>
       <c r="H15" s="15">
         <f t="shared" si="2"/>
-        <v>263</v>
+        <v>229</v>
       </c>
       <c r="I15" s="15">
         <f t="shared" si="3"/>
-        <v>525</v>
+        <v>458</v>
       </c>
       <c r="J15" s="15">
         <f t="shared" si="4"/>
-        <v>525</v>
+        <v>458</v>
       </c>
       <c r="K15" s="15">
         <f t="shared" si="5"/>
-        <v>1050</v>
+        <v>915</v>
       </c>
       <c r="L15" s="15">
         <f t="shared" si="6"/>
-        <v>1969</v>
+        <v>1716</v>
       </c>
       <c r="M15" s="15">
         <f t="shared" si="7"/>
-        <v>350</v>
+        <v>305</v>
       </c>
       <c r="N15" s="15">
         <f t="shared" si="8"/>
-        <v>700</v>
-      </c>
-    </row>
-    <row r="16" ht="31.95" customHeight="1" spans="1:14">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="31.95" customHeight="1">
       <c r="A16" s="16">
         <v>135</v>
       </c>
@@ -4231,48 +3658,48 @@
       </c>
       <c r="E16" s="19">
         <f>ROUND(配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A16/配置!$B$6,0),1),配置!$B$7),0)</f>
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="F16" s="19">
         <f t="shared" si="0"/>
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="G16" s="19">
         <f t="shared" si="1"/>
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="H16" s="19">
         <f t="shared" si="2"/>
-        <v>300</v>
+        <v>263</v>
       </c>
       <c r="I16" s="19">
         <f t="shared" si="3"/>
-        <v>600</v>
+        <v>525</v>
       </c>
       <c r="J16" s="19">
         <f t="shared" si="4"/>
-        <v>600</v>
+        <v>525</v>
       </c>
       <c r="K16" s="19">
         <f t="shared" si="5"/>
-        <v>1200</v>
+        <v>1050</v>
       </c>
       <c r="L16" s="19">
         <f t="shared" si="6"/>
-        <v>2250</v>
+        <v>1969</v>
       </c>
       <c r="M16" s="19">
         <f t="shared" si="7"/>
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="N16" s="19">
         <f t="shared" si="8"/>
-        <v>800</v>
+        <v>700</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -4280,16 +3707,15 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="92" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:2">
+    <row r="1" spans="1:2" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>101</v>
       </c>
@@ -4297,7 +3723,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" ht="42" customHeight="1" spans="1:2">
+    <row r="2" spans="1:2" ht="42" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>102</v>
       </c>
@@ -4305,7 +3731,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="3" ht="42" customHeight="1" spans="1:2">
+    <row r="3" spans="1:2" ht="42" customHeight="1">
       <c r="A3" s="4" t="s">
         <v>104</v>
       </c>
@@ -4313,7 +3739,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="4" ht="42" customHeight="1" spans="1:2">
+    <row r="4" spans="1:2" ht="42" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>106</v>
       </c>
@@ -4321,7 +3747,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="5" ht="42" customHeight="1" spans="1:2">
+    <row r="5" spans="1:2" ht="42" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>108</v>
       </c>
@@ -4329,7 +3755,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="6" ht="42" customHeight="1" spans="1:2">
+    <row r="6" spans="1:2" ht="42" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>110</v>
       </c>
@@ -4337,7 +3763,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="7" ht="42" customHeight="1" spans="1:2">
+    <row r="7" spans="1:2" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>112</v>
       </c>
@@ -4345,7 +3771,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="8" ht="42" customHeight="1" spans="1:2">
+    <row r="8" spans="1:2" ht="42" customHeight="1">
       <c r="A8" s="4" t="s">
         <v>114</v>
       </c>
@@ -4353,7 +3779,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="9" ht="42" customHeight="1" spans="1:2">
+    <row r="9" spans="1:2" ht="42" customHeight="1">
       <c r="A9" s="4" t="s">
         <v>116</v>
       </c>
@@ -4361,7 +3787,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="10" ht="42" customHeight="1" spans="1:2">
+    <row r="10" spans="1:2" ht="42" customHeight="1">
       <c r="A10" s="6" t="s">
         <v>118</v>
       </c>
@@ -4370,11 +3796,11 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/balance_tables/时间轴.xlsx
+++ b/balance_tables/时间轴.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gameproduct\小厨西\balance_tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A97B32CF-CACC-4E0D-83B0-F888D2A16E89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{144B9947-F99F-4B1A-80FE-D6891D01CD86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -900,14 +900,14 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1132,19 +1132,19 @@
                   <c:v>277</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>7227</c:v>
+                  <c:v>465</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>29035</c:v>
+                  <c:v>1510</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>56076</c:v>
+                  <c:v>3740</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>86653</c:v>
+                  <c:v>7223</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>120000</c:v>
+                  <c:v>12000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1636,7 +1636,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="37.950000000000003" customHeight="1">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="46" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="45"/>
@@ -1697,7 +1697,7 @@
       <c r="Q3" s="45"/>
     </row>
     <row r="5" spans="1:17" ht="30" customHeight="1">
-      <c r="A5" s="46" t="s">
+      <c r="A5" s="47" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="45"/>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="B9" s="22">
         <f>配置!B8</f>
-        <v>120000</v>
+        <v>12000</v>
       </c>
       <c r="D9" s="17" t="s">
         <v>13</v>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="I11" s="12">
         <f>ROUND(IF(H11&lt;=配置!$B$6,配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(H11/配置!$B$6,0),1),配置!$B$7),配置!$B$5+(配置!$B$8-配置!$B$5)*POWER(MIN(MAX((H11-配置!$B$6)/(配置!$B$9-配置!$B$6),0),1),配置!$B$10)),0)</f>
-        <v>7227</v>
+        <v>465</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="15" customHeight="1">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="I12" s="12">
         <f>ROUND(IF(H12&lt;=配置!$B$6,配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(H12/配置!$B$6,0),1),配置!$B$7),配置!$B$5+(配置!$B$8-配置!$B$5)*POWER(MIN(MAX((H12-配置!$B$6)/(配置!$B$9-配置!$B$6),0),1),配置!$B$10)),0)</f>
-        <v>29035</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="15" customHeight="1">
@@ -1857,7 +1857,7 @@
       </c>
       <c r="I13" s="12">
         <f>ROUND(IF(H13&lt;=配置!$B$6,配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(H13/配置!$B$6,0),1),配置!$B$7),配置!$B$5+(配置!$B$8-配置!$B$5)*POWER(MIN(MAX((H13-配置!$B$6)/(配置!$B$9-配置!$B$6),0),1),配置!$B$10)),0)</f>
-        <v>56076</v>
+        <v>3740</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="15" customHeight="1">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="I14" s="12">
         <f>ROUND(IF(H14&lt;=配置!$B$6,配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(H14/配置!$B$6,0),1),配置!$B$7),配置!$B$5+(配置!$B$8-配置!$B$5)*POWER(MIN(MAX((H14-配置!$B$6)/(配置!$B$9-配置!$B$6),0),1),配置!$B$10)),0)</f>
-        <v>86653</v>
+        <v>7223</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="15" customHeight="1">
@@ -1877,11 +1877,11 @@
       </c>
       <c r="I15" s="15">
         <f>ROUND(IF(H15&lt;=配置!$B$6,配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(H15/配置!$B$6,0),1),配置!$B$7),配置!$B$5+(配置!$B$8-配置!$B$5)*POWER(MIN(MAX((H15-配置!$B$6)/(配置!$B$9-配置!$B$6),0),1),配置!$B$10)),0)</f>
-        <v>120000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="20" spans="1:17" ht="28.05" customHeight="1">
-      <c r="A20" s="46" t="s">
+      <c r="A20" s="47" t="s">
         <v>16</v>
       </c>
       <c r="B20" s="45"/>
@@ -1929,7 +1929,7 @@
       <c r="I21" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="J21" s="47" t="s">
+      <c r="J21" s="48" t="s">
         <v>25</v>
       </c>
       <c r="K21" s="45"/>
@@ -2521,27 +2521,27 @@
       </c>
       <c r="D35" s="12">
         <f>事件!E15</f>
-        <v>7227</v>
+        <v>465</v>
       </c>
       <c r="E35" s="12">
         <f>事件!F15</f>
-        <v>7227</v>
+        <v>465</v>
       </c>
       <c r="F35" s="12">
         <f>事件!G15</f>
-        <v>14454</v>
+        <v>930</v>
       </c>
       <c r="G35" s="12">
         <f>事件!H15</f>
-        <v>5420</v>
+        <v>349</v>
       </c>
       <c r="H35" s="12">
         <f>事件!K15</f>
-        <v>21681</v>
+        <v>1395</v>
       </c>
       <c r="I35" s="26" t="str">
         <f>TEXT(事件!M15,"0")&amp;"–"&amp;TEXT(事件!N15,"0")</f>
-        <v>7227–14454</v>
+        <v>465–930</v>
       </c>
     </row>
     <row r="36" spans="1:17" ht="15" customHeight="1">
@@ -2559,31 +2559,31 @@
       </c>
       <c r="D36" s="15">
         <f>事件!E16</f>
-        <v>15116</v>
+        <v>747</v>
       </c>
       <c r="E36" s="15">
         <f>事件!F16</f>
-        <v>15116</v>
+        <v>747</v>
       </c>
       <c r="F36" s="15">
         <f>事件!G16</f>
-        <v>30232</v>
+        <v>1494</v>
       </c>
       <c r="G36" s="15">
         <f>事件!H16</f>
-        <v>11337</v>
+        <v>560</v>
       </c>
       <c r="H36" s="15">
         <f>事件!K16</f>
-        <v>45348</v>
+        <v>2241</v>
       </c>
       <c r="I36" s="27" t="str">
         <f>TEXT(事件!M16,"0")&amp;"–"&amp;TEXT(事件!N16,"0")</f>
-        <v>15116–30232</v>
+        <v>747–1494</v>
       </c>
     </row>
     <row r="38" spans="1:17" ht="28.05" customHeight="1">
-      <c r="A38" s="46" t="s">
+      <c r="A38" s="47" t="s">
         <v>36</v>
       </c>
       <c r="B38" s="45"/>
@@ -2856,7 +2856,7 @@
         <v>74</v>
       </c>
       <c r="B8" s="43">
-        <v>120000</v>
+        <v>12000</v>
       </c>
       <c r="C8" t="s">
         <v>75</v>
@@ -2890,7 +2890,7 @@
         <v>82</v>
       </c>
       <c r="B10" s="43">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="C10" t="s">
         <v>83</v>
@@ -3805,43 +3805,43 @@
       </c>
       <c r="E15" s="12">
         <f>ROUND(IF(A15&lt;=配置!$B$6,配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A15/配置!$B$6,0),1),配置!$B$7),配置!$B$5+(配置!$B$8-配置!$B$5)*POWER(MIN(MAX((A15-配置!$B$6)/(配置!$B$9-配置!$B$6),0),1),配置!$B$10)),0)</f>
-        <v>7227</v>
+        <v>465</v>
       </c>
       <c r="F15" s="12">
         <f t="shared" si="0"/>
-        <v>7227</v>
+        <v>465</v>
       </c>
       <c r="G15" s="12">
         <f t="shared" si="1"/>
-        <v>14454</v>
+        <v>930</v>
       </c>
       <c r="H15" s="12">
         <f t="shared" si="2"/>
-        <v>5420</v>
+        <v>349</v>
       </c>
       <c r="I15" s="12">
         <f t="shared" si="3"/>
-        <v>10841</v>
+        <v>698</v>
       </c>
       <c r="J15" s="12">
         <f t="shared" si="4"/>
-        <v>10841</v>
+        <v>698</v>
       </c>
       <c r="K15" s="12">
         <f t="shared" si="5"/>
-        <v>21681</v>
+        <v>1395</v>
       </c>
       <c r="L15" s="12">
         <f t="shared" si="6"/>
-        <v>40652</v>
+        <v>2616</v>
       </c>
       <c r="M15" s="12">
         <f t="shared" si="7"/>
-        <v>7227</v>
+        <v>465</v>
       </c>
       <c r="N15" s="12">
         <f t="shared" si="8"/>
-        <v>14454</v>
+        <v>930</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="31.95" customHeight="1">
@@ -3859,43 +3859,43 @@
       </c>
       <c r="E16" s="15">
         <f>ROUND(IF(A16&lt;=配置!$B$6,配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A16/配置!$B$6,0),1),配置!$B$7),配置!$B$5+(配置!$B$8-配置!$B$5)*POWER(MIN(MAX((A16-配置!$B$6)/(配置!$B$9-配置!$B$6),0),1),配置!$B$10)),0)</f>
-        <v>15116</v>
+        <v>747</v>
       </c>
       <c r="F16" s="15">
         <f t="shared" si="0"/>
-        <v>15116</v>
+        <v>747</v>
       </c>
       <c r="G16" s="15">
         <f t="shared" si="1"/>
-        <v>30232</v>
+        <v>1494</v>
       </c>
       <c r="H16" s="15">
         <f t="shared" si="2"/>
-        <v>11337</v>
+        <v>560</v>
       </c>
       <c r="I16" s="15">
         <f t="shared" si="3"/>
-        <v>22674</v>
+        <v>1121</v>
       </c>
       <c r="J16" s="15">
         <f t="shared" si="4"/>
-        <v>22674</v>
+        <v>1121</v>
       </c>
       <c r="K16" s="15">
         <f t="shared" si="5"/>
-        <v>45348</v>
+        <v>2241</v>
       </c>
       <c r="L16" s="15">
         <f t="shared" si="6"/>
-        <v>85028</v>
+        <v>4202</v>
       </c>
       <c r="M16" s="15">
         <f t="shared" si="7"/>
-        <v>15116</v>
+        <v>747</v>
       </c>
       <c r="N16" s="15">
         <f t="shared" si="8"/>
-        <v>30232</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="22.05" customHeight="1">
@@ -3913,43 +3913,43 @@
       </c>
       <c r="E17" s="39">
         <f>ROUND(IF(A17&lt;=配置!$B$6,配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A17/配置!$B$6,0),1),配置!$B$7),配置!$B$5+(配置!$B$8-配置!$B$5)*POWER(MIN(MAX((A17-配置!$B$6)/(配置!$B$9-配置!$B$6),0),1),配置!$B$10)),0)</f>
-        <v>24166</v>
+        <v>1209</v>
       </c>
       <c r="F17" s="40">
         <f t="shared" si="0"/>
-        <v>24166</v>
+        <v>1209</v>
       </c>
       <c r="G17" s="40">
         <f t="shared" si="1"/>
-        <v>48332</v>
+        <v>2418</v>
       </c>
       <c r="H17" s="40">
         <f t="shared" si="2"/>
-        <v>18125</v>
+        <v>907</v>
       </c>
       <c r="I17" s="40">
         <f t="shared" si="3"/>
-        <v>36249</v>
+        <v>1814</v>
       </c>
       <c r="J17" s="40">
         <f t="shared" si="4"/>
-        <v>36249</v>
+        <v>1814</v>
       </c>
       <c r="K17" s="40">
         <f t="shared" si="5"/>
-        <v>72498</v>
+        <v>3627</v>
       </c>
       <c r="L17" s="40">
         <f t="shared" si="6"/>
-        <v>135934</v>
+        <v>6801</v>
       </c>
       <c r="M17" s="40">
         <f t="shared" si="7"/>
-        <v>24166</v>
+        <v>1209</v>
       </c>
       <c r="N17" s="41">
         <f t="shared" si="8"/>
-        <v>48332</v>
+        <v>2418</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="22.05" customHeight="1">
@@ -3967,43 +3967,43 @@
       </c>
       <c r="E18" s="39">
         <f>ROUND(IF(A18&lt;=配置!$B$6,配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A18/配置!$B$6,0),1),配置!$B$7),配置!$B$5+(配置!$B$8-配置!$B$5)*POWER(MIN(MAX((A18-配置!$B$6)/(配置!$B$9-配置!$B$6),0),1),配置!$B$10)),0)</f>
-        <v>34104</v>
+        <v>1858</v>
       </c>
       <c r="F18" s="40">
         <f t="shared" si="0"/>
-        <v>34104</v>
+        <v>1858</v>
       </c>
       <c r="G18" s="40">
         <f t="shared" si="1"/>
-        <v>68208</v>
+        <v>3716</v>
       </c>
       <c r="H18" s="40">
         <f t="shared" si="2"/>
-        <v>25578</v>
+        <v>1394</v>
       </c>
       <c r="I18" s="40">
         <f t="shared" si="3"/>
-        <v>51156</v>
+        <v>2787</v>
       </c>
       <c r="J18" s="40">
         <f t="shared" si="4"/>
-        <v>51156</v>
+        <v>2787</v>
       </c>
       <c r="K18" s="40">
         <f t="shared" si="5"/>
-        <v>102312</v>
+        <v>5574</v>
       </c>
       <c r="L18" s="40">
         <f t="shared" si="6"/>
-        <v>191835</v>
+        <v>10451</v>
       </c>
       <c r="M18" s="40">
         <f t="shared" si="7"/>
-        <v>34104</v>
+        <v>1858</v>
       </c>
       <c r="N18" s="41">
         <f t="shared" si="8"/>
-        <v>68208</v>
+        <v>3716</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="22.05" customHeight="1">
@@ -4021,43 +4021,43 @@
       </c>
       <c r="E19" s="39">
         <f>ROUND(IF(A19&lt;=配置!$B$6,配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A19/配置!$B$6,0),1),配置!$B$7),配置!$B$5+(配置!$B$8-配置!$B$5)*POWER(MIN(MAX((A19-配置!$B$6)/(配置!$B$9-配置!$B$6),0),1),配置!$B$10)),0)</f>
-        <v>44774</v>
+        <v>2701</v>
       </c>
       <c r="F19" s="40">
         <f t="shared" si="0"/>
-        <v>44774</v>
+        <v>2701</v>
       </c>
       <c r="G19" s="40">
         <f t="shared" si="1"/>
-        <v>89548</v>
+        <v>5402</v>
       </c>
       <c r="H19" s="40">
         <f t="shared" si="2"/>
-        <v>33581</v>
+        <v>2026</v>
       </c>
       <c r="I19" s="40">
         <f t="shared" si="3"/>
-        <v>67161</v>
+        <v>4052</v>
       </c>
       <c r="J19" s="40">
         <f t="shared" si="4"/>
-        <v>67161</v>
+        <v>4052</v>
       </c>
       <c r="K19" s="40">
         <f t="shared" si="5"/>
-        <v>134322</v>
+        <v>8103</v>
       </c>
       <c r="L19" s="40">
         <f t="shared" si="6"/>
-        <v>251854</v>
+        <v>15193</v>
       </c>
       <c r="M19" s="40">
         <f t="shared" si="7"/>
-        <v>44774</v>
+        <v>2701</v>
       </c>
       <c r="N19" s="41">
         <f t="shared" si="8"/>
-        <v>89548</v>
+        <v>5402</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="22.05" customHeight="1">
@@ -4075,43 +4075,43 @@
       </c>
       <c r="E20" s="39">
         <f>ROUND(IF(A20&lt;=配置!$B$6,配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A20/配置!$B$6,0),1),配置!$B$7),配置!$B$5+(配置!$B$8-配置!$B$5)*POWER(MIN(MAX((A20-配置!$B$6)/(配置!$B$9-配置!$B$6),0),1),配置!$B$10)),0)</f>
-        <v>54152</v>
+        <v>3553</v>
       </c>
       <c r="F20" s="40">
         <f t="shared" si="0"/>
-        <v>54152</v>
+        <v>3553</v>
       </c>
       <c r="G20" s="40">
         <f t="shared" si="1"/>
-        <v>108304</v>
+        <v>7106</v>
       </c>
       <c r="H20" s="40">
         <f t="shared" si="2"/>
-        <v>40614</v>
+        <v>2665</v>
       </c>
       <c r="I20" s="40">
         <f t="shared" si="3"/>
-        <v>81228</v>
+        <v>5330</v>
       </c>
       <c r="J20" s="40">
         <f t="shared" si="4"/>
-        <v>81228</v>
+        <v>5330</v>
       </c>
       <c r="K20" s="40">
         <f t="shared" si="5"/>
-        <v>162456</v>
+        <v>10659</v>
       </c>
       <c r="L20" s="40">
         <f t="shared" si="6"/>
-        <v>304605</v>
+        <v>19986</v>
       </c>
       <c r="M20" s="40">
         <f t="shared" si="7"/>
-        <v>54152</v>
+        <v>3553</v>
       </c>
       <c r="N20" s="41">
         <f t="shared" si="8"/>
-        <v>108304</v>
+        <v>7106</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="22.05" customHeight="1">
@@ -4129,43 +4129,43 @@
       </c>
       <c r="E21" s="39">
         <f>ROUND(IF(A21&lt;=配置!$B$6,配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A21/配置!$B$6,0),1),配置!$B$7),配置!$B$5+(配置!$B$8-配置!$B$5)*POWER(MIN(MAX((A21-配置!$B$6)/(配置!$B$9-配置!$B$6),0),1),配置!$B$10)),0)</f>
-        <v>56076</v>
+        <v>3740</v>
       </c>
       <c r="F21" s="40">
         <f t="shared" si="0"/>
-        <v>56076</v>
+        <v>3740</v>
       </c>
       <c r="G21" s="40">
         <f t="shared" si="1"/>
-        <v>112152</v>
+        <v>7480</v>
       </c>
       <c r="H21" s="40">
         <f t="shared" si="2"/>
-        <v>42057</v>
+        <v>2805</v>
       </c>
       <c r="I21" s="40">
         <f t="shared" si="3"/>
-        <v>84114</v>
+        <v>5610</v>
       </c>
       <c r="J21" s="40">
         <f t="shared" si="4"/>
-        <v>84114</v>
+        <v>5610</v>
       </c>
       <c r="K21" s="40">
         <f t="shared" si="5"/>
-        <v>168228</v>
+        <v>11220</v>
       </c>
       <c r="L21" s="40">
         <f t="shared" si="6"/>
-        <v>315428</v>
+        <v>21038</v>
       </c>
       <c r="M21" s="40">
         <f t="shared" si="7"/>
-        <v>56076</v>
+        <v>3740</v>
       </c>
       <c r="N21" s="41">
         <f t="shared" si="8"/>
-        <v>112152</v>
+        <v>7480</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="22.05" customHeight="1">
@@ -4183,43 +4183,43 @@
       </c>
       <c r="E22" s="39">
         <f>ROUND(IF(A22&lt;=配置!$B$6,配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A22/配置!$B$6,0),1),配置!$B$7),配置!$B$5+(配置!$B$8-配置!$B$5)*POWER(MIN(MAX((A22-配置!$B$6)/(配置!$B$9-配置!$B$6),0),1),配置!$B$10)),0)</f>
-        <v>67936</v>
+        <v>4980</v>
       </c>
       <c r="F22" s="40">
         <f t="shared" si="0"/>
-        <v>67936</v>
+        <v>4980</v>
       </c>
       <c r="G22" s="40">
         <f t="shared" si="1"/>
-        <v>135872</v>
+        <v>9960</v>
       </c>
       <c r="H22" s="40">
         <f t="shared" si="2"/>
-        <v>50952</v>
+        <v>3735</v>
       </c>
       <c r="I22" s="40">
         <f t="shared" si="3"/>
-        <v>101904</v>
+        <v>7470</v>
       </c>
       <c r="J22" s="40">
         <f t="shared" si="4"/>
-        <v>101904</v>
+        <v>7470</v>
       </c>
       <c r="K22" s="40">
         <f t="shared" si="5"/>
-        <v>203808</v>
+        <v>14940</v>
       </c>
       <c r="L22" s="40">
         <f t="shared" si="6"/>
-        <v>382140</v>
+        <v>28013</v>
       </c>
       <c r="M22" s="40">
         <f t="shared" si="7"/>
-        <v>67936</v>
+        <v>4980</v>
       </c>
       <c r="N22" s="41">
         <f t="shared" si="8"/>
-        <v>135872</v>
+        <v>9960</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="22.05" customHeight="1">
@@ -4237,43 +4237,43 @@
       </c>
       <c r="E23" s="39">
         <f>ROUND(IF(A23&lt;=配置!$B$6,配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A23/配置!$B$6,0),1),配置!$B$7),配置!$B$5+(配置!$B$8-配置!$B$5)*POWER(MIN(MAX((A23-配置!$B$6)/(配置!$B$9-配置!$B$6),0),1),配置!$B$10)),0)</f>
-        <v>80297</v>
+        <v>6424</v>
       </c>
       <c r="F23" s="40">
         <f t="shared" si="0"/>
-        <v>80297</v>
+        <v>6424</v>
       </c>
       <c r="G23" s="40">
         <f t="shared" si="1"/>
-        <v>160594</v>
+        <v>12848</v>
       </c>
       <c r="H23" s="40">
         <f t="shared" si="2"/>
-        <v>60223</v>
+        <v>4818</v>
       </c>
       <c r="I23" s="40">
         <f t="shared" si="3"/>
-        <v>120446</v>
+        <v>9636</v>
       </c>
       <c r="J23" s="40">
         <f t="shared" si="4"/>
-        <v>120446</v>
+        <v>9636</v>
       </c>
       <c r="K23" s="40">
         <f t="shared" si="5"/>
-        <v>240891</v>
+        <v>19272</v>
       </c>
       <c r="L23" s="40">
         <f t="shared" si="6"/>
-        <v>451671</v>
+        <v>36135</v>
       </c>
       <c r="M23" s="40">
         <f t="shared" si="7"/>
-        <v>80297</v>
+        <v>6424</v>
       </c>
       <c r="N23" s="41">
         <f t="shared" si="8"/>
-        <v>160594</v>
+        <v>12848</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="22.05" customHeight="1">
@@ -4291,43 +4291,43 @@
       </c>
       <c r="E24" s="39">
         <f>ROUND(IF(A24&lt;=配置!$B$6,配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A24/配置!$B$6,0),1),配置!$B$7),配置!$B$5+(配置!$B$8-配置!$B$5)*POWER(MIN(MAX((A24-配置!$B$6)/(配置!$B$9-配置!$B$6),0),1),配置!$B$10)),0)</f>
-        <v>93118</v>
+        <v>8073</v>
       </c>
       <c r="F24" s="40">
         <f t="shared" si="0"/>
-        <v>93118</v>
+        <v>8073</v>
       </c>
       <c r="G24" s="40">
         <f t="shared" si="1"/>
-        <v>186236</v>
+        <v>16146</v>
       </c>
       <c r="H24" s="40">
         <f t="shared" si="2"/>
-        <v>69839</v>
+        <v>6055</v>
       </c>
       <c r="I24" s="40">
         <f t="shared" si="3"/>
-        <v>139677</v>
+        <v>12110</v>
       </c>
       <c r="J24" s="40">
         <f t="shared" si="4"/>
-        <v>139677</v>
+        <v>12110</v>
       </c>
       <c r="K24" s="40">
         <f t="shared" si="5"/>
-        <v>279354</v>
+        <v>24219</v>
       </c>
       <c r="L24" s="40">
         <f t="shared" si="6"/>
-        <v>523789</v>
+        <v>45411</v>
       </c>
       <c r="M24" s="40">
         <f t="shared" si="7"/>
-        <v>93118</v>
+        <v>8073</v>
       </c>
       <c r="N24" s="41">
         <f t="shared" si="8"/>
-        <v>186236</v>
+        <v>16146</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="22.05" customHeight="1">
@@ -4345,43 +4345,43 @@
       </c>
       <c r="E25" s="39">
         <f>ROUND(IF(A25&lt;=配置!$B$6,配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A25/配置!$B$6,0),1),配置!$B$7),配置!$B$5+(配置!$B$8-配置!$B$5)*POWER(MIN(MAX((A25-配置!$B$6)/(配置!$B$9-配置!$B$6),0),1),配置!$B$10)),0)</f>
-        <v>106362</v>
+        <v>9931</v>
       </c>
       <c r="F25" s="40">
         <f t="shared" si="0"/>
-        <v>106362</v>
+        <v>9931</v>
       </c>
       <c r="G25" s="40">
         <f t="shared" si="1"/>
-        <v>212724</v>
+        <v>19862</v>
       </c>
       <c r="H25" s="40">
         <f t="shared" si="2"/>
-        <v>79772</v>
+        <v>7448</v>
       </c>
       <c r="I25" s="40">
         <f t="shared" si="3"/>
-        <v>159543</v>
+        <v>14897</v>
       </c>
       <c r="J25" s="40">
         <f t="shared" si="4"/>
-        <v>159543</v>
+        <v>14897</v>
       </c>
       <c r="K25" s="40">
         <f t="shared" si="5"/>
-        <v>319086</v>
+        <v>29793</v>
       </c>
       <c r="L25" s="40">
         <f t="shared" si="6"/>
-        <v>598286</v>
+        <v>55862</v>
       </c>
       <c r="M25" s="40">
         <f t="shared" si="7"/>
-        <v>106362</v>
+        <v>9931</v>
       </c>
       <c r="N25" s="41">
         <f t="shared" si="8"/>
-        <v>212724</v>
+        <v>19862</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="22.05" customHeight="1">
@@ -4399,43 +4399,43 @@
       </c>
       <c r="E26" s="39">
         <f>ROUND(IF(A26&lt;=配置!$B$6,配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A26/配置!$B$6,0),1),配置!$B$7),配置!$B$5+(配置!$B$8-配置!$B$5)*POWER(MIN(MAX((A26-配置!$B$6)/(配置!$B$9-配置!$B$6),0),1),配置!$B$10)),0)</f>
-        <v>120000</v>
+        <v>12000</v>
       </c>
       <c r="F26" s="40">
         <f t="shared" si="0"/>
-        <v>120000</v>
+        <v>12000</v>
       </c>
       <c r="G26" s="40">
         <f t="shared" si="1"/>
-        <v>240000</v>
+        <v>24000</v>
       </c>
       <c r="H26" s="40">
         <f t="shared" si="2"/>
-        <v>90000</v>
+        <v>9000</v>
       </c>
       <c r="I26" s="40">
         <f t="shared" si="3"/>
-        <v>180000</v>
+        <v>18000</v>
       </c>
       <c r="J26" s="40">
         <f t="shared" si="4"/>
-        <v>180000</v>
+        <v>18000</v>
       </c>
       <c r="K26" s="40">
         <f t="shared" si="5"/>
-        <v>360000</v>
+        <v>36000</v>
       </c>
       <c r="L26" s="40">
         <f t="shared" si="6"/>
-        <v>675000</v>
+        <v>67500</v>
       </c>
       <c r="M26" s="40">
         <f t="shared" si="7"/>
-        <v>120000</v>
+        <v>12000</v>
       </c>
       <c r="N26" s="41">
         <f t="shared" si="8"/>
-        <v>240000</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="22.05" customHeight="1">
@@ -4453,43 +4453,43 @@
       </c>
       <c r="E27" s="39">
         <f>ROUND(IF(A27&lt;=配置!$B$6,配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A27/配置!$B$6,0),1),配置!$B$7),配置!$B$5+(配置!$B$8-配置!$B$5)*POWER(MIN(MAX((A27-配置!$B$6)/(配置!$B$9-配置!$B$6),0),1),配置!$B$10)),0)</f>
-        <v>120000</v>
+        <v>12000</v>
       </c>
       <c r="F27" s="40">
         <f t="shared" si="0"/>
-        <v>120000</v>
+        <v>12000</v>
       </c>
       <c r="G27" s="40">
         <f t="shared" si="1"/>
-        <v>240000</v>
+        <v>24000</v>
       </c>
       <c r="H27" s="40">
         <f t="shared" si="2"/>
-        <v>90000</v>
+        <v>9000</v>
       </c>
       <c r="I27" s="40">
         <f t="shared" si="3"/>
-        <v>180000</v>
+        <v>18000</v>
       </c>
       <c r="J27" s="40">
         <f t="shared" si="4"/>
-        <v>180000</v>
+        <v>18000</v>
       </c>
       <c r="K27" s="40">
         <f t="shared" si="5"/>
-        <v>360000</v>
+        <v>36000</v>
       </c>
       <c r="L27" s="40">
         <f t="shared" si="6"/>
-        <v>675000</v>
+        <v>67500</v>
       </c>
       <c r="M27" s="40">
         <f t="shared" si="7"/>
-        <v>120000</v>
+        <v>12000</v>
       </c>
       <c r="N27" s="41">
         <f t="shared" si="8"/>
-        <v>240000</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="22.05" customHeight="1">
@@ -4507,43 +4507,43 @@
       </c>
       <c r="E28" s="39">
         <f>ROUND(IF(A28&lt;=配置!$B$6,配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A28/配置!$B$6,0),1),配置!$B$7),配置!$B$5+(配置!$B$8-配置!$B$5)*POWER(MIN(MAX((A28-配置!$B$6)/(配置!$B$9-配置!$B$6),0),1),配置!$B$10)),0)</f>
-        <v>120000</v>
+        <v>12000</v>
       </c>
       <c r="F28" s="40">
         <f t="shared" si="0"/>
-        <v>120000</v>
+        <v>12000</v>
       </c>
       <c r="G28" s="40">
         <f t="shared" si="1"/>
-        <v>240000</v>
+        <v>24000</v>
       </c>
       <c r="H28" s="40">
         <f t="shared" si="2"/>
-        <v>90000</v>
+        <v>9000</v>
       </c>
       <c r="I28" s="40">
         <f t="shared" si="3"/>
-        <v>180000</v>
+        <v>18000</v>
       </c>
       <c r="J28" s="40">
         <f t="shared" si="4"/>
-        <v>180000</v>
+        <v>18000</v>
       </c>
       <c r="K28" s="40">
         <f t="shared" si="5"/>
-        <v>360000</v>
+        <v>36000</v>
       </c>
       <c r="L28" s="40">
         <f t="shared" si="6"/>
-        <v>675000</v>
+        <v>67500</v>
       </c>
       <c r="M28" s="40">
         <f t="shared" si="7"/>
-        <v>120000</v>
+        <v>12000</v>
       </c>
       <c r="N28" s="41">
         <f t="shared" si="8"/>
-        <v>240000</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="22.05" customHeight="1">
@@ -4561,43 +4561,43 @@
       </c>
       <c r="E29" s="39">
         <f>ROUND(IF(A29&lt;=配置!$B$6,配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A29/配置!$B$6,0),1),配置!$B$7),配置!$B$5+(配置!$B$8-配置!$B$5)*POWER(MIN(MAX((A29-配置!$B$6)/(配置!$B$9-配置!$B$6),0),1),配置!$B$10)),0)</f>
-        <v>120000</v>
+        <v>12000</v>
       </c>
       <c r="F29" s="40">
         <f t="shared" si="0"/>
-        <v>120000</v>
+        <v>12000</v>
       </c>
       <c r="G29" s="40">
         <f t="shared" si="1"/>
-        <v>240000</v>
+        <v>24000</v>
       </c>
       <c r="H29" s="40">
         <f t="shared" si="2"/>
-        <v>90000</v>
+        <v>9000</v>
       </c>
       <c r="I29" s="40">
         <f t="shared" si="3"/>
-        <v>180000</v>
+        <v>18000</v>
       </c>
       <c r="J29" s="40">
         <f t="shared" si="4"/>
-        <v>180000</v>
+        <v>18000</v>
       </c>
       <c r="K29" s="40">
         <f t="shared" si="5"/>
-        <v>360000</v>
+        <v>36000</v>
       </c>
       <c r="L29" s="40">
         <f t="shared" si="6"/>
-        <v>675000</v>
+        <v>67500</v>
       </c>
       <c r="M29" s="40">
         <f t="shared" si="7"/>
-        <v>120000</v>
+        <v>12000</v>
       </c>
       <c r="N29" s="41">
         <f t="shared" si="8"/>
-        <v>240000</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="22.05" customHeight="1">
@@ -4615,43 +4615,43 @@
       </c>
       <c r="E30" s="39">
         <f>ROUND(IF(A30&lt;=配置!$B$6,配置!$B$4+(配置!$B$5-配置!$B$4)*POWER(MIN(MAX(A30/配置!$B$6,0),1),配置!$B$7),配置!$B$5+(配置!$B$8-配置!$B$5)*POWER(MIN(MAX((A30-配置!$B$6)/(配置!$B$9-配置!$B$6),0),1),配置!$B$10)),0)</f>
-        <v>120000</v>
+        <v>12000</v>
       </c>
       <c r="F30" s="40">
         <f t="shared" si="0"/>
-        <v>120000</v>
+        <v>12000</v>
       </c>
       <c r="G30" s="40">
         <f t="shared" si="1"/>
-        <v>240000</v>
+        <v>24000</v>
       </c>
       <c r="H30" s="40">
         <f t="shared" si="2"/>
-        <v>90000</v>
+        <v>9000</v>
       </c>
       <c r="I30" s="40">
         <f t="shared" si="3"/>
-        <v>180000</v>
+        <v>18000</v>
       </c>
       <c r="J30" s="40">
         <f t="shared" si="4"/>
-        <v>180000</v>
+        <v>18000</v>
       </c>
       <c r="K30" s="40">
         <f t="shared" si="5"/>
-        <v>360000</v>
+        <v>36000</v>
       </c>
       <c r="L30" s="40">
         <f t="shared" si="6"/>
-        <v>675000</v>
+        <v>67500</v>
       </c>
       <c r="M30" s="40">
         <f t="shared" si="7"/>
-        <v>120000</v>
+        <v>12000</v>
       </c>
       <c r="N30" s="41">
         <f t="shared" si="8"/>
-        <v>240000</v>
+        <v>24000</v>
       </c>
     </row>
   </sheetData>

--- a/balance_tables/时间轴.xlsx
+++ b/balance_tables/时间轴.xlsx
@@ -752,7 +752,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
@@ -823,7 +823,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
@@ -893,9 +893,9 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TimelineEventsTable" displayName="TimelineEventsTable" ref="A1:N16" headerRowCount="1" totalsRowShown="0">
-  <tableColumns count="14">
-    <tableColumn id="1" name="请求时间(s)"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TimelineEventsTable" displayName="TimelineEventsTable" ref="A1:O14" headerRowCount="1" totalsRowShown="0">
+  <tableColumns count="15">
+    <tableColumn id="1" name="路程进度"/>
     <tableColumn id="2" name="事件ID"/>
     <tableColumn id="3" name="类型"/>
     <tableColumn id="4" name="说明"/>
@@ -929,6 +929,7 @@
     <tableColumn id="14" name="门基础最高">
       <calculatedColumnFormula>ROUND(E2*2,0)</calculatedColumnFormula>
     </tableColumn>
+    <tableColumn id="15" name="前进倍率"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>

--- a/balance_tables/时间轴.xlsx
+++ b/balance_tables/时间轴.xlsx
@@ -4116,7 +4116,7 @@
       </c>
       <c r="D2" s="15" t="inlineStr">
         <is>
-          <t>总路程0.5%处提供开局食材选择</t>
+          <t>总路程1%处提供开局食材选择</t>
         </is>
       </c>
       <c r="E2" s="89" t="n"/>
